--- a/Product Listing.xlsx
+++ b/Product Listing.xlsx
@@ -1,40 +1,124 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upload Results" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Products'!$A$1:$AB$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="9">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="18"/>
+    </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F7F7F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFD9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE5D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,19 +126,344 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>anzorlist</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>SKU
+REQUIRED
+REQUIRED. The Anzor SKU exactly as it appears on the website, e.g. R985. This is the join key: the system fetches anzorjewelrycorp.com/Scripts/prodview.asp?SKU=&lt;this&gt; and extracts everything else.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Include?
+Optional.
+Y to include this row in the next run, N to stage it without uploading. Blank counts as Y.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Marketplaces
+Optional.
+Comma-separated marketplace codes: US, CA, MX, UK, DE, FR, IT, ES, NL, SE, PL, BE, IE, JP, AU, SG. Blank uses ANZOR_MARKETPLACES from .env (default US). EU codes need a separate SP-API authorization from US/CA/MX.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Amazon Product Type
+Optional.
+Blank is recommended — it is inferred from the SKU prefix (R=RING, E=EARRING, P=PENDANT, B=BRACELET, N=NECKLACE, S=JEWELRY_SET) and confirmed against Amazon's Product Type Definitions API. Set it only to override.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Variations
+Optional.
+'site' (default) builds a parent/child variation family from the ring sizes or chain lengths on the product page. 'none' lists a single standalone item using the base size only.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Quantity
+Optional.
+Sellable units. Blank uses ANZOR_DEFAULT_QUANTITY from .env. For a made-to-order size family this applies to every child SKU.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Price Override (USD)
+Optional.
+Blank is recommended. By default the price is the website price marked up by PRICE_MARKUP_AMAZON (0.20) so the Amazon referral fee does not eat your margin. Enter a number here to set the exact Amazon price instead, bypassing the markup.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>List Price / MSRP (USD)
+Optional.
+Optional strike-through comparison price. Blank uses the website's MSRP if it has one. Amazon requires this to be a genuine former or manufacturer price.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Condition
+Optional.
+Blank means new_new (brand new). Anything else needs a condition note.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Handling Time (days)
+Optional.
+Business days between order and ship. Blank uses ANZOR_HANDLING_TIME_DAYS (3). Be honest here — late shipment rate is an account-health metric.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>UPC / EAN
+Optional.
+Leave BLANK unless you own real GS1 barcodes. Blank triggers the GTIN-exemption path, which is the correct route for own-manufactured jewelry. Never invent a barcode — Amazon verifies them against the GS1 registry.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Title Override
+Optional.
+Blank is recommended — a compliant title is generated from the extracted specs. Amazon caps jewelry titles at 200 characters and rejects ALL CAPS, promotional language ('BEST', 'SALE'), and symbols like ! $ ?.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Bullet 1
+Optional.
+Optional override for the first bullet. Blank generates one from the specs. 500 characters max, no promotional or price claims.</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Bullet 2
+Optional.
+Optional. See Bullet 1.</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Bullet 3
+Optional.
+Optional. See Bullet 1.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Bullet 4
+Optional.
+Optional. See Bullet 1.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>Bullet 5
+Optional.
+Optional. See Bullet 1.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Description Override
+Optional.
+Blank is recommended. The generated description is sanitised: shipping promises, phone numbers, competitor mentions, and site-navigation text are stripped, because Amazon suppresses listings that contain them.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Search Terms
+Optional.
+Optional backend keywords, space or comma separated, 250 bytes max for most marketplaces. Do not repeat words already in the title — Amazon ignores duplicates. No brand names you do not own, no competitor terms.</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>Metal Type
+Optional.
+Blank uses the metal parsed from the website's Item Details. Override only when the site data is wrong or ambiguous.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Metal Stamp
+Optional.
+Purity stamp such as 14k, 18k, 925, 950. Blank uses the parsed value.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Gem Type
+Optional.
+Primary stone. Blank uses the parsed value. Use 'none' for plain metal pieces. FTC rules require lab-grown and simulated stones to be disclosed — the generator copies the site's qualifier verbatim and never upgrades 'simulated' to 'genuine'.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>Total Gem Weight (ct)
+Optional.
+Total carat weight. Blank uses the parsed value. Amazon requires this to be accurate to the stated precision; over-stating carat weight is an FTC violation.</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>Metal Weight (g)
+Optional.
+Gross metal weight in grams. Blank uses the parsed value.</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <t>Target Gender
+Optional.
+Blank defaults to 'unisex'. Drives Amazon's department browse-node placement.</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
+      <text>
+        <t>Style
+Optional.
+Optional style keyword, e.g. Solitaire, Halo, Eternity, Tennis, Stud.</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
+      <text>
+        <t>Ring Sizes Override
+Optional.
+Optional comma-separated sizes, e.g. 5,5.5,6,6.5,7. Blank uses the sizes offered on the product page. Only used when Variations = site.</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0" shapeId="0">
+      <text>
+        <t>Notes (not uploaded)
+Optional.
+Free text for your own tracking. Never sent to Amazon.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -341,28 +750,2758 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="118" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Anzor Jewelry → Amazon listing sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Fill in the Products tab. Only the SKU column is required — everything else is either optional or has a sensible default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>How it works</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>1.  You enter a SKU, e.g. R985.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2.  The system fetches that product from anzorjewelrycorp.com and extracts the title, description, Item Details specs, price, images, and available ring sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>3.  It writes Amazon-compliant copy from those extracted facts, prices the item with your fee markup, hosts the images, and builds the listing payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>4.  It validates that payload against Amazon's own JSON schema for the product type, offline, before anything is sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>5.  It submits in VALIDATION_PREVIEW mode first — Amazon checks the listing and returns errors without creating anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>6.  Only after you review the preview and pass --confirm does anything go live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>The only column you must fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SKU. Everything else is an override that beats the website data. A blank cell means 'use what the site says' — it never blanks out a value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Columns worth knowing about</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Include? — set to N to keep a row in the sheet without uploading it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Marketplaces — comma-separated codes (US, CA, MX, UK, DE, ...). Blank uses your .env default. Note that the EU marketplaces need a second, separate SP-API authorization from US/CA/MX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Variations — 'site' builds a proper parent/child family from the ring sizes on the product page, so all sizes share one detail page and one review count. 'none' lists a single standalone item. Use 'none' for earrings and pendants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Price Override — leave blank. The default price is the website price plus your PRICE_MARKUP_AMAZON (20%), which absorbs Amazon's referral fee. Filling this in bypasses the markup entirely and sets the exact price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>UPC / EAN — leave blank. Blank routes the SKU through GTIN exemption, which is the correct path for jewelry you manufacture. Never invent a barcode: Amazon validates them against the GS1 registry and a fake one can suspend the account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Title / Bullet / Description overrides — leave blank unless you have a reason. Generated copy is checked against the extracted specs so it cannot claim a carat weight, metal purity, or stone origin the website does not state. Anything you type here bypasses that check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Hover any column header for its full explanation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>What to run</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>anzorlist doctor                    # check credentials and config</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>anzorlist workbook validate         # check this sheet, no network</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>anzorlist build --all               # extract, price, write copy, build payloads</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>anzorlist amazon preflight          # category gating + product-type check</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>anzorlist amazon validate           # Amazon's own dry-run, creates nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>anzorlist amazon submit --confirm   # the only command that creates listings</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Nothing is created on Amazon without --confirm, and nothing becomes buyable without a second explicit step. Every submission is recorded in a local ledger with the exact payload sent, so any listing can be traced or rolled back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>After a run, the Upload Results tab is filled in with the status, submission ID, and any Amazon-reported issue for each SKU.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="34" customWidth="1" min="28" max="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Include?</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Marketplaces</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Amazon Product Type</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Variations</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Price Override (USD)</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>List Price / MSRP (USD)</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Handling Time (days)</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>UPC / EAN</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>Title Override</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>Bullet 1</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Bullet 2</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Bullet 3</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Bullet 4</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Bullet 5</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Description Override</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>Search Terms</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>Metal Type</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>Metal Stamp</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>Gem Type</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>Total Gem Weight (ct)</t>
+        </is>
+      </c>
+      <c r="X1" s="7" t="inlineStr">
+        <is>
+          <t>Metal Weight (g)</t>
+        </is>
+      </c>
+      <c r="Y1" s="7" t="inlineStr">
+        <is>
+          <t>Target Gender</t>
+        </is>
+      </c>
+      <c r="Z1" s="7" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="AA1" s="7" t="inlineStr">
+        <is>
+          <t>Ring Sizes Override</t>
+        </is>
+      </c>
+      <c r="AB1" s="8" t="inlineStr">
+        <is>
+          <t>Notes (not uploaded)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>R985</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>new_new</t>
+        </is>
+      </c>
+      <c r="Y2" s="9" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="AB2" s="9" t="inlineStr">
+        <is>
+          <t>Example row — delete or set Include=N once you add your own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>E1154</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>new_new</t>
+        </is>
+      </c>
+      <c r="Y3" s="9" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="AB3" s="9" t="inlineStr">
+        <is>
+          <t>Example row — earrings have no size axis, so Variations = none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>S220</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>new_new</t>
+        </is>
+      </c>
+      <c r="AB4" s="9" t="inlineStr">
+        <is>
+          <t>Example row, staged (Include = N) so it is skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>E711</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>new_new</t>
+        </is>
+      </c>
+      <c r="AB5" s="9" t="inlineStr">
+        <is>
+          <t>Example row, staged (Include = N) so it is skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="n"/>
+      <c r="O6" s="12" t="n"/>
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="12" t="n"/>
+      <c r="T6" s="13" t="n"/>
+      <c r="U6" s="13" t="n"/>
+      <c r="V6" s="13" t="n"/>
+      <c r="W6" s="13" t="n"/>
+      <c r="X6" s="13" t="n"/>
+      <c r="Y6" s="13" t="n"/>
+      <c r="Z6" s="13" t="n"/>
+      <c r="AA6" s="13" t="n"/>
+      <c r="AB6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="12" t="n"/>
+      <c r="P7" s="12" t="n"/>
+      <c r="Q7" s="12" t="n"/>
+      <c r="R7" s="12" t="n"/>
+      <c r="S7" s="12" t="n"/>
+      <c r="T7" s="13" t="n"/>
+      <c r="U7" s="13" t="n"/>
+      <c r="V7" s="13" t="n"/>
+      <c r="W7" s="13" t="n"/>
+      <c r="X7" s="13" t="n"/>
+      <c r="Y7" s="13" t="n"/>
+      <c r="Z7" s="13" t="n"/>
+      <c r="AA7" s="13" t="n"/>
+      <c r="AB7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="12" t="n"/>
+      <c r="N8" s="12" t="n"/>
+      <c r="O8" s="12" t="n"/>
+      <c r="P8" s="12" t="n"/>
+      <c r="Q8" s="12" t="n"/>
+      <c r="R8" s="12" t="n"/>
+      <c r="S8" s="12" t="n"/>
+      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="13" t="n"/>
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="13" t="n"/>
+      <c r="Y8" s="13" t="n"/>
+      <c r="Z8" s="13" t="n"/>
+      <c r="AA8" s="13" t="n"/>
+      <c r="AB8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+      <c r="P9" s="12" t="n"/>
+      <c r="Q9" s="12" t="n"/>
+      <c r="R9" s="12" t="n"/>
+      <c r="S9" s="12" t="n"/>
+      <c r="T9" s="13" t="n"/>
+      <c r="U9" s="13" t="n"/>
+      <c r="V9" s="13" t="n"/>
+      <c r="W9" s="13" t="n"/>
+      <c r="X9" s="13" t="n"/>
+      <c r="Y9" s="13" t="n"/>
+      <c r="Z9" s="13" t="n"/>
+      <c r="AA9" s="13" t="n"/>
+      <c r="AB9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
+      <c r="P10" s="12" t="n"/>
+      <c r="Q10" s="12" t="n"/>
+      <c r="R10" s="12" t="n"/>
+      <c r="S10" s="12" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="13" t="n"/>
+      <c r="V10" s="13" t="n"/>
+      <c r="W10" s="13" t="n"/>
+      <c r="X10" s="13" t="n"/>
+      <c r="Y10" s="13" t="n"/>
+      <c r="Z10" s="13" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12" t="n"/>
+      <c r="P11" s="12" t="n"/>
+      <c r="Q11" s="12" t="n"/>
+      <c r="R11" s="12" t="n"/>
+      <c r="S11" s="12" t="n"/>
+      <c r="T11" s="13" t="n"/>
+      <c r="U11" s="13" t="n"/>
+      <c r="V11" s="13" t="n"/>
+      <c r="W11" s="13" t="n"/>
+      <c r="X11" s="13" t="n"/>
+      <c r="Y11" s="13" t="n"/>
+      <c r="Z11" s="13" t="n"/>
+      <c r="AA11" s="13" t="n"/>
+      <c r="AB11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="11" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
+      <c r="P12" s="12" t="n"/>
+      <c r="Q12" s="12" t="n"/>
+      <c r="R12" s="12" t="n"/>
+      <c r="S12" s="12" t="n"/>
+      <c r="T12" s="13" t="n"/>
+      <c r="U12" s="13" t="n"/>
+      <c r="V12" s="13" t="n"/>
+      <c r="W12" s="13" t="n"/>
+      <c r="X12" s="13" t="n"/>
+      <c r="Y12" s="13" t="n"/>
+      <c r="Z12" s="13" t="n"/>
+      <c r="AA12" s="13" t="n"/>
+      <c r="AB12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
+      <c r="P13" s="12" t="n"/>
+      <c r="Q13" s="12" t="n"/>
+      <c r="R13" s="12" t="n"/>
+      <c r="S13" s="12" t="n"/>
+      <c r="T13" s="13" t="n"/>
+      <c r="U13" s="13" t="n"/>
+      <c r="V13" s="13" t="n"/>
+      <c r="W13" s="13" t="n"/>
+      <c r="X13" s="13" t="n"/>
+      <c r="Y13" s="13" t="n"/>
+      <c r="Z13" s="13" t="n"/>
+      <c r="AA13" s="13" t="n"/>
+      <c r="AB13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="12" t="n"/>
+      <c r="P14" s="12" t="n"/>
+      <c r="Q14" s="12" t="n"/>
+      <c r="R14" s="12" t="n"/>
+      <c r="S14" s="12" t="n"/>
+      <c r="T14" s="13" t="n"/>
+      <c r="U14" s="13" t="n"/>
+      <c r="V14" s="13" t="n"/>
+      <c r="W14" s="13" t="n"/>
+      <c r="X14" s="13" t="n"/>
+      <c r="Y14" s="13" t="n"/>
+      <c r="Z14" s="13" t="n"/>
+      <c r="AA14" s="13" t="n"/>
+      <c r="AB14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="12" t="n"/>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="12" t="n"/>
+      <c r="P15" s="12" t="n"/>
+      <c r="Q15" s="12" t="n"/>
+      <c r="R15" s="12" t="n"/>
+      <c r="S15" s="12" t="n"/>
+      <c r="T15" s="13" t="n"/>
+      <c r="U15" s="13" t="n"/>
+      <c r="V15" s="13" t="n"/>
+      <c r="W15" s="13" t="n"/>
+      <c r="X15" s="13" t="n"/>
+      <c r="Y15" s="13" t="n"/>
+      <c r="Z15" s="13" t="n"/>
+      <c r="AA15" s="13" t="n"/>
+      <c r="AB15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="11" t="n"/>
+      <c r="K16" s="11" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="12" t="n"/>
+      <c r="P16" s="12" t="n"/>
+      <c r="Q16" s="12" t="n"/>
+      <c r="R16" s="12" t="n"/>
+      <c r="S16" s="12" t="n"/>
+      <c r="T16" s="13" t="n"/>
+      <c r="U16" s="13" t="n"/>
+      <c r="V16" s="13" t="n"/>
+      <c r="W16" s="13" t="n"/>
+      <c r="X16" s="13" t="n"/>
+      <c r="Y16" s="13" t="n"/>
+      <c r="Z16" s="13" t="n"/>
+      <c r="AA16" s="13" t="n"/>
+      <c r="AB16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
+      <c r="P17" s="12" t="n"/>
+      <c r="Q17" s="12" t="n"/>
+      <c r="R17" s="12" t="n"/>
+      <c r="S17" s="12" t="n"/>
+      <c r="T17" s="13" t="n"/>
+      <c r="U17" s="13" t="n"/>
+      <c r="V17" s="13" t="n"/>
+      <c r="W17" s="13" t="n"/>
+      <c r="X17" s="13" t="n"/>
+      <c r="Y17" s="13" t="n"/>
+      <c r="Z17" s="13" t="n"/>
+      <c r="AA17" s="13" t="n"/>
+      <c r="AB17" s="14" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="11" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="12" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="12" t="n"/>
+      <c r="P18" s="12" t="n"/>
+      <c r="Q18" s="12" t="n"/>
+      <c r="R18" s="12" t="n"/>
+      <c r="S18" s="12" t="n"/>
+      <c r="T18" s="13" t="n"/>
+      <c r="U18" s="13" t="n"/>
+      <c r="V18" s="13" t="n"/>
+      <c r="W18" s="13" t="n"/>
+      <c r="X18" s="13" t="n"/>
+      <c r="Y18" s="13" t="n"/>
+      <c r="Z18" s="13" t="n"/>
+      <c r="AA18" s="13" t="n"/>
+      <c r="AB18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
+      <c r="P19" s="12" t="n"/>
+      <c r="Q19" s="12" t="n"/>
+      <c r="R19" s="12" t="n"/>
+      <c r="S19" s="12" t="n"/>
+      <c r="T19" s="13" t="n"/>
+      <c r="U19" s="13" t="n"/>
+      <c r="V19" s="13" t="n"/>
+      <c r="W19" s="13" t="n"/>
+      <c r="X19" s="13" t="n"/>
+      <c r="Y19" s="13" t="n"/>
+      <c r="Z19" s="13" t="n"/>
+      <c r="AA19" s="13" t="n"/>
+      <c r="AB19" s="14" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="11" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="12" t="n"/>
+      <c r="P20" s="12" t="n"/>
+      <c r="Q20" s="12" t="n"/>
+      <c r="R20" s="12" t="n"/>
+      <c r="S20" s="12" t="n"/>
+      <c r="T20" s="13" t="n"/>
+      <c r="U20" s="13" t="n"/>
+      <c r="V20" s="13" t="n"/>
+      <c r="W20" s="13" t="n"/>
+      <c r="X20" s="13" t="n"/>
+      <c r="Y20" s="13" t="n"/>
+      <c r="Z20" s="13" t="n"/>
+      <c r="AA20" s="13" t="n"/>
+      <c r="AB20" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="12" t="n"/>
+      <c r="P21" s="12" t="n"/>
+      <c r="Q21" s="12" t="n"/>
+      <c r="R21" s="12" t="n"/>
+      <c r="S21" s="12" t="n"/>
+      <c r="T21" s="13" t="n"/>
+      <c r="U21" s="13" t="n"/>
+      <c r="V21" s="13" t="n"/>
+      <c r="W21" s="13" t="n"/>
+      <c r="X21" s="13" t="n"/>
+      <c r="Y21" s="13" t="n"/>
+      <c r="Z21" s="13" t="n"/>
+      <c r="AA21" s="13" t="n"/>
+      <c r="AB21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="12" t="n"/>
+      <c r="P22" s="12" t="n"/>
+      <c r="Q22" s="12" t="n"/>
+      <c r="R22" s="12" t="n"/>
+      <c r="S22" s="12" t="n"/>
+      <c r="T22" s="13" t="n"/>
+      <c r="U22" s="13" t="n"/>
+      <c r="V22" s="13" t="n"/>
+      <c r="W22" s="13" t="n"/>
+      <c r="X22" s="13" t="n"/>
+      <c r="Y22" s="13" t="n"/>
+      <c r="Z22" s="13" t="n"/>
+      <c r="AA22" s="13" t="n"/>
+      <c r="AB22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="12" t="n"/>
+      <c r="P23" s="12" t="n"/>
+      <c r="Q23" s="12" t="n"/>
+      <c r="R23" s="12" t="n"/>
+      <c r="S23" s="12" t="n"/>
+      <c r="T23" s="13" t="n"/>
+      <c r="U23" s="13" t="n"/>
+      <c r="V23" s="13" t="n"/>
+      <c r="W23" s="13" t="n"/>
+      <c r="X23" s="13" t="n"/>
+      <c r="Y23" s="13" t="n"/>
+      <c r="Z23" s="13" t="n"/>
+      <c r="AA23" s="13" t="n"/>
+      <c r="AB23" s="14" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="12" t="n"/>
+      <c r="P24" s="12" t="n"/>
+      <c r="Q24" s="12" t="n"/>
+      <c r="R24" s="12" t="n"/>
+      <c r="S24" s="12" t="n"/>
+      <c r="T24" s="13" t="n"/>
+      <c r="U24" s="13" t="n"/>
+      <c r="V24" s="13" t="n"/>
+      <c r="W24" s="13" t="n"/>
+      <c r="X24" s="13" t="n"/>
+      <c r="Y24" s="13" t="n"/>
+      <c r="Z24" s="13" t="n"/>
+      <c r="AA24" s="13" t="n"/>
+      <c r="AB24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="11" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="12" t="n"/>
+      <c r="P25" s="12" t="n"/>
+      <c r="Q25" s="12" t="n"/>
+      <c r="R25" s="12" t="n"/>
+      <c r="S25" s="12" t="n"/>
+      <c r="T25" s="13" t="n"/>
+      <c r="U25" s="13" t="n"/>
+      <c r="V25" s="13" t="n"/>
+      <c r="W25" s="13" t="n"/>
+      <c r="X25" s="13" t="n"/>
+      <c r="Y25" s="13" t="n"/>
+      <c r="Z25" s="13" t="n"/>
+      <c r="AA25" s="13" t="n"/>
+      <c r="AB25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="11" t="n"/>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="11" t="n"/>
+      <c r="K26" s="11" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="12" t="n"/>
+      <c r="P26" s="12" t="n"/>
+      <c r="Q26" s="12" t="n"/>
+      <c r="R26" s="12" t="n"/>
+      <c r="S26" s="12" t="n"/>
+      <c r="T26" s="13" t="n"/>
+      <c r="U26" s="13" t="n"/>
+      <c r="V26" s="13" t="n"/>
+      <c r="W26" s="13" t="n"/>
+      <c r="X26" s="13" t="n"/>
+      <c r="Y26" s="13" t="n"/>
+      <c r="Z26" s="13" t="n"/>
+      <c r="AA26" s="13" t="n"/>
+      <c r="AB26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="12" t="n"/>
+      <c r="P27" s="12" t="n"/>
+      <c r="Q27" s="12" t="n"/>
+      <c r="R27" s="12" t="n"/>
+      <c r="S27" s="12" t="n"/>
+      <c r="T27" s="13" t="n"/>
+      <c r="U27" s="13" t="n"/>
+      <c r="V27" s="13" t="n"/>
+      <c r="W27" s="13" t="n"/>
+      <c r="X27" s="13" t="n"/>
+      <c r="Y27" s="13" t="n"/>
+      <c r="Z27" s="13" t="n"/>
+      <c r="AA27" s="13" t="n"/>
+      <c r="AB27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="11" t="n"/>
+      <c r="K28" s="11" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="12" t="n"/>
+      <c r="P28" s="12" t="n"/>
+      <c r="Q28" s="12" t="n"/>
+      <c r="R28" s="12" t="n"/>
+      <c r="S28" s="12" t="n"/>
+      <c r="T28" s="13" t="n"/>
+      <c r="U28" s="13" t="n"/>
+      <c r="V28" s="13" t="n"/>
+      <c r="W28" s="13" t="n"/>
+      <c r="X28" s="13" t="n"/>
+      <c r="Y28" s="13" t="n"/>
+      <c r="Z28" s="13" t="n"/>
+      <c r="AA28" s="13" t="n"/>
+      <c r="AB28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="12" t="n"/>
+      <c r="P29" s="12" t="n"/>
+      <c r="Q29" s="12" t="n"/>
+      <c r="R29" s="12" t="n"/>
+      <c r="S29" s="12" t="n"/>
+      <c r="T29" s="13" t="n"/>
+      <c r="U29" s="13" t="n"/>
+      <c r="V29" s="13" t="n"/>
+      <c r="W29" s="13" t="n"/>
+      <c r="X29" s="13" t="n"/>
+      <c r="Y29" s="13" t="n"/>
+      <c r="Z29" s="13" t="n"/>
+      <c r="AA29" s="13" t="n"/>
+      <c r="AB29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="12" t="n"/>
+      <c r="P30" s="12" t="n"/>
+      <c r="Q30" s="12" t="n"/>
+      <c r="R30" s="12" t="n"/>
+      <c r="S30" s="12" t="n"/>
+      <c r="T30" s="13" t="n"/>
+      <c r="U30" s="13" t="n"/>
+      <c r="V30" s="13" t="n"/>
+      <c r="W30" s="13" t="n"/>
+      <c r="X30" s="13" t="n"/>
+      <c r="Y30" s="13" t="n"/>
+      <c r="Z30" s="13" t="n"/>
+      <c r="AA30" s="13" t="n"/>
+      <c r="AB30" s="14" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="12" t="n"/>
+      <c r="P31" s="12" t="n"/>
+      <c r="Q31" s="12" t="n"/>
+      <c r="R31" s="12" t="n"/>
+      <c r="S31" s="12" t="n"/>
+      <c r="T31" s="13" t="n"/>
+      <c r="U31" s="13" t="n"/>
+      <c r="V31" s="13" t="n"/>
+      <c r="W31" s="13" t="n"/>
+      <c r="X31" s="13" t="n"/>
+      <c r="Y31" s="13" t="n"/>
+      <c r="Z31" s="13" t="n"/>
+      <c r="AA31" s="13" t="n"/>
+      <c r="AB31" s="14" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n"/>
+      <c r="J32" s="11" t="n"/>
+      <c r="K32" s="11" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="12" t="n"/>
+      <c r="P32" s="12" t="n"/>
+      <c r="Q32" s="12" t="n"/>
+      <c r="R32" s="12" t="n"/>
+      <c r="S32" s="12" t="n"/>
+      <c r="T32" s="13" t="n"/>
+      <c r="U32" s="13" t="n"/>
+      <c r="V32" s="13" t="n"/>
+      <c r="W32" s="13" t="n"/>
+      <c r="X32" s="13" t="n"/>
+      <c r="Y32" s="13" t="n"/>
+      <c r="Z32" s="13" t="n"/>
+      <c r="AA32" s="13" t="n"/>
+      <c r="AB32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+      <c r="N33" s="12" t="n"/>
+      <c r="O33" s="12" t="n"/>
+      <c r="P33" s="12" t="n"/>
+      <c r="Q33" s="12" t="n"/>
+      <c r="R33" s="12" t="n"/>
+      <c r="S33" s="12" t="n"/>
+      <c r="T33" s="13" t="n"/>
+      <c r="U33" s="13" t="n"/>
+      <c r="V33" s="13" t="n"/>
+      <c r="W33" s="13" t="n"/>
+      <c r="X33" s="13" t="n"/>
+      <c r="Y33" s="13" t="n"/>
+      <c r="Z33" s="13" t="n"/>
+      <c r="AA33" s="13" t="n"/>
+      <c r="AB33" s="14" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="11" t="n"/>
+      <c r="K34" s="11" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="12" t="n"/>
+      <c r="N34" s="12" t="n"/>
+      <c r="O34" s="12" t="n"/>
+      <c r="P34" s="12" t="n"/>
+      <c r="Q34" s="12" t="n"/>
+      <c r="R34" s="12" t="n"/>
+      <c r="S34" s="12" t="n"/>
+      <c r="T34" s="13" t="n"/>
+      <c r="U34" s="13" t="n"/>
+      <c r="V34" s="13" t="n"/>
+      <c r="W34" s="13" t="n"/>
+      <c r="X34" s="13" t="n"/>
+      <c r="Y34" s="13" t="n"/>
+      <c r="Z34" s="13" t="n"/>
+      <c r="AA34" s="13" t="n"/>
+      <c r="AB34" s="14" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="11" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="12" t="n"/>
+      <c r="N35" s="12" t="n"/>
+      <c r="O35" s="12" t="n"/>
+      <c r="P35" s="12" t="n"/>
+      <c r="Q35" s="12" t="n"/>
+      <c r="R35" s="12" t="n"/>
+      <c r="S35" s="12" t="n"/>
+      <c r="T35" s="13" t="n"/>
+      <c r="U35" s="13" t="n"/>
+      <c r="V35" s="13" t="n"/>
+      <c r="W35" s="13" t="n"/>
+      <c r="X35" s="13" t="n"/>
+      <c r="Y35" s="13" t="n"/>
+      <c r="Z35" s="13" t="n"/>
+      <c r="AA35" s="13" t="n"/>
+      <c r="AB35" s="14" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="11" t="n"/>
+      <c r="J36" s="11" t="n"/>
+      <c r="K36" s="11" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+      <c r="N36" s="12" t="n"/>
+      <c r="O36" s="12" t="n"/>
+      <c r="P36" s="12" t="n"/>
+      <c r="Q36" s="12" t="n"/>
+      <c r="R36" s="12" t="n"/>
+      <c r="S36" s="12" t="n"/>
+      <c r="T36" s="13" t="n"/>
+      <c r="U36" s="13" t="n"/>
+      <c r="V36" s="13" t="n"/>
+      <c r="W36" s="13" t="n"/>
+      <c r="X36" s="13" t="n"/>
+      <c r="Y36" s="13" t="n"/>
+      <c r="Z36" s="13" t="n"/>
+      <c r="AA36" s="13" t="n"/>
+      <c r="AB36" s="14" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="11" t="n"/>
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="12" t="n"/>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="12" t="n"/>
+      <c r="P37" s="12" t="n"/>
+      <c r="Q37" s="12" t="n"/>
+      <c r="R37" s="12" t="n"/>
+      <c r="S37" s="12" t="n"/>
+      <c r="T37" s="13" t="n"/>
+      <c r="U37" s="13" t="n"/>
+      <c r="V37" s="13" t="n"/>
+      <c r="W37" s="13" t="n"/>
+      <c r="X37" s="13" t="n"/>
+      <c r="Y37" s="13" t="n"/>
+      <c r="Z37" s="13" t="n"/>
+      <c r="AA37" s="13" t="n"/>
+      <c r="AB37" s="14" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
+      <c r="I38" s="11" t="n"/>
+      <c r="J38" s="11" t="n"/>
+      <c r="K38" s="11" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="12" t="n"/>
+      <c r="N38" s="12" t="n"/>
+      <c r="O38" s="12" t="n"/>
+      <c r="P38" s="12" t="n"/>
+      <c r="Q38" s="12" t="n"/>
+      <c r="R38" s="12" t="n"/>
+      <c r="S38" s="12" t="n"/>
+      <c r="T38" s="13" t="n"/>
+      <c r="U38" s="13" t="n"/>
+      <c r="V38" s="13" t="n"/>
+      <c r="W38" s="13" t="n"/>
+      <c r="X38" s="13" t="n"/>
+      <c r="Y38" s="13" t="n"/>
+      <c r="Z38" s="13" t="n"/>
+      <c r="AA38" s="13" t="n"/>
+      <c r="AB38" s="14" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="12" t="n"/>
+      <c r="N39" s="12" t="n"/>
+      <c r="O39" s="12" t="n"/>
+      <c r="P39" s="12" t="n"/>
+      <c r="Q39" s="12" t="n"/>
+      <c r="R39" s="12" t="n"/>
+      <c r="S39" s="12" t="n"/>
+      <c r="T39" s="13" t="n"/>
+      <c r="U39" s="13" t="n"/>
+      <c r="V39" s="13" t="n"/>
+      <c r="W39" s="13" t="n"/>
+      <c r="X39" s="13" t="n"/>
+      <c r="Y39" s="13" t="n"/>
+      <c r="Z39" s="13" t="n"/>
+      <c r="AA39" s="13" t="n"/>
+      <c r="AB39" s="14" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="11" t="n"/>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="12" t="n"/>
+      <c r="M40" s="12" t="n"/>
+      <c r="N40" s="12" t="n"/>
+      <c r="O40" s="12" t="n"/>
+      <c r="P40" s="12" t="n"/>
+      <c r="Q40" s="12" t="n"/>
+      <c r="R40" s="12" t="n"/>
+      <c r="S40" s="12" t="n"/>
+      <c r="T40" s="13" t="n"/>
+      <c r="U40" s="13" t="n"/>
+      <c r="V40" s="13" t="n"/>
+      <c r="W40" s="13" t="n"/>
+      <c r="X40" s="13" t="n"/>
+      <c r="Y40" s="13" t="n"/>
+      <c r="Z40" s="13" t="n"/>
+      <c r="AA40" s="13" t="n"/>
+      <c r="AB40" s="14" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="11" t="n"/>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="12" t="n"/>
+      <c r="M41" s="12" t="n"/>
+      <c r="N41" s="12" t="n"/>
+      <c r="O41" s="12" t="n"/>
+      <c r="P41" s="12" t="n"/>
+      <c r="Q41" s="12" t="n"/>
+      <c r="R41" s="12" t="n"/>
+      <c r="S41" s="12" t="n"/>
+      <c r="T41" s="13" t="n"/>
+      <c r="U41" s="13" t="n"/>
+      <c r="V41" s="13" t="n"/>
+      <c r="W41" s="13" t="n"/>
+      <c r="X41" s="13" t="n"/>
+      <c r="Y41" s="13" t="n"/>
+      <c r="Z41" s="13" t="n"/>
+      <c r="AA41" s="13" t="n"/>
+      <c r="AB41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="11" t="n"/>
+      <c r="K42" s="11" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="12" t="n"/>
+      <c r="N42" s="12" t="n"/>
+      <c r="O42" s="12" t="n"/>
+      <c r="P42" s="12" t="n"/>
+      <c r="Q42" s="12" t="n"/>
+      <c r="R42" s="12" t="n"/>
+      <c r="S42" s="12" t="n"/>
+      <c r="T42" s="13" t="n"/>
+      <c r="U42" s="13" t="n"/>
+      <c r="V42" s="13" t="n"/>
+      <c r="W42" s="13" t="n"/>
+      <c r="X42" s="13" t="n"/>
+      <c r="Y42" s="13" t="n"/>
+      <c r="Z42" s="13" t="n"/>
+      <c r="AA42" s="13" t="n"/>
+      <c r="AB42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="11" t="n"/>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="12" t="n"/>
+      <c r="M43" s="12" t="n"/>
+      <c r="N43" s="12" t="n"/>
+      <c r="O43" s="12" t="n"/>
+      <c r="P43" s="12" t="n"/>
+      <c r="Q43" s="12" t="n"/>
+      <c r="R43" s="12" t="n"/>
+      <c r="S43" s="12" t="n"/>
+      <c r="T43" s="13" t="n"/>
+      <c r="U43" s="13" t="n"/>
+      <c r="V43" s="13" t="n"/>
+      <c r="W43" s="13" t="n"/>
+      <c r="X43" s="13" t="n"/>
+      <c r="Y43" s="13" t="n"/>
+      <c r="Z43" s="13" t="n"/>
+      <c r="AA43" s="13" t="n"/>
+      <c r="AB43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="11" t="n"/>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="11" t="n"/>
+      <c r="K44" s="11" t="n"/>
+      <c r="L44" s="12" t="n"/>
+      <c r="M44" s="12" t="n"/>
+      <c r="N44" s="12" t="n"/>
+      <c r="O44" s="12" t="n"/>
+      <c r="P44" s="12" t="n"/>
+      <c r="Q44" s="12" t="n"/>
+      <c r="R44" s="12" t="n"/>
+      <c r="S44" s="12" t="n"/>
+      <c r="T44" s="13" t="n"/>
+      <c r="U44" s="13" t="n"/>
+      <c r="V44" s="13" t="n"/>
+      <c r="W44" s="13" t="n"/>
+      <c r="X44" s="13" t="n"/>
+      <c r="Y44" s="13" t="n"/>
+      <c r="Z44" s="13" t="n"/>
+      <c r="AA44" s="13" t="n"/>
+      <c r="AB44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="11" t="n"/>
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="12" t="n"/>
+      <c r="M45" s="12" t="n"/>
+      <c r="N45" s="12" t="n"/>
+      <c r="O45" s="12" t="n"/>
+      <c r="P45" s="12" t="n"/>
+      <c r="Q45" s="12" t="n"/>
+      <c r="R45" s="12" t="n"/>
+      <c r="S45" s="12" t="n"/>
+      <c r="T45" s="13" t="n"/>
+      <c r="U45" s="13" t="n"/>
+      <c r="V45" s="13" t="n"/>
+      <c r="W45" s="13" t="n"/>
+      <c r="X45" s="13" t="n"/>
+      <c r="Y45" s="13" t="n"/>
+      <c r="Z45" s="13" t="n"/>
+      <c r="AA45" s="13" t="n"/>
+      <c r="AB45" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AB1"/>
+  <dataValidations count="13">
+    <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Include?" error="Choose one of: Y, N" promptTitle="Include?" prompt="Y to include this row in the next run, N to stage it without uploading. Blank counts as Y." type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Amazon Product Type" error="Choose one of: RING, EARRING, NECKLACE, BRACELET, CHARM, ANKLET, BODY_JEWELRY, JEWELRY_SET, PENDANT, LOOSE_STONE" promptTitle="Amazon Product Type" prompt="Blank is recommended — it is inferred from the SKU prefix (R=RING, E=EARRING, P=PENDANT, B=BRACELET, N=NECKLACE, S=JEWELRY_SET) and confirmed against Amazon's Product Type Definitions API. Set it only to override." type="list">
+      <formula1>"RING,EARRING,NECKLACE,BRACELET,CHARM,ANKLET,BODY_JEWELRY,JEWELRY_SET,PENDANT,LOOSE_STONE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Variations" error="Choose one of: site, none" promptTitle="Variations" prompt="'site' (default) builds a parent/child variation family from the ring sizes or chain lengths on the product page. 'none' lists a single standalone item using the base size only." type="list">
+      <formula1>"site,none"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Quantity" error="Whole number, zero or greater." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Price Override (USD)" error="A number greater than zero, or blank to use the website value." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid List Price / MSRP (USD)" error="A number greater than zero, or blank to use the website value." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Condition" error="Choose one of: new_new, used_like_new, used_very_good, used_good, used_acceptable" promptTitle="Condition" prompt="Blank means new_new (brand new). Anything else needs a condition note." type="list">
+      <formula1>"new_new,used_like_new,used_very_good,used_good,used_acceptable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Handling Time (days)" error="Whole number, zero or greater." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Metal Type" error="Choose one of: yellow_gold, white_gold, rose_gold, two_tone_gold, platinum, sterling_silver, palladium, titanium, stainless_steel" promptTitle="Metal Type" prompt="Blank uses the metal parsed from the website's Item Details. Override only when the site data is wrong or ambiguous." type="list">
+      <formula1>"yellow_gold,white_gold,rose_gold,two_tone_gold,platinum,sterling_silver,palladium,titanium,stainless_steel"</formula1>
+    </dataValidation>
+    <dataValidation sqref="V2:V5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Gem Type" error="Choose one of: diamond, sapphire, ruby, emerald, pearl, topaz, amethyst, garnet, aquamarine, opal, tanzanite, morganite, citrine, peridot, none" promptTitle="Gem Type" prompt="Primary stone. Blank uses the parsed value. Use 'none' for plain metal pieces. FTC rules require lab-grown and simulated stones to be disclosed — the generator copies the site's qualifier verbatim and never upgrades 'simulated' to 'genuine'." type="list">
+      <formula1>"diamond,sapphire,ruby,emerald,pearl,topaz,amethyst,garnet,aquamarine,opal,tanzanite,morganite,citrine,peridot,none"</formula1>
+    </dataValidation>
+    <dataValidation sqref="W2:W5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Total Gem Weight (ct)" error="A number greater than zero, or blank to use the website value." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="X2:X5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Metal Weight (g)" error="A number greater than zero, or blank to use the website value." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y2:Y5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Target Gender" error="Choose one of: female, male, unisex" promptTitle="Target Gender" prompt="Blank defaults to 'unisex'. Drives Amazon's department browse-node placement." type="list">
+      <formula1>"female,male,unisex"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Allowed values</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Include?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>Y to include this row in the next run, N to stage it without uploading. Blank counts as Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Amazon Product Type</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RING</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Blank is recommended — it is inferred from the SKU prefix (R=RING, E=EARRING, P=PENDANT, B=BRACELET, N=NECKLACE, S=JEWELRY_SET) and confirmed against Amazon's Product Type Definitions API. Set it only to override.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EARRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NECKLACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BRACELET</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CHARM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ANKLET</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BODY_JEWELRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JEWELRY_SET</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PENDANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LOOSE_STONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Variations</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>'site' (default) builds a parent/child variation family from the ring sizes or chain lengths on the product page. 'none' lists a single standalone item using the base size only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>new_new</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Blank means new_new (brand new). Anything else needs a condition note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>used_like_new</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>used_very_good</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>used_good</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>used_acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Metal Type</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>yellow_gold</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Blank uses the metal parsed from the website's Item Details. Override only when the site data is wrong or ambiguous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>white_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rose_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>two_tone_gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>platinum</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sterling_silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>palladium</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>titanium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>stainless_steel</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Gem Type</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>diamond</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Primary stone. Blank uses the parsed value. Use 'none' for plain metal pieces. FTC rules require lab-grown and simulated stones to be disclosed — the generator copies the site's qualifier verbatim and never upgrades 'simulated' to 'genuine'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sapphire</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ruby</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>emerald</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>pearl</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>topaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>amethyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>garnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>aquamarine</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>opal</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>tanzanite</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>morganite</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>citrine</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>peridot</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Target Gender</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>Blank defaults to 'unisex'. Drives Amazon's department browse-node placement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>Marketplace codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>Marketplace ID</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Country / region / currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A2VIGQ35RCS4UG</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>United Arab Emirates — EU region, AED, amazon.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A39IBJ37TRP1C6</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Australia — FE region, AUD, amazon.com.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AMEN7PMS3EDWL</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Belgium — EU region, EUR, amazon.com.be</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>A2Q3Y263D00KWC</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Brazil — NA region, BRL, amazon.com.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>A2EUQ1WTGCTBG2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Canada — NA region, CAD, amazon.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A1PA6795UKMFR9</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Germany — EU region, EUR, amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ARBP9OOSHTCHU</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Egypt — EU region, EGP, amazon.eg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A1RKKUPIHCS9HS</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Spain — EU region, EUR, amazon.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A13V1IB3VIYZZH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>France — EU region, EUR, amazon.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>A28R8C7NBKEWEA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ireland — EU region, EUR, amazon.ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>A21TJRUUN4KGV</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>India — EU region, INR, amazon.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>APJ6JRA9NG5V4</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Italy — EU region, EUR, amazon.it</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>A1VC38T7YXB528</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Japan — FE region, JPY, amazon.co.jp</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>A1AM78C64UM0Y8</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Mexico — NA region, MXN, amazon.com.mx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>A1805IZSGTT6HS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Netherlands — EU region, EUR, amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>A1C3SOZRARQ6R3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Poland — EU region, PLN, amazon.pl</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>A17E79C6D8DWNP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Saudi Arabia — EU region, SAR, amazon.sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A2NODRKZP88ZB9</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Sweden — EU region, SEK, amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A19VAU5U5O7RUS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Singapore — FE region, SGD, amazon.sg</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>A33AVAJ2PDY3EV</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Turkey — EU region, TRY, amazon.com.tr</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>A1F83G8C2ARO7P</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>United Kingdom — EU region, GBP, amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ATVPDKIKX0DER</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>United States — NA region, USD, amazon.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Child SKU</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>Submission ID</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>Issue Code</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>Payload</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>(filled in automatically after `anzorlist amazon validate` or `submit`)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Product Listing.xlsx
+++ b/Product Listing.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="150" yWindow="645" windowWidth="28455" windowHeight="11700" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,14 +14,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Products'!$A$1:$AB$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="125725" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,39 +30,50 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="18"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="FF1F3864"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Consolas"/>
-      <color rgb="00333333"/>
+      <color rgb="FF333333"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
+    <font/>
   </fonts>
   <fills count="11">
     <fill>
@@ -74,47 +84,47 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007F7F7F"/>
+        <fgColor rgb="FF7F7F7F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFD9"/>
+        <fgColor rgb="FFE2EFD9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBE5D6"/>
+        <fgColor rgb="FFFBE5D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,23 +138,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -184,9 +195,10 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -988,8 +1000,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -998,11 +1009,7 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="44" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="13" max="17"/>
     <col width="50" customWidth="1" min="18" max="18"/>
     <col width="40" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
@@ -1016,7 +1023,7 @@
     <col width="34" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="33.95" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
           <t>SKU</t>
@@ -1159,150 +1166,232 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>R985</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>R2254</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>new_new</t>
         </is>
       </c>
-      <c r="Y2" s="9" t="inlineStr">
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="19" t="n"/>
+      <c r="L2" s="19" t="n"/>
+      <c r="M2" s="19" t="n"/>
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" s="19" t="n"/>
+      <c r="P2" s="19" t="n"/>
+      <c r="Q2" s="19" t="n"/>
+      <c r="R2" s="19" t="n"/>
+      <c r="S2" s="19" t="n"/>
+      <c r="T2" s="19" t="n"/>
+      <c r="U2" s="19" t="n"/>
+      <c r="V2" s="19" t="n"/>
+      <c r="W2" s="19" t="n"/>
+      <c r="X2" s="19" t="n"/>
+      <c r="Y2" s="19" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="AB2" s="9" t="inlineStr">
+      <c r="Z2" s="19" t="n"/>
+      <c r="AA2" s="19" t="n"/>
+      <c r="AB2" s="19" t="inlineStr">
         <is>
           <t>Example row — delete or set Include=N once you add your own.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>E1154</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>R1794</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="n">
+      <c r="D3" s="19" t="n"/>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="G3" s="19" t="n"/>
+      <c r="H3" s="19" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>new_new</t>
         </is>
       </c>
-      <c r="Y3" s="9" t="inlineStr">
+      <c r="J3" s="19" t="n"/>
+      <c r="K3" s="19" t="n"/>
+      <c r="L3" s="19" t="n"/>
+      <c r="M3" s="19" t="n"/>
+      <c r="N3" s="19" t="n"/>
+      <c r="O3" s="19" t="n"/>
+      <c r="P3" s="19" t="n"/>
+      <c r="Q3" s="19" t="n"/>
+      <c r="R3" s="19" t="n"/>
+      <c r="S3" s="19" t="n"/>
+      <c r="T3" s="19" t="n"/>
+      <c r="U3" s="19" t="n"/>
+      <c r="V3" s="19" t="n"/>
+      <c r="W3" s="19" t="n"/>
+      <c r="X3" s="19" t="n"/>
+      <c r="Y3" s="19" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="AB3" s="9" t="inlineStr">
+      <c r="Z3" s="19" t="n"/>
+      <c r="AA3" s="19" t="n"/>
+      <c r="AB3" s="19" t="inlineStr">
         <is>
           <t>Example row — earrings have no size axis, so Variations = none.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>S220</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>R1279</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="n">
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="G4" s="19" t="n"/>
+      <c r="H4" s="19" t="n"/>
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>new_new</t>
         </is>
       </c>
-      <c r="AB4" s="9" t="inlineStr">
+      <c r="J4" s="19" t="n"/>
+      <c r="K4" s="19" t="n"/>
+      <c r="L4" s="19" t="n"/>
+      <c r="M4" s="19" t="n"/>
+      <c r="N4" s="19" t="n"/>
+      <c r="O4" s="19" t="n"/>
+      <c r="P4" s="19" t="n"/>
+      <c r="Q4" s="19" t="n"/>
+      <c r="R4" s="19" t="n"/>
+      <c r="S4" s="19" t="n"/>
+      <c r="T4" s="19" t="n"/>
+      <c r="U4" s="19" t="n"/>
+      <c r="V4" s="19" t="n"/>
+      <c r="W4" s="19" t="n"/>
+      <c r="X4" s="19" t="n"/>
+      <c r="Y4" s="19" t="n"/>
+      <c r="Z4" s="19" t="n"/>
+      <c r="AA4" s="19" t="n"/>
+      <c r="AB4" s="19" t="inlineStr">
         <is>
           <t>Example row, staged (Include = N) so it is skipped.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>E711</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>E1661</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="n">
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>new_new</t>
         </is>
       </c>
-      <c r="AB5" s="9" t="inlineStr">
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="19" t="n"/>
+      <c r="L5" s="19" t="n"/>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="19" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="19" t="n"/>
+      <c r="V5" s="19" t="n"/>
+      <c r="W5" s="19" t="n"/>
+      <c r="X5" s="19" t="n"/>
+      <c r="Y5" s="19" t="n"/>
+      <c r="Z5" s="19" t="n"/>
+      <c r="AA5" s="19" t="n"/>
+      <c r="AB5" s="19" t="inlineStr">
         <is>
           <t>Example row, staged (Include = N) so it is skipped.</t>
         </is>
@@ -2565,8 +2654,7 @@
   <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="2"/>
     <col width="90" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -2605,14 +2693,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>Amazon Product Type</t>
@@ -2630,7 +2717,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>EARRING</t>
@@ -2638,7 +2724,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>NECKLACE</t>
@@ -2646,7 +2731,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>BRACELET</t>
@@ -2654,7 +2738,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>CHARM</t>
@@ -2662,7 +2745,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>ANKLET</t>
@@ -2670,7 +2752,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>BODY_JEWELRY</t>
@@ -2678,7 +2759,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>JEWELRY_SET</t>
@@ -2686,7 +2766,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>PENDANT</t>
@@ -2694,14 +2773,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>LOOSE_STONE</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>Variations</t>
@@ -2719,7 +2797,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>none</t>
@@ -2744,7 +2821,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>used_like_new</t>
@@ -2752,7 +2828,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>used_very_good</t>
@@ -2760,7 +2835,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>used_good</t>
@@ -2768,14 +2842,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>used_acceptable</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>Metal Type</t>
@@ -2793,7 +2866,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>white_gold</t>
@@ -2801,7 +2873,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>rose_gold</t>
@@ -2809,7 +2880,6 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>two_tone_gold</t>
@@ -2817,7 +2887,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>platinum</t>
@@ -2825,7 +2894,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>sterling_silver</t>
@@ -2833,7 +2901,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>palladium</t>
@@ -2841,7 +2908,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>titanium</t>
@@ -2849,14 +2915,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>stainless_steel</t>
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
           <t>Gem Type</t>
@@ -2874,7 +2939,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>sapphire</t>
@@ -2882,7 +2946,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>ruby</t>
@@ -2890,7 +2953,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>emerald</t>
@@ -2898,7 +2960,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
           <t>pearl</t>
@@ -2906,7 +2967,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>topaz</t>
@@ -2914,7 +2974,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
           <t>amethyst</t>
@@ -2922,7 +2981,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
           <t>garnet</t>
@@ -2930,7 +2988,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
           <t>aquamarine</t>
@@ -2938,7 +2995,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
           <t>opal</t>
@@ -2946,7 +3002,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
           <t>tanzanite</t>
@@ -2954,7 +3009,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>morganite</t>
@@ -2962,7 +3016,6 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
           <t>citrine</t>
@@ -2970,7 +3023,6 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
           <t>peridot</t>
@@ -2978,7 +3030,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
           <t>none</t>
@@ -3003,7 +3054,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
           <t>male</t>
@@ -3011,7 +3061,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>unisex</t>
@@ -3442,7 +3491,7 @@
     <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
           <t>SKU</t>

--- a/Product Listing.xlsx
+++ b/Product Listing.xlsx
@@ -1274,7 +1274,7 @@
       <c r="X3" s="19" t="n"/>
       <c r="Y3" s="19" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="Z3" s="19" t="n"/>

--- a/Product Listing.xlsx
+++ b/Product Listing.xlsx
@@ -1219,11 +1219,7 @@
       </c>
       <c r="Z2" s="19" t="n"/>
       <c r="AA2" s="19" t="n"/>
-      <c r="AB2" s="19" t="inlineStr">
-        <is>
-          <t>Example row — delete or set Include=N once you add your own.</t>
-        </is>
-      </c>
+      <c r="AB2" s="19" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
@@ -1279,11 +1275,7 @@
       </c>
       <c r="Z3" s="19" t="n"/>
       <c r="AA3" s="19" t="n"/>
-      <c r="AB3" s="19" t="inlineStr">
-        <is>
-          <t>Example row — earrings have no size axis, so Variations = none.</t>
-        </is>
-      </c>
+      <c r="AB3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
@@ -1335,11 +1327,7 @@
       <c r="Y4" s="19" t="n"/>
       <c r="Z4" s="19" t="n"/>
       <c r="AA4" s="19" t="n"/>
-      <c r="AB4" s="19" t="inlineStr">
-        <is>
-          <t>Example row, staged (Include = N) so it is skipped.</t>
-        </is>
-      </c>
+      <c r="AB4" s="19" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
@@ -1391,11 +1379,7 @@
       <c r="Y5" s="19" t="n"/>
       <c r="Z5" s="19" t="n"/>
       <c r="AA5" s="19" t="n"/>
-      <c r="AB5" s="19" t="inlineStr">
-        <is>
-          <t>Example row, staged (Include = N) so it is skipped.</t>
-        </is>
-      </c>
+      <c r="AB5" s="19" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n"/>

--- a/Product Listing.xlsx
+++ b/Product Listing.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upload Results" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Products'!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Products'!$A$1:$AB$149</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="1"/>
 </workbook>
@@ -75,7 +75,7 @@
     </font>
     <font/>
   </fonts>
-  <fills count="11">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -127,8 +127,33 @@
         <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFD9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE5D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -151,11 +176,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -196,6 +235,11 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -995,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB45"/>
+  <dimension ref="A1:AB149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1382,1207 +1426,6631 @@
       <c r="AB5" s="19" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n"/>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="12" t="n"/>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="12" t="n"/>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="12" t="n"/>
-      <c r="R6" s="12" t="n"/>
-      <c r="S6" s="12" t="n"/>
-      <c r="T6" s="13" t="n"/>
-      <c r="U6" s="13" t="n"/>
-      <c r="V6" s="13" t="n"/>
-      <c r="W6" s="13" t="n"/>
-      <c r="X6" s="13" t="n"/>
-      <c r="Y6" s="13" t="n"/>
-      <c r="Z6" s="13" t="n"/>
-      <c r="AA6" s="13" t="n"/>
-      <c r="AB6" s="14" t="n"/>
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>N405</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="n"/>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="21" t="n"/>
+      <c r="J6" s="21" t="n"/>
+      <c r="K6" s="21" t="n"/>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="22" t="n"/>
+      <c r="P6" s="22" t="n"/>
+      <c r="Q6" s="22" t="n"/>
+      <c r="R6" s="22" t="n"/>
+      <c r="S6" s="22" t="n"/>
+      <c r="T6" s="23" t="n"/>
+      <c r="U6" s="23" t="n"/>
+      <c r="V6" s="23" t="n"/>
+      <c r="W6" s="23" t="n"/>
+      <c r="X6" s="23" t="n"/>
+      <c r="Y6" s="23" t="n"/>
+      <c r="Z6" s="23" t="n"/>
+      <c r="AA6" s="23" t="n"/>
+      <c r="AB6" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n"/>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="12" t="n"/>
-      <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-      <c r="Q7" s="12" t="n"/>
-      <c r="R7" s="12" t="n"/>
-      <c r="S7" s="12" t="n"/>
-      <c r="T7" s="13" t="n"/>
-      <c r="U7" s="13" t="n"/>
-      <c r="V7" s="13" t="n"/>
-      <c r="W7" s="13" t="n"/>
-      <c r="X7" s="13" t="n"/>
-      <c r="Y7" s="13" t="n"/>
-      <c r="Z7" s="13" t="n"/>
-      <c r="AA7" s="13" t="n"/>
-      <c r="AB7" s="14" t="n"/>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>B229</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="23" t="n"/>
+      <c r="U7" s="23" t="n"/>
+      <c r="V7" s="23" t="n"/>
+      <c r="W7" s="23" t="n"/>
+      <c r="X7" s="23" t="n"/>
+      <c r="Y7" s="23" t="n"/>
+      <c r="Z7" s="23" t="n"/>
+      <c r="AA7" s="23" t="n"/>
+      <c r="AB7" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="12" t="n"/>
-      <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="12" t="n"/>
-      <c r="R8" s="12" t="n"/>
-      <c r="S8" s="12" t="n"/>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="13" t="n"/>
-      <c r="V8" s="13" t="n"/>
-      <c r="W8" s="13" t="n"/>
-      <c r="X8" s="13" t="n"/>
-      <c r="Y8" s="13" t="n"/>
-      <c r="Z8" s="13" t="n"/>
-      <c r="AA8" s="13" t="n"/>
-      <c r="AB8" s="14" t="n"/>
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>B228</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="22" t="n"/>
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="22" t="n"/>
+      <c r="Q8" s="22" t="n"/>
+      <c r="R8" s="22" t="n"/>
+      <c r="S8" s="22" t="n"/>
+      <c r="T8" s="23" t="n"/>
+      <c r="U8" s="23" t="n"/>
+      <c r="V8" s="23" t="n"/>
+      <c r="W8" s="23" t="n"/>
+      <c r="X8" s="23" t="n"/>
+      <c r="Y8" s="23" t="n"/>
+      <c r="Z8" s="23" t="n"/>
+      <c r="AA8" s="23" t="n"/>
+      <c r="AB8" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n"/>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="12" t="n"/>
-      <c r="R9" s="12" t="n"/>
-      <c r="S9" s="12" t="n"/>
-      <c r="T9" s="13" t="n"/>
-      <c r="U9" s="13" t="n"/>
-      <c r="V9" s="13" t="n"/>
-      <c r="W9" s="13" t="n"/>
-      <c r="X9" s="13" t="n"/>
-      <c r="Y9" s="13" t="n"/>
-      <c r="Z9" s="13" t="n"/>
-      <c r="AA9" s="13" t="n"/>
-      <c r="AB9" s="14" t="n"/>
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>B227</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="21" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="22" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="22" t="n"/>
+      <c r="P9" s="22" t="n"/>
+      <c r="Q9" s="22" t="n"/>
+      <c r="R9" s="22" t="n"/>
+      <c r="S9" s="22" t="n"/>
+      <c r="T9" s="23" t="n"/>
+      <c r="U9" s="23" t="n"/>
+      <c r="V9" s="23" t="n"/>
+      <c r="W9" s="23" t="n"/>
+      <c r="X9" s="23" t="n"/>
+      <c r="Y9" s="23" t="n"/>
+      <c r="Z9" s="23" t="n"/>
+      <c r="AA9" s="23" t="n"/>
+      <c r="AB9" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-      <c r="Q10" s="12" t="n"/>
-      <c r="R10" s="12" t="n"/>
-      <c r="S10" s="12" t="n"/>
-      <c r="T10" s="13" t="n"/>
-      <c r="U10" s="13" t="n"/>
-      <c r="V10" s="13" t="n"/>
-      <c r="W10" s="13" t="n"/>
-      <c r="X10" s="13" t="n"/>
-      <c r="Y10" s="13" t="n"/>
-      <c r="Z10" s="13" t="n"/>
-      <c r="AA10" s="13" t="n"/>
-      <c r="AB10" s="14" t="n"/>
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>B226</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="22" t="n"/>
+      <c r="R10" s="22" t="n"/>
+      <c r="S10" s="22" t="n"/>
+      <c r="T10" s="23" t="n"/>
+      <c r="U10" s="23" t="n"/>
+      <c r="V10" s="23" t="n"/>
+      <c r="W10" s="23" t="n"/>
+      <c r="X10" s="23" t="n"/>
+      <c r="Y10" s="23" t="n"/>
+      <c r="Z10" s="23" t="n"/>
+      <c r="AA10" s="23" t="n"/>
+      <c r="AB10" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
-      <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="12" t="n"/>
-      <c r="R11" s="12" t="n"/>
-      <c r="S11" s="12" t="n"/>
-      <c r="T11" s="13" t="n"/>
-      <c r="U11" s="13" t="n"/>
-      <c r="V11" s="13" t="n"/>
-      <c r="W11" s="13" t="n"/>
-      <c r="X11" s="13" t="n"/>
-      <c r="Y11" s="13" t="n"/>
-      <c r="Z11" s="13" t="n"/>
-      <c r="AA11" s="13" t="n"/>
-      <c r="AB11" s="14" t="n"/>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>B225</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="22" t="n"/>
+      <c r="R11" s="22" t="n"/>
+      <c r="S11" s="22" t="n"/>
+      <c r="T11" s="23" t="n"/>
+      <c r="U11" s="23" t="n"/>
+      <c r="V11" s="23" t="n"/>
+      <c r="W11" s="23" t="n"/>
+      <c r="X11" s="23" t="n"/>
+      <c r="Y11" s="23" t="n"/>
+      <c r="Z11" s="23" t="n"/>
+      <c r="AA11" s="23" t="n"/>
+      <c r="AB11" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="11" t="n"/>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
-      <c r="Q12" s="12" t="n"/>
-      <c r="R12" s="12" t="n"/>
-      <c r="S12" s="12" t="n"/>
-      <c r="T12" s="13" t="n"/>
-      <c r="U12" s="13" t="n"/>
-      <c r="V12" s="13" t="n"/>
-      <c r="W12" s="13" t="n"/>
-      <c r="X12" s="13" t="n"/>
-      <c r="Y12" s="13" t="n"/>
-      <c r="Z12" s="13" t="n"/>
-      <c r="AA12" s="13" t="n"/>
-      <c r="AB12" s="14" t="n"/>
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>B224</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="21" t="n"/>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="22" t="n"/>
+      <c r="R12" s="22" t="n"/>
+      <c r="S12" s="22" t="n"/>
+      <c r="T12" s="23" t="n"/>
+      <c r="U12" s="23" t="n"/>
+      <c r="V12" s="23" t="n"/>
+      <c r="W12" s="23" t="n"/>
+      <c r="X12" s="23" t="n"/>
+      <c r="Y12" s="23" t="n"/>
+      <c r="Z12" s="23" t="n"/>
+      <c r="AA12" s="23" t="n"/>
+      <c r="AB12" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-      <c r="Q13" s="12" t="n"/>
-      <c r="R13" s="12" t="n"/>
-      <c r="S13" s="12" t="n"/>
-      <c r="T13" s="13" t="n"/>
-      <c r="U13" s="13" t="n"/>
-      <c r="V13" s="13" t="n"/>
-      <c r="W13" s="13" t="n"/>
-      <c r="X13" s="13" t="n"/>
-      <c r="Y13" s="13" t="n"/>
-      <c r="Z13" s="13" t="n"/>
-      <c r="AA13" s="13" t="n"/>
-      <c r="AB13" s="14" t="n"/>
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>B223</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="21" t="n"/>
+      <c r="J13" s="21" t="n"/>
+      <c r="K13" s="21" t="n"/>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="22" t="n"/>
+      <c r="N13" s="22" t="n"/>
+      <c r="O13" s="22" t="n"/>
+      <c r="P13" s="22" t="n"/>
+      <c r="Q13" s="22" t="n"/>
+      <c r="R13" s="22" t="n"/>
+      <c r="S13" s="22" t="n"/>
+      <c r="T13" s="23" t="n"/>
+      <c r="U13" s="23" t="n"/>
+      <c r="V13" s="23" t="n"/>
+      <c r="W13" s="23" t="n"/>
+      <c r="X13" s="23" t="n"/>
+      <c r="Y13" s="23" t="n"/>
+      <c r="Z13" s="23" t="n"/>
+      <c r="AA13" s="23" t="n"/>
+      <c r="AB13" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
-      <c r="N14" s="12" t="n"/>
-      <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
-      <c r="Q14" s="12" t="n"/>
-      <c r="R14" s="12" t="n"/>
-      <c r="S14" s="12" t="n"/>
-      <c r="T14" s="13" t="n"/>
-      <c r="U14" s="13" t="n"/>
-      <c r="V14" s="13" t="n"/>
-      <c r="W14" s="13" t="n"/>
-      <c r="X14" s="13" t="n"/>
-      <c r="Y14" s="13" t="n"/>
-      <c r="Z14" s="13" t="n"/>
-      <c r="AA14" s="13" t="n"/>
-      <c r="AB14" s="14" t="n"/>
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>B222</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="21" t="n"/>
+      <c r="J14" s="21" t="n"/>
+      <c r="K14" s="21" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="22" t="n"/>
+      <c r="R14" s="22" t="n"/>
+      <c r="S14" s="22" t="n"/>
+      <c r="T14" s="23" t="n"/>
+      <c r="U14" s="23" t="n"/>
+      <c r="V14" s="23" t="n"/>
+      <c r="W14" s="23" t="n"/>
+      <c r="X14" s="23" t="n"/>
+      <c r="Y14" s="23" t="n"/>
+      <c r="Z14" s="23" t="n"/>
+      <c r="AA14" s="23" t="n"/>
+      <c r="AB14" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
-      <c r="N15" s="12" t="n"/>
-      <c r="O15" s="12" t="n"/>
-      <c r="P15" s="12" t="n"/>
-      <c r="Q15" s="12" t="n"/>
-      <c r="R15" s="12" t="n"/>
-      <c r="S15" s="12" t="n"/>
-      <c r="T15" s="13" t="n"/>
-      <c r="U15" s="13" t="n"/>
-      <c r="V15" s="13" t="n"/>
-      <c r="W15" s="13" t="n"/>
-      <c r="X15" s="13" t="n"/>
-      <c r="Y15" s="13" t="n"/>
-      <c r="Z15" s="13" t="n"/>
-      <c r="AA15" s="13" t="n"/>
-      <c r="AB15" s="14" t="n"/>
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>B221</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="21" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="21" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="22" t="n"/>
+      <c r="Q15" s="22" t="n"/>
+      <c r="R15" s="22" t="n"/>
+      <c r="S15" s="22" t="n"/>
+      <c r="T15" s="23" t="n"/>
+      <c r="U15" s="23" t="n"/>
+      <c r="V15" s="23" t="n"/>
+      <c r="W15" s="23" t="n"/>
+      <c r="X15" s="23" t="n"/>
+      <c r="Y15" s="23" t="n"/>
+      <c r="Z15" s="23" t="n"/>
+      <c r="AA15" s="23" t="n"/>
+      <c r="AB15" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="11" t="n"/>
-      <c r="K16" s="11" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
-      <c r="Q16" s="12" t="n"/>
-      <c r="R16" s="12" t="n"/>
-      <c r="S16" s="12" t="n"/>
-      <c r="T16" s="13" t="n"/>
-      <c r="U16" s="13" t="n"/>
-      <c r="V16" s="13" t="n"/>
-      <c r="W16" s="13" t="n"/>
-      <c r="X16" s="13" t="n"/>
-      <c r="Y16" s="13" t="n"/>
-      <c r="Z16" s="13" t="n"/>
-      <c r="AA16" s="13" t="n"/>
-      <c r="AB16" s="14" t="n"/>
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>B220</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="21" t="n"/>
+      <c r="J16" s="21" t="n"/>
+      <c r="K16" s="21" t="n"/>
+      <c r="L16" s="22" t="n"/>
+      <c r="M16" s="22" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="22" t="n"/>
+      <c r="P16" s="22" t="n"/>
+      <c r="Q16" s="22" t="n"/>
+      <c r="R16" s="22" t="n"/>
+      <c r="S16" s="22" t="n"/>
+      <c r="T16" s="23" t="n"/>
+      <c r="U16" s="23" t="n"/>
+      <c r="V16" s="23" t="n"/>
+      <c r="W16" s="23" t="n"/>
+      <c r="X16" s="23" t="n"/>
+      <c r="Y16" s="23" t="n"/>
+      <c r="Z16" s="23" t="n"/>
+      <c r="AA16" s="23" t="n"/>
+      <c r="AB16" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="11" t="n"/>
-      <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
-      <c r="Q17" s="12" t="n"/>
-      <c r="R17" s="12" t="n"/>
-      <c r="S17" s="12" t="n"/>
-      <c r="T17" s="13" t="n"/>
-      <c r="U17" s="13" t="n"/>
-      <c r="V17" s="13" t="n"/>
-      <c r="W17" s="13" t="n"/>
-      <c r="X17" s="13" t="n"/>
-      <c r="Y17" s="13" t="n"/>
-      <c r="Z17" s="13" t="n"/>
-      <c r="AA17" s="13" t="n"/>
-      <c r="AB17" s="14" t="n"/>
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>B219</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="21" t="n"/>
+      <c r="J17" s="21" t="n"/>
+      <c r="K17" s="21" t="n"/>
+      <c r="L17" s="22" t="n"/>
+      <c r="M17" s="22" t="n"/>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="22" t="n"/>
+      <c r="Q17" s="22" t="n"/>
+      <c r="R17" s="22" t="n"/>
+      <c r="S17" s="22" t="n"/>
+      <c r="T17" s="23" t="n"/>
+      <c r="U17" s="23" t="n"/>
+      <c r="V17" s="23" t="n"/>
+      <c r="W17" s="23" t="n"/>
+      <c r="X17" s="23" t="n"/>
+      <c r="Y17" s="23" t="n"/>
+      <c r="Z17" s="23" t="n"/>
+      <c r="AA17" s="23" t="n"/>
+      <c r="AB17" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="11" t="n"/>
-      <c r="J18" s="11" t="n"/>
-      <c r="K18" s="11" t="n"/>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
-      <c r="Q18" s="12" t="n"/>
-      <c r="R18" s="12" t="n"/>
-      <c r="S18" s="12" t="n"/>
-      <c r="T18" s="13" t="n"/>
-      <c r="U18" s="13" t="n"/>
-      <c r="V18" s="13" t="n"/>
-      <c r="W18" s="13" t="n"/>
-      <c r="X18" s="13" t="n"/>
-      <c r="Y18" s="13" t="n"/>
-      <c r="Z18" s="13" t="n"/>
-      <c r="AA18" s="13" t="n"/>
-      <c r="AB18" s="14" t="n"/>
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>B218</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="n"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="21" t="n"/>
+      <c r="J18" s="21" t="n"/>
+      <c r="K18" s="21" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22" t="n"/>
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="22" t="n"/>
+      <c r="R18" s="22" t="n"/>
+      <c r="S18" s="22" t="n"/>
+      <c r="T18" s="23" t="n"/>
+      <c r="U18" s="23" t="n"/>
+      <c r="V18" s="23" t="n"/>
+      <c r="W18" s="23" t="n"/>
+      <c r="X18" s="23" t="n"/>
+      <c r="Y18" s="23" t="n"/>
+      <c r="Z18" s="23" t="n"/>
+      <c r="AA18" s="23" t="n"/>
+      <c r="AB18" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="11" t="n"/>
-      <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="12" t="n"/>
-      <c r="O19" s="12" t="n"/>
-      <c r="P19" s="12" t="n"/>
-      <c r="Q19" s="12" t="n"/>
-      <c r="R19" s="12" t="n"/>
-      <c r="S19" s="12" t="n"/>
-      <c r="T19" s="13" t="n"/>
-      <c r="U19" s="13" t="n"/>
-      <c r="V19" s="13" t="n"/>
-      <c r="W19" s="13" t="n"/>
-      <c r="X19" s="13" t="n"/>
-      <c r="Y19" s="13" t="n"/>
-      <c r="Z19" s="13" t="n"/>
-      <c r="AA19" s="13" t="n"/>
-      <c r="AB19" s="14" t="n"/>
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>B216</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+      <c r="I19" s="21" t="n"/>
+      <c r="J19" s="21" t="n"/>
+      <c r="K19" s="21" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="n"/>
+      <c r="S19" s="22" t="n"/>
+      <c r="T19" s="23" t="n"/>
+      <c r="U19" s="23" t="n"/>
+      <c r="V19" s="23" t="n"/>
+      <c r="W19" s="23" t="n"/>
+      <c r="X19" s="23" t="n"/>
+      <c r="Y19" s="23" t="n"/>
+      <c r="Z19" s="23" t="n"/>
+      <c r="AA19" s="23" t="n"/>
+      <c r="AB19" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="11" t="n"/>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="11" t="n"/>
-      <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="12" t="n"/>
-      <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
-      <c r="Q20" s="12" t="n"/>
-      <c r="R20" s="12" t="n"/>
-      <c r="S20" s="12" t="n"/>
-      <c r="T20" s="13" t="n"/>
-      <c r="U20" s="13" t="n"/>
-      <c r="V20" s="13" t="n"/>
-      <c r="W20" s="13" t="n"/>
-      <c r="X20" s="13" t="n"/>
-      <c r="Y20" s="13" t="n"/>
-      <c r="Z20" s="13" t="n"/>
-      <c r="AA20" s="13" t="n"/>
-      <c r="AB20" s="14" t="n"/>
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>B215</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="21" t="n"/>
+      <c r="J20" s="21" t="n"/>
+      <c r="K20" s="21" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="23" t="n"/>
+      <c r="U20" s="23" t="n"/>
+      <c r="V20" s="23" t="n"/>
+      <c r="W20" s="23" t="n"/>
+      <c r="X20" s="23" t="n"/>
+      <c r="Y20" s="23" t="n"/>
+      <c r="Z20" s="23" t="n"/>
+      <c r="AA20" s="23" t="n"/>
+      <c r="AB20" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="11" t="n"/>
-      <c r="K21" s="11" t="n"/>
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="12" t="n"/>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="12" t="n"/>
-      <c r="R21" s="12" t="n"/>
-      <c r="S21" s="12" t="n"/>
-      <c r="T21" s="13" t="n"/>
-      <c r="U21" s="13" t="n"/>
-      <c r="V21" s="13" t="n"/>
-      <c r="W21" s="13" t="n"/>
-      <c r="X21" s="13" t="n"/>
-      <c r="Y21" s="13" t="n"/>
-      <c r="Z21" s="13" t="n"/>
-      <c r="AA21" s="13" t="n"/>
-      <c r="AB21" s="14" t="n"/>
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>B214</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="21" t="n"/>
+      <c r="J21" s="21" t="n"/>
+      <c r="K21" s="21" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="22" t="n"/>
+      <c r="R21" s="22" t="n"/>
+      <c r="S21" s="22" t="n"/>
+      <c r="T21" s="23" t="n"/>
+      <c r="U21" s="23" t="n"/>
+      <c r="V21" s="23" t="n"/>
+      <c r="W21" s="23" t="n"/>
+      <c r="X21" s="23" t="n"/>
+      <c r="Y21" s="23" t="n"/>
+      <c r="Z21" s="23" t="n"/>
+      <c r="AA21" s="23" t="n"/>
+      <c r="AB21" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n"/>
-      <c r="I22" s="11" t="n"/>
-      <c r="J22" s="11" t="n"/>
-      <c r="K22" s="11" t="n"/>
-      <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="12" t="n"/>
-      <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="12" t="n"/>
-      <c r="R22" s="12" t="n"/>
-      <c r="S22" s="12" t="n"/>
-      <c r="T22" s="13" t="n"/>
-      <c r="U22" s="13" t="n"/>
-      <c r="V22" s="13" t="n"/>
-      <c r="W22" s="13" t="n"/>
-      <c r="X22" s="13" t="n"/>
-      <c r="Y22" s="13" t="n"/>
-      <c r="Z22" s="13" t="n"/>
-      <c r="AA22" s="13" t="n"/>
-      <c r="AB22" s="14" t="n"/>
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>B213</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="21" t="n"/>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="21" t="n"/>
+      <c r="J22" s="21" t="n"/>
+      <c r="K22" s="21" t="n"/>
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="22" t="n"/>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="22" t="n"/>
+      <c r="P22" s="22" t="n"/>
+      <c r="Q22" s="22" t="n"/>
+      <c r="R22" s="22" t="n"/>
+      <c r="S22" s="22" t="n"/>
+      <c r="T22" s="23" t="n"/>
+      <c r="U22" s="23" t="n"/>
+      <c r="V22" s="23" t="n"/>
+      <c r="W22" s="23" t="n"/>
+      <c r="X22" s="23" t="n"/>
+      <c r="Y22" s="23" t="n"/>
+      <c r="Z22" s="23" t="n"/>
+      <c r="AA22" s="23" t="n"/>
+      <c r="AB22" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="11" t="n"/>
-      <c r="K23" s="11" t="n"/>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n"/>
-      <c r="O23" s="12" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="12" t="n"/>
-      <c r="R23" s="12" t="n"/>
-      <c r="S23" s="12" t="n"/>
-      <c r="T23" s="13" t="n"/>
-      <c r="U23" s="13" t="n"/>
-      <c r="V23" s="13" t="n"/>
-      <c r="W23" s="13" t="n"/>
-      <c r="X23" s="13" t="n"/>
-      <c r="Y23" s="13" t="n"/>
-      <c r="Z23" s="13" t="n"/>
-      <c r="AA23" s="13" t="n"/>
-      <c r="AB23" s="14" t="n"/>
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>B211</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="21" t="n"/>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="21" t="n"/>
+      <c r="L23" s="22" t="n"/>
+      <c r="M23" s="22" t="n"/>
+      <c r="N23" s="22" t="n"/>
+      <c r="O23" s="22" t="n"/>
+      <c r="P23" s="22" t="n"/>
+      <c r="Q23" s="22" t="n"/>
+      <c r="R23" s="22" t="n"/>
+      <c r="S23" s="22" t="n"/>
+      <c r="T23" s="23" t="n"/>
+      <c r="U23" s="23" t="n"/>
+      <c r="V23" s="23" t="n"/>
+      <c r="W23" s="23" t="n"/>
+      <c r="X23" s="23" t="n"/>
+      <c r="Y23" s="23" t="n"/>
+      <c r="Z23" s="23" t="n"/>
+      <c r="AA23" s="23" t="n"/>
+      <c r="AB23" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n"/>
-      <c r="I24" s="11" t="n"/>
-      <c r="J24" s="11" t="n"/>
-      <c r="K24" s="11" t="n"/>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="12" t="n"/>
-      <c r="R24" s="12" t="n"/>
-      <c r="S24" s="12" t="n"/>
-      <c r="T24" s="13" t="n"/>
-      <c r="U24" s="13" t="n"/>
-      <c r="V24" s="13" t="n"/>
-      <c r="W24" s="13" t="n"/>
-      <c r="X24" s="13" t="n"/>
-      <c r="Y24" s="13" t="n"/>
-      <c r="Z24" s="13" t="n"/>
-      <c r="AA24" s="13" t="n"/>
-      <c r="AB24" s="14" t="n"/>
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>B210</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
+      <c r="J24" s="21" t="n"/>
+      <c r="K24" s="21" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22" t="n"/>
+      <c r="P24" s="22" t="n"/>
+      <c r="Q24" s="22" t="n"/>
+      <c r="R24" s="22" t="n"/>
+      <c r="S24" s="22" t="n"/>
+      <c r="T24" s="23" t="n"/>
+      <c r="U24" s="23" t="n"/>
+      <c r="V24" s="23" t="n"/>
+      <c r="W24" s="23" t="n"/>
+      <c r="X24" s="23" t="n"/>
+      <c r="Y24" s="23" t="n"/>
+      <c r="Z24" s="23" t="n"/>
+      <c r="AA24" s="23" t="n"/>
+      <c r="AB24" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="11" t="n"/>
-      <c r="K25" s="11" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="12" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="12" t="n"/>
-      <c r="R25" s="12" t="n"/>
-      <c r="S25" s="12" t="n"/>
-      <c r="T25" s="13" t="n"/>
-      <c r="U25" s="13" t="n"/>
-      <c r="V25" s="13" t="n"/>
-      <c r="W25" s="13" t="n"/>
-      <c r="X25" s="13" t="n"/>
-      <c r="Y25" s="13" t="n"/>
-      <c r="Z25" s="13" t="n"/>
-      <c r="AA25" s="13" t="n"/>
-      <c r="AB25" s="14" t="n"/>
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>B170</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="21" t="n"/>
+      <c r="J25" s="21" t="n"/>
+      <c r="K25" s="21" t="n"/>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="22" t="n"/>
+      <c r="N25" s="22" t="n"/>
+      <c r="O25" s="22" t="n"/>
+      <c r="P25" s="22" t="n"/>
+      <c r="Q25" s="22" t="n"/>
+      <c r="R25" s="22" t="n"/>
+      <c r="S25" s="22" t="n"/>
+      <c r="T25" s="23" t="n"/>
+      <c r="U25" s="23" t="n"/>
+      <c r="V25" s="23" t="n"/>
+      <c r="W25" s="23" t="n"/>
+      <c r="X25" s="23" t="n"/>
+      <c r="Y25" s="23" t="n"/>
+      <c r="Z25" s="23" t="n"/>
+      <c r="AA25" s="23" t="n"/>
+      <c r="AB25" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="11" t="n"/>
-      <c r="I26" s="11" t="n"/>
-      <c r="J26" s="11" t="n"/>
-      <c r="K26" s="11" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n"/>
-      <c r="O26" s="12" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="12" t="n"/>
-      <c r="R26" s="12" t="n"/>
-      <c r="S26" s="12" t="n"/>
-      <c r="T26" s="13" t="n"/>
-      <c r="U26" s="13" t="n"/>
-      <c r="V26" s="13" t="n"/>
-      <c r="W26" s="13" t="n"/>
-      <c r="X26" s="13" t="n"/>
-      <c r="Y26" s="13" t="n"/>
-      <c r="Z26" s="13" t="n"/>
-      <c r="AA26" s="13" t="n"/>
-      <c r="AB26" s="14" t="n"/>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>B106</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="21" t="n"/>
+      <c r="J26" s="21" t="n"/>
+      <c r="K26" s="21" t="n"/>
+      <c r="L26" s="22" t="n"/>
+      <c r="M26" s="22" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="22" t="n"/>
+      <c r="P26" s="22" t="n"/>
+      <c r="Q26" s="22" t="n"/>
+      <c r="R26" s="22" t="n"/>
+      <c r="S26" s="22" t="n"/>
+      <c r="T26" s="23" t="n"/>
+      <c r="U26" s="23" t="n"/>
+      <c r="V26" s="23" t="n"/>
+      <c r="W26" s="23" t="n"/>
+      <c r="X26" s="23" t="n"/>
+      <c r="Y26" s="23" t="n"/>
+      <c r="Z26" s="23" t="n"/>
+      <c r="AA26" s="23" t="n"/>
+      <c r="AB26" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Bracelets</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="11" t="n"/>
-      <c r="K27" s="11" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="12" t="n"/>
-      <c r="O27" s="12" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="12" t="n"/>
-      <c r="R27" s="12" t="n"/>
-      <c r="S27" s="12" t="n"/>
-      <c r="T27" s="13" t="n"/>
-      <c r="U27" s="13" t="n"/>
-      <c r="V27" s="13" t="n"/>
-      <c r="W27" s="13" t="n"/>
-      <c r="X27" s="13" t="n"/>
-      <c r="Y27" s="13" t="n"/>
-      <c r="Z27" s="13" t="n"/>
-      <c r="AA27" s="13" t="n"/>
-      <c r="AB27" s="14" t="n"/>
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>S250</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="21" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="21" t="n"/>
+      <c r="J27" s="21" t="n"/>
+      <c r="K27" s="21" t="n"/>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="22" t="n"/>
+      <c r="N27" s="22" t="n"/>
+      <c r="O27" s="22" t="n"/>
+      <c r="P27" s="22" t="n"/>
+      <c r="Q27" s="22" t="n"/>
+      <c r="R27" s="22" t="n"/>
+      <c r="S27" s="22" t="n"/>
+      <c r="T27" s="23" t="n"/>
+      <c r="U27" s="23" t="n"/>
+      <c r="V27" s="23" t="n"/>
+      <c r="W27" s="23" t="n"/>
+      <c r="X27" s="23" t="n"/>
+      <c r="Y27" s="23" t="n"/>
+      <c r="Z27" s="23" t="n"/>
+      <c r="AA27" s="23" t="n"/>
+      <c r="AB27" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="11" t="n"/>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="11" t="n"/>
-      <c r="K28" s="11" t="n"/>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="12" t="n"/>
-      <c r="O28" s="12" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="12" t="n"/>
-      <c r="R28" s="12" t="n"/>
-      <c r="S28" s="12" t="n"/>
-      <c r="T28" s="13" t="n"/>
-      <c r="U28" s="13" t="n"/>
-      <c r="V28" s="13" t="n"/>
-      <c r="W28" s="13" t="n"/>
-      <c r="X28" s="13" t="n"/>
-      <c r="Y28" s="13" t="n"/>
-      <c r="Z28" s="13" t="n"/>
-      <c r="AA28" s="13" t="n"/>
-      <c r="AB28" s="14" t="n"/>
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>S249</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="21" t="n"/>
+      <c r="J28" s="21" t="n"/>
+      <c r="K28" s="21" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="22" t="n"/>
+      <c r="N28" s="22" t="n"/>
+      <c r="O28" s="22" t="n"/>
+      <c r="P28" s="22" t="n"/>
+      <c r="Q28" s="22" t="n"/>
+      <c r="R28" s="22" t="n"/>
+      <c r="S28" s="22" t="n"/>
+      <c r="T28" s="23" t="n"/>
+      <c r="U28" s="23" t="n"/>
+      <c r="V28" s="23" t="n"/>
+      <c r="W28" s="23" t="n"/>
+      <c r="X28" s="23" t="n"/>
+      <c r="Y28" s="23" t="n"/>
+      <c r="Z28" s="23" t="n"/>
+      <c r="AA28" s="23" t="n"/>
+      <c r="AB28" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="12" t="n"/>
-      <c r="P29" s="12" t="n"/>
-      <c r="Q29" s="12" t="n"/>
-      <c r="R29" s="12" t="n"/>
-      <c r="S29" s="12" t="n"/>
-      <c r="T29" s="13" t="n"/>
-      <c r="U29" s="13" t="n"/>
-      <c r="V29" s="13" t="n"/>
-      <c r="W29" s="13" t="n"/>
-      <c r="X29" s="13" t="n"/>
-      <c r="Y29" s="13" t="n"/>
-      <c r="Z29" s="13" t="n"/>
-      <c r="AA29" s="13" t="n"/>
-      <c r="AB29" s="14" t="n"/>
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>S248</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="21" t="n"/>
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="21" t="n"/>
+      <c r="J29" s="21" t="n"/>
+      <c r="K29" s="21" t="n"/>
+      <c r="L29" s="22" t="n"/>
+      <c r="M29" s="22" t="n"/>
+      <c r="N29" s="22" t="n"/>
+      <c r="O29" s="22" t="n"/>
+      <c r="P29" s="22" t="n"/>
+      <c r="Q29" s="22" t="n"/>
+      <c r="R29" s="22" t="n"/>
+      <c r="S29" s="22" t="n"/>
+      <c r="T29" s="23" t="n"/>
+      <c r="U29" s="23" t="n"/>
+      <c r="V29" s="23" t="n"/>
+      <c r="W29" s="23" t="n"/>
+      <c r="X29" s="23" t="n"/>
+      <c r="Y29" s="23" t="n"/>
+      <c r="Z29" s="23" t="n"/>
+      <c r="AA29" s="23" t="n"/>
+      <c r="AB29" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="n"/>
-      <c r="I30" s="11" t="n"/>
-      <c r="J30" s="11" t="n"/>
-      <c r="K30" s="11" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="12" t="n"/>
-      <c r="P30" s="12" t="n"/>
-      <c r="Q30" s="12" t="n"/>
-      <c r="R30" s="12" t="n"/>
-      <c r="S30" s="12" t="n"/>
-      <c r="T30" s="13" t="n"/>
-      <c r="U30" s="13" t="n"/>
-      <c r="V30" s="13" t="n"/>
-      <c r="W30" s="13" t="n"/>
-      <c r="X30" s="13" t="n"/>
-      <c r="Y30" s="13" t="n"/>
-      <c r="Z30" s="13" t="n"/>
-      <c r="AA30" s="13" t="n"/>
-      <c r="AB30" s="14" t="n"/>
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>S247</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="21" t="n"/>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="21" t="n"/>
+      <c r="J30" s="21" t="n"/>
+      <c r="K30" s="21" t="n"/>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="22" t="n"/>
+      <c r="N30" s="22" t="n"/>
+      <c r="O30" s="22" t="n"/>
+      <c r="P30" s="22" t="n"/>
+      <c r="Q30" s="22" t="n"/>
+      <c r="R30" s="22" t="n"/>
+      <c r="S30" s="22" t="n"/>
+      <c r="T30" s="23" t="n"/>
+      <c r="U30" s="23" t="n"/>
+      <c r="V30" s="23" t="n"/>
+      <c r="W30" s="23" t="n"/>
+      <c r="X30" s="23" t="n"/>
+      <c r="Y30" s="23" t="n"/>
+      <c r="Z30" s="23" t="n"/>
+      <c r="AA30" s="23" t="n"/>
+      <c r="AB30" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="11" t="n"/>
-      <c r="J31" s="11" t="n"/>
-      <c r="K31" s="11" t="n"/>
-      <c r="L31" s="12" t="n"/>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="12" t="n"/>
-      <c r="O31" s="12" t="n"/>
-      <c r="P31" s="12" t="n"/>
-      <c r="Q31" s="12" t="n"/>
-      <c r="R31" s="12" t="n"/>
-      <c r="S31" s="12" t="n"/>
-      <c r="T31" s="13" t="n"/>
-      <c r="U31" s="13" t="n"/>
-      <c r="V31" s="13" t="n"/>
-      <c r="W31" s="13" t="n"/>
-      <c r="X31" s="13" t="n"/>
-      <c r="Y31" s="13" t="n"/>
-      <c r="Z31" s="13" t="n"/>
-      <c r="AA31" s="13" t="n"/>
-      <c r="AB31" s="14" t="n"/>
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>S246</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="n"/>
+      <c r="G31" s="21" t="n"/>
+      <c r="H31" s="21" t="n"/>
+      <c r="I31" s="21" t="n"/>
+      <c r="J31" s="21" t="n"/>
+      <c r="K31" s="21" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="22" t="n"/>
+      <c r="N31" s="22" t="n"/>
+      <c r="O31" s="22" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="22" t="n"/>
+      <c r="R31" s="22" t="n"/>
+      <c r="S31" s="22" t="n"/>
+      <c r="T31" s="23" t="n"/>
+      <c r="U31" s="23" t="n"/>
+      <c r="V31" s="23" t="n"/>
+      <c r="W31" s="23" t="n"/>
+      <c r="X31" s="23" t="n"/>
+      <c r="Y31" s="23" t="n"/>
+      <c r="Z31" s="23" t="n"/>
+      <c r="AA31" s="23" t="n"/>
+      <c r="AB31" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="11" t="n"/>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
-      <c r="O32" s="12" t="n"/>
-      <c r="P32" s="12" t="n"/>
-      <c r="Q32" s="12" t="n"/>
-      <c r="R32" s="12" t="n"/>
-      <c r="S32" s="12" t="n"/>
-      <c r="T32" s="13" t="n"/>
-      <c r="U32" s="13" t="n"/>
-      <c r="V32" s="13" t="n"/>
-      <c r="W32" s="13" t="n"/>
-      <c r="X32" s="13" t="n"/>
-      <c r="Y32" s="13" t="n"/>
-      <c r="Z32" s="13" t="n"/>
-      <c r="AA32" s="13" t="n"/>
-      <c r="AB32" s="14" t="n"/>
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>S245</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="n"/>
+      <c r="G32" s="21" t="n"/>
+      <c r="H32" s="21" t="n"/>
+      <c r="I32" s="21" t="n"/>
+      <c r="J32" s="21" t="n"/>
+      <c r="K32" s="21" t="n"/>
+      <c r="L32" s="22" t="n"/>
+      <c r="M32" s="22" t="n"/>
+      <c r="N32" s="22" t="n"/>
+      <c r="O32" s="22" t="n"/>
+      <c r="P32" s="22" t="n"/>
+      <c r="Q32" s="22" t="n"/>
+      <c r="R32" s="22" t="n"/>
+      <c r="S32" s="22" t="n"/>
+      <c r="T32" s="23" t="n"/>
+      <c r="U32" s="23" t="n"/>
+      <c r="V32" s="23" t="n"/>
+      <c r="W32" s="23" t="n"/>
+      <c r="X32" s="23" t="n"/>
+      <c r="Y32" s="23" t="n"/>
+      <c r="Z32" s="23" t="n"/>
+      <c r="AA32" s="23" t="n"/>
+      <c r="AB32" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="11" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="12" t="n"/>
-      <c r="O33" s="12" t="n"/>
-      <c r="P33" s="12" t="n"/>
-      <c r="Q33" s="12" t="n"/>
-      <c r="R33" s="12" t="n"/>
-      <c r="S33" s="12" t="n"/>
-      <c r="T33" s="13" t="n"/>
-      <c r="U33" s="13" t="n"/>
-      <c r="V33" s="13" t="n"/>
-      <c r="W33" s="13" t="n"/>
-      <c r="X33" s="13" t="n"/>
-      <c r="Y33" s="13" t="n"/>
-      <c r="Z33" s="13" t="n"/>
-      <c r="AA33" s="13" t="n"/>
-      <c r="AB33" s="14" t="n"/>
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>S244</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="21" t="n"/>
+      <c r="I33" s="21" t="n"/>
+      <c r="J33" s="21" t="n"/>
+      <c r="K33" s="21" t="n"/>
+      <c r="L33" s="22" t="n"/>
+      <c r="M33" s="22" t="n"/>
+      <c r="N33" s="22" t="n"/>
+      <c r="O33" s="22" t="n"/>
+      <c r="P33" s="22" t="n"/>
+      <c r="Q33" s="22" t="n"/>
+      <c r="R33" s="22" t="n"/>
+      <c r="S33" s="22" t="n"/>
+      <c r="T33" s="23" t="n"/>
+      <c r="U33" s="23" t="n"/>
+      <c r="V33" s="23" t="n"/>
+      <c r="W33" s="23" t="n"/>
+      <c r="X33" s="23" t="n"/>
+      <c r="Y33" s="23" t="n"/>
+      <c r="Z33" s="23" t="n"/>
+      <c r="AA33" s="23" t="n"/>
+      <c r="AB33" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="11" t="n"/>
-      <c r="I34" s="11" t="n"/>
-      <c r="J34" s="11" t="n"/>
-      <c r="K34" s="11" t="n"/>
-      <c r="L34" s="12" t="n"/>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="12" t="n"/>
-      <c r="O34" s="12" t="n"/>
-      <c r="P34" s="12" t="n"/>
-      <c r="Q34" s="12" t="n"/>
-      <c r="R34" s="12" t="n"/>
-      <c r="S34" s="12" t="n"/>
-      <c r="T34" s="13" t="n"/>
-      <c r="U34" s="13" t="n"/>
-      <c r="V34" s="13" t="n"/>
-      <c r="W34" s="13" t="n"/>
-      <c r="X34" s="13" t="n"/>
-      <c r="Y34" s="13" t="n"/>
-      <c r="Z34" s="13" t="n"/>
-      <c r="AA34" s="13" t="n"/>
-      <c r="AB34" s="14" t="n"/>
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>S243</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="n"/>
+      <c r="G34" s="21" t="n"/>
+      <c r="H34" s="21" t="n"/>
+      <c r="I34" s="21" t="n"/>
+      <c r="J34" s="21" t="n"/>
+      <c r="K34" s="21" t="n"/>
+      <c r="L34" s="22" t="n"/>
+      <c r="M34" s="22" t="n"/>
+      <c r="N34" s="22" t="n"/>
+      <c r="O34" s="22" t="n"/>
+      <c r="P34" s="22" t="n"/>
+      <c r="Q34" s="22" t="n"/>
+      <c r="R34" s="22" t="n"/>
+      <c r="S34" s="22" t="n"/>
+      <c r="T34" s="23" t="n"/>
+      <c r="U34" s="23" t="n"/>
+      <c r="V34" s="23" t="n"/>
+      <c r="W34" s="23" t="n"/>
+      <c r="X34" s="23" t="n"/>
+      <c r="Y34" s="23" t="n"/>
+      <c r="Z34" s="23" t="n"/>
+      <c r="AA34" s="23" t="n"/>
+      <c r="AB34" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="11" t="n"/>
-      <c r="J35" s="11" t="n"/>
-      <c r="K35" s="11" t="n"/>
-      <c r="L35" s="12" t="n"/>
-      <c r="M35" s="12" t="n"/>
-      <c r="N35" s="12" t="n"/>
-      <c r="O35" s="12" t="n"/>
-      <c r="P35" s="12" t="n"/>
-      <c r="Q35" s="12" t="n"/>
-      <c r="R35" s="12" t="n"/>
-      <c r="S35" s="12" t="n"/>
-      <c r="T35" s="13" t="n"/>
-      <c r="U35" s="13" t="n"/>
-      <c r="V35" s="13" t="n"/>
-      <c r="W35" s="13" t="n"/>
-      <c r="X35" s="13" t="n"/>
-      <c r="Y35" s="13" t="n"/>
-      <c r="Z35" s="13" t="n"/>
-      <c r="AA35" s="13" t="n"/>
-      <c r="AB35" s="14" t="n"/>
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>S242</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="21" t="n"/>
+      <c r="H35" s="21" t="n"/>
+      <c r="I35" s="21" t="n"/>
+      <c r="J35" s="21" t="n"/>
+      <c r="K35" s="21" t="n"/>
+      <c r="L35" s="22" t="n"/>
+      <c r="M35" s="22" t="n"/>
+      <c r="N35" s="22" t="n"/>
+      <c r="O35" s="22" t="n"/>
+      <c r="P35" s="22" t="n"/>
+      <c r="Q35" s="22" t="n"/>
+      <c r="R35" s="22" t="n"/>
+      <c r="S35" s="22" t="n"/>
+      <c r="T35" s="23" t="n"/>
+      <c r="U35" s="23" t="n"/>
+      <c r="V35" s="23" t="n"/>
+      <c r="W35" s="23" t="n"/>
+      <c r="X35" s="23" t="n"/>
+      <c r="Y35" s="23" t="n"/>
+      <c r="Z35" s="23" t="n"/>
+      <c r="AA35" s="23" t="n"/>
+      <c r="AB35" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="n"/>
-      <c r="I36" s="11" t="n"/>
-      <c r="J36" s="11" t="n"/>
-      <c r="K36" s="11" t="n"/>
-      <c r="L36" s="12" t="n"/>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="12" t="n"/>
-      <c r="O36" s="12" t="n"/>
-      <c r="P36" s="12" t="n"/>
-      <c r="Q36" s="12" t="n"/>
-      <c r="R36" s="12" t="n"/>
-      <c r="S36" s="12" t="n"/>
-      <c r="T36" s="13" t="n"/>
-      <c r="U36" s="13" t="n"/>
-      <c r="V36" s="13" t="n"/>
-      <c r="W36" s="13" t="n"/>
-      <c r="X36" s="13" t="n"/>
-      <c r="Y36" s="13" t="n"/>
-      <c r="Z36" s="13" t="n"/>
-      <c r="AA36" s="13" t="n"/>
-      <c r="AB36" s="14" t="n"/>
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>S241</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="21" t="n"/>
+      <c r="H36" s="21" t="n"/>
+      <c r="I36" s="21" t="n"/>
+      <c r="J36" s="21" t="n"/>
+      <c r="K36" s="21" t="n"/>
+      <c r="L36" s="22" t="n"/>
+      <c r="M36" s="22" t="n"/>
+      <c r="N36" s="22" t="n"/>
+      <c r="O36" s="22" t="n"/>
+      <c r="P36" s="22" t="n"/>
+      <c r="Q36" s="22" t="n"/>
+      <c r="R36" s="22" t="n"/>
+      <c r="S36" s="22" t="n"/>
+      <c r="T36" s="23" t="n"/>
+      <c r="U36" s="23" t="n"/>
+      <c r="V36" s="23" t="n"/>
+      <c r="W36" s="23" t="n"/>
+      <c r="X36" s="23" t="n"/>
+      <c r="Y36" s="23" t="n"/>
+      <c r="Z36" s="23" t="n"/>
+      <c r="AA36" s="23" t="n"/>
+      <c r="AB36" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="11" t="n"/>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="12" t="n"/>
-      <c r="M37" s="12" t="n"/>
-      <c r="N37" s="12" t="n"/>
-      <c r="O37" s="12" t="n"/>
-      <c r="P37" s="12" t="n"/>
-      <c r="Q37" s="12" t="n"/>
-      <c r="R37" s="12" t="n"/>
-      <c r="S37" s="12" t="n"/>
-      <c r="T37" s="13" t="n"/>
-      <c r="U37" s="13" t="n"/>
-      <c r="V37" s="13" t="n"/>
-      <c r="W37" s="13" t="n"/>
-      <c r="X37" s="13" t="n"/>
-      <c r="Y37" s="13" t="n"/>
-      <c r="Z37" s="13" t="n"/>
-      <c r="AA37" s="13" t="n"/>
-      <c r="AB37" s="14" t="n"/>
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>S240</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="21" t="n"/>
+      <c r="H37" s="21" t="n"/>
+      <c r="I37" s="21" t="n"/>
+      <c r="J37" s="21" t="n"/>
+      <c r="K37" s="21" t="n"/>
+      <c r="L37" s="22" t="n"/>
+      <c r="M37" s="22" t="n"/>
+      <c r="N37" s="22" t="n"/>
+      <c r="O37" s="22" t="n"/>
+      <c r="P37" s="22" t="n"/>
+      <c r="Q37" s="22" t="n"/>
+      <c r="R37" s="22" t="n"/>
+      <c r="S37" s="22" t="n"/>
+      <c r="T37" s="23" t="n"/>
+      <c r="U37" s="23" t="n"/>
+      <c r="V37" s="23" t="n"/>
+      <c r="W37" s="23" t="n"/>
+      <c r="X37" s="23" t="n"/>
+      <c r="Y37" s="23" t="n"/>
+      <c r="Z37" s="23" t="n"/>
+      <c r="AA37" s="23" t="n"/>
+      <c r="AB37" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="11" t="n"/>
-      <c r="I38" s="11" t="n"/>
-      <c r="J38" s="11" t="n"/>
-      <c r="K38" s="11" t="n"/>
-      <c r="L38" s="12" t="n"/>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="12" t="n"/>
-      <c r="O38" s="12" t="n"/>
-      <c r="P38" s="12" t="n"/>
-      <c r="Q38" s="12" t="n"/>
-      <c r="R38" s="12" t="n"/>
-      <c r="S38" s="12" t="n"/>
-      <c r="T38" s="13" t="n"/>
-      <c r="U38" s="13" t="n"/>
-      <c r="V38" s="13" t="n"/>
-      <c r="W38" s="13" t="n"/>
-      <c r="X38" s="13" t="n"/>
-      <c r="Y38" s="13" t="n"/>
-      <c r="Z38" s="13" t="n"/>
-      <c r="AA38" s="13" t="n"/>
-      <c r="AB38" s="14" t="n"/>
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>S239</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="21" t="n"/>
+      <c r="H38" s="21" t="n"/>
+      <c r="I38" s="21" t="n"/>
+      <c r="J38" s="21" t="n"/>
+      <c r="K38" s="21" t="n"/>
+      <c r="L38" s="22" t="n"/>
+      <c r="M38" s="22" t="n"/>
+      <c r="N38" s="22" t="n"/>
+      <c r="O38" s="22" t="n"/>
+      <c r="P38" s="22" t="n"/>
+      <c r="Q38" s="22" t="n"/>
+      <c r="R38" s="22" t="n"/>
+      <c r="S38" s="22" t="n"/>
+      <c r="T38" s="23" t="n"/>
+      <c r="U38" s="23" t="n"/>
+      <c r="V38" s="23" t="n"/>
+      <c r="W38" s="23" t="n"/>
+      <c r="X38" s="23" t="n"/>
+      <c r="Y38" s="23" t="n"/>
+      <c r="Z38" s="23" t="n"/>
+      <c r="AA38" s="23" t="n"/>
+      <c r="AB38" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="11" t="n"/>
-      <c r="I39" s="11" t="n"/>
-      <c r="J39" s="11" t="n"/>
-      <c r="K39" s="11" t="n"/>
-      <c r="L39" s="12" t="n"/>
-      <c r="M39" s="12" t="n"/>
-      <c r="N39" s="12" t="n"/>
-      <c r="O39" s="12" t="n"/>
-      <c r="P39" s="12" t="n"/>
-      <c r="Q39" s="12" t="n"/>
-      <c r="R39" s="12" t="n"/>
-      <c r="S39" s="12" t="n"/>
-      <c r="T39" s="13" t="n"/>
-      <c r="U39" s="13" t="n"/>
-      <c r="V39" s="13" t="n"/>
-      <c r="W39" s="13" t="n"/>
-      <c r="X39" s="13" t="n"/>
-      <c r="Y39" s="13" t="n"/>
-      <c r="Z39" s="13" t="n"/>
-      <c r="AA39" s="13" t="n"/>
-      <c r="AB39" s="14" t="n"/>
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>S238</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="21" t="n"/>
+      <c r="H39" s="21" t="n"/>
+      <c r="I39" s="21" t="n"/>
+      <c r="J39" s="21" t="n"/>
+      <c r="K39" s="21" t="n"/>
+      <c r="L39" s="22" t="n"/>
+      <c r="M39" s="22" t="n"/>
+      <c r="N39" s="22" t="n"/>
+      <c r="O39" s="22" t="n"/>
+      <c r="P39" s="22" t="n"/>
+      <c r="Q39" s="22" t="n"/>
+      <c r="R39" s="22" t="n"/>
+      <c r="S39" s="22" t="n"/>
+      <c r="T39" s="23" t="n"/>
+      <c r="U39" s="23" t="n"/>
+      <c r="V39" s="23" t="n"/>
+      <c r="W39" s="23" t="n"/>
+      <c r="X39" s="23" t="n"/>
+      <c r="Y39" s="23" t="n"/>
+      <c r="Z39" s="23" t="n"/>
+      <c r="AA39" s="23" t="n"/>
+      <c r="AB39" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="11" t="n"/>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="11" t="n"/>
-      <c r="K40" s="11" t="n"/>
-      <c r="L40" s="12" t="n"/>
-      <c r="M40" s="12" t="n"/>
-      <c r="N40" s="12" t="n"/>
-      <c r="O40" s="12" t="n"/>
-      <c r="P40" s="12" t="n"/>
-      <c r="Q40" s="12" t="n"/>
-      <c r="R40" s="12" t="n"/>
-      <c r="S40" s="12" t="n"/>
-      <c r="T40" s="13" t="n"/>
-      <c r="U40" s="13" t="n"/>
-      <c r="V40" s="13" t="n"/>
-      <c r="W40" s="13" t="n"/>
-      <c r="X40" s="13" t="n"/>
-      <c r="Y40" s="13" t="n"/>
-      <c r="Z40" s="13" t="n"/>
-      <c r="AA40" s="13" t="n"/>
-      <c r="AB40" s="14" t="n"/>
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>S237</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="21" t="n"/>
+      <c r="I40" s="21" t="n"/>
+      <c r="J40" s="21" t="n"/>
+      <c r="K40" s="21" t="n"/>
+      <c r="L40" s="22" t="n"/>
+      <c r="M40" s="22" t="n"/>
+      <c r="N40" s="22" t="n"/>
+      <c r="O40" s="22" t="n"/>
+      <c r="P40" s="22" t="n"/>
+      <c r="Q40" s="22" t="n"/>
+      <c r="R40" s="22" t="n"/>
+      <c r="S40" s="22" t="n"/>
+      <c r="T40" s="23" t="n"/>
+      <c r="U40" s="23" t="n"/>
+      <c r="V40" s="23" t="n"/>
+      <c r="W40" s="23" t="n"/>
+      <c r="X40" s="23" t="n"/>
+      <c r="Y40" s="23" t="n"/>
+      <c r="Z40" s="23" t="n"/>
+      <c r="AA40" s="23" t="n"/>
+      <c r="AB40" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="n"/>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-      <c r="I41" s="11" t="n"/>
-      <c r="J41" s="11" t="n"/>
-      <c r="K41" s="11" t="n"/>
-      <c r="L41" s="12" t="n"/>
-      <c r="M41" s="12" t="n"/>
-      <c r="N41" s="12" t="n"/>
-      <c r="O41" s="12" t="n"/>
-      <c r="P41" s="12" t="n"/>
-      <c r="Q41" s="12" t="n"/>
-      <c r="R41" s="12" t="n"/>
-      <c r="S41" s="12" t="n"/>
-      <c r="T41" s="13" t="n"/>
-      <c r="U41" s="13" t="n"/>
-      <c r="V41" s="13" t="n"/>
-      <c r="W41" s="13" t="n"/>
-      <c r="X41" s="13" t="n"/>
-      <c r="Y41" s="13" t="n"/>
-      <c r="Z41" s="13" t="n"/>
-      <c r="AA41" s="13" t="n"/>
-      <c r="AB41" s="14" t="n"/>
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>S236</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="21" t="n"/>
+      <c r="I41" s="21" t="n"/>
+      <c r="J41" s="21" t="n"/>
+      <c r="K41" s="21" t="n"/>
+      <c r="L41" s="22" t="n"/>
+      <c r="M41" s="22" t="n"/>
+      <c r="N41" s="22" t="n"/>
+      <c r="O41" s="22" t="n"/>
+      <c r="P41" s="22" t="n"/>
+      <c r="Q41" s="22" t="n"/>
+      <c r="R41" s="22" t="n"/>
+      <c r="S41" s="22" t="n"/>
+      <c r="T41" s="23" t="n"/>
+      <c r="U41" s="23" t="n"/>
+      <c r="V41" s="23" t="n"/>
+      <c r="W41" s="23" t="n"/>
+      <c r="X41" s="23" t="n"/>
+      <c r="Y41" s="23" t="n"/>
+      <c r="Z41" s="23" t="n"/>
+      <c r="AA41" s="23" t="n"/>
+      <c r="AB41" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n"/>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
-      <c r="H42" s="11" t="n"/>
-      <c r="I42" s="11" t="n"/>
-      <c r="J42" s="11" t="n"/>
-      <c r="K42" s="11" t="n"/>
-      <c r="L42" s="12" t="n"/>
-      <c r="M42" s="12" t="n"/>
-      <c r="N42" s="12" t="n"/>
-      <c r="O42" s="12" t="n"/>
-      <c r="P42" s="12" t="n"/>
-      <c r="Q42" s="12" t="n"/>
-      <c r="R42" s="12" t="n"/>
-      <c r="S42" s="12" t="n"/>
-      <c r="T42" s="13" t="n"/>
-      <c r="U42" s="13" t="n"/>
-      <c r="V42" s="13" t="n"/>
-      <c r="W42" s="13" t="n"/>
-      <c r="X42" s="13" t="n"/>
-      <c r="Y42" s="13" t="n"/>
-      <c r="Z42" s="13" t="n"/>
-      <c r="AA42" s="13" t="n"/>
-      <c r="AB42" s="14" t="n"/>
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>S235</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="21" t="n"/>
+      <c r="I42" s="21" t="n"/>
+      <c r="J42" s="21" t="n"/>
+      <c r="K42" s="21" t="n"/>
+      <c r="L42" s="22" t="n"/>
+      <c r="M42" s="22" t="n"/>
+      <c r="N42" s="22" t="n"/>
+      <c r="O42" s="22" t="n"/>
+      <c r="P42" s="22" t="n"/>
+      <c r="Q42" s="22" t="n"/>
+      <c r="R42" s="22" t="n"/>
+      <c r="S42" s="22" t="n"/>
+      <c r="T42" s="23" t="n"/>
+      <c r="U42" s="23" t="n"/>
+      <c r="V42" s="23" t="n"/>
+      <c r="W42" s="23" t="n"/>
+      <c r="X42" s="23" t="n"/>
+      <c r="Y42" s="23" t="n"/>
+      <c r="Z42" s="23" t="n"/>
+      <c r="AA42" s="23" t="n"/>
+      <c r="AB42" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="11" t="n"/>
-      <c r="I43" s="11" t="n"/>
-      <c r="J43" s="11" t="n"/>
-      <c r="K43" s="11" t="n"/>
-      <c r="L43" s="12" t="n"/>
-      <c r="M43" s="12" t="n"/>
-      <c r="N43" s="12" t="n"/>
-      <c r="O43" s="12" t="n"/>
-      <c r="P43" s="12" t="n"/>
-      <c r="Q43" s="12" t="n"/>
-      <c r="R43" s="12" t="n"/>
-      <c r="S43" s="12" t="n"/>
-      <c r="T43" s="13" t="n"/>
-      <c r="U43" s="13" t="n"/>
-      <c r="V43" s="13" t="n"/>
-      <c r="W43" s="13" t="n"/>
-      <c r="X43" s="13" t="n"/>
-      <c r="Y43" s="13" t="n"/>
-      <c r="Z43" s="13" t="n"/>
-      <c r="AA43" s="13" t="n"/>
-      <c r="AB43" s="14" t="n"/>
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>S234</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="21" t="n"/>
+      <c r="I43" s="21" t="n"/>
+      <c r="J43" s="21" t="n"/>
+      <c r="K43" s="21" t="n"/>
+      <c r="L43" s="22" t="n"/>
+      <c r="M43" s="22" t="n"/>
+      <c r="N43" s="22" t="n"/>
+      <c r="O43" s="22" t="n"/>
+      <c r="P43" s="22" t="n"/>
+      <c r="Q43" s="22" t="n"/>
+      <c r="R43" s="22" t="n"/>
+      <c r="S43" s="22" t="n"/>
+      <c r="T43" s="23" t="n"/>
+      <c r="U43" s="23" t="n"/>
+      <c r="V43" s="23" t="n"/>
+      <c r="W43" s="23" t="n"/>
+      <c r="X43" s="23" t="n"/>
+      <c r="Y43" s="23" t="n"/>
+      <c r="Z43" s="23" t="n"/>
+      <c r="AA43" s="23" t="n"/>
+      <c r="AB43" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="11" t="n"/>
-      <c r="I44" s="11" t="n"/>
-      <c r="J44" s="11" t="n"/>
-      <c r="K44" s="11" t="n"/>
-      <c r="L44" s="12" t="n"/>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="12" t="n"/>
-      <c r="O44" s="12" t="n"/>
-      <c r="P44" s="12" t="n"/>
-      <c r="Q44" s="12" t="n"/>
-      <c r="R44" s="12" t="n"/>
-      <c r="S44" s="12" t="n"/>
-      <c r="T44" s="13" t="n"/>
-      <c r="U44" s="13" t="n"/>
-      <c r="V44" s="13" t="n"/>
-      <c r="W44" s="13" t="n"/>
-      <c r="X44" s="13" t="n"/>
-      <c r="Y44" s="13" t="n"/>
-      <c r="Z44" s="13" t="n"/>
-      <c r="AA44" s="13" t="n"/>
-      <c r="AB44" s="14" t="n"/>
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>S233</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="n"/>
+      <c r="H44" s="21" t="n"/>
+      <c r="I44" s="21" t="n"/>
+      <c r="J44" s="21" t="n"/>
+      <c r="K44" s="21" t="n"/>
+      <c r="L44" s="22" t="n"/>
+      <c r="M44" s="22" t="n"/>
+      <c r="N44" s="22" t="n"/>
+      <c r="O44" s="22" t="n"/>
+      <c r="P44" s="22" t="n"/>
+      <c r="Q44" s="22" t="n"/>
+      <c r="R44" s="22" t="n"/>
+      <c r="S44" s="22" t="n"/>
+      <c r="T44" s="23" t="n"/>
+      <c r="U44" s="23" t="n"/>
+      <c r="V44" s="23" t="n"/>
+      <c r="W44" s="23" t="n"/>
+      <c r="X44" s="23" t="n"/>
+      <c r="Y44" s="23" t="n"/>
+      <c r="Z44" s="23" t="n"/>
+      <c r="AA44" s="23" t="n"/>
+      <c r="AB44" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="n"/>
-      <c r="I45" s="11" t="n"/>
-      <c r="J45" s="11" t="n"/>
-      <c r="K45" s="11" t="n"/>
-      <c r="L45" s="12" t="n"/>
-      <c r="M45" s="12" t="n"/>
-      <c r="N45" s="12" t="n"/>
-      <c r="O45" s="12" t="n"/>
-      <c r="P45" s="12" t="n"/>
-      <c r="Q45" s="12" t="n"/>
-      <c r="R45" s="12" t="n"/>
-      <c r="S45" s="12" t="n"/>
-      <c r="T45" s="13" t="n"/>
-      <c r="U45" s="13" t="n"/>
-      <c r="V45" s="13" t="n"/>
-      <c r="W45" s="13" t="n"/>
-      <c r="X45" s="13" t="n"/>
-      <c r="Y45" s="13" t="n"/>
-      <c r="Z45" s="13" t="n"/>
-      <c r="AA45" s="13" t="n"/>
-      <c r="AB45" s="14" t="n"/>
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>S232</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="20" t="n"/>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="21" t="n"/>
+      <c r="I45" s="21" t="n"/>
+      <c r="J45" s="21" t="n"/>
+      <c r="K45" s="21" t="n"/>
+      <c r="L45" s="22" t="n"/>
+      <c r="M45" s="22" t="n"/>
+      <c r="N45" s="22" t="n"/>
+      <c r="O45" s="22" t="n"/>
+      <c r="P45" s="22" t="n"/>
+      <c r="Q45" s="22" t="n"/>
+      <c r="R45" s="22" t="n"/>
+      <c r="S45" s="22" t="n"/>
+      <c r="T45" s="23" t="n"/>
+      <c r="U45" s="23" t="n"/>
+      <c r="V45" s="23" t="n"/>
+      <c r="W45" s="23" t="n"/>
+      <c r="X45" s="23" t="n"/>
+      <c r="Y45" s="23" t="n"/>
+      <c r="Z45" s="23" t="n"/>
+      <c r="AA45" s="23" t="n"/>
+      <c r="AB45" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>S231</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="21" t="n"/>
+      <c r="I46" s="21" t="n"/>
+      <c r="J46" s="21" t="n"/>
+      <c r="K46" s="21" t="n"/>
+      <c r="L46" s="22" t="n"/>
+      <c r="M46" s="22" t="n"/>
+      <c r="N46" s="22" t="n"/>
+      <c r="O46" s="22" t="n"/>
+      <c r="P46" s="22" t="n"/>
+      <c r="Q46" s="22" t="n"/>
+      <c r="R46" s="22" t="n"/>
+      <c r="S46" s="22" t="n"/>
+      <c r="T46" s="23" t="n"/>
+      <c r="U46" s="23" t="n"/>
+      <c r="V46" s="23" t="n"/>
+      <c r="W46" s="23" t="n"/>
+      <c r="X46" s="23" t="n"/>
+      <c r="Y46" s="23" t="n"/>
+      <c r="Z46" s="23" t="n"/>
+      <c r="AA46" s="23" t="n"/>
+      <c r="AB46" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>S230</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20" t="n"/>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="21" t="n"/>
+      <c r="I47" s="21" t="n"/>
+      <c r="J47" s="21" t="n"/>
+      <c r="K47" s="21" t="n"/>
+      <c r="L47" s="22" t="n"/>
+      <c r="M47" s="22" t="n"/>
+      <c r="N47" s="22" t="n"/>
+      <c r="O47" s="22" t="n"/>
+      <c r="P47" s="22" t="n"/>
+      <c r="Q47" s="22" t="n"/>
+      <c r="R47" s="22" t="n"/>
+      <c r="S47" s="22" t="n"/>
+      <c r="T47" s="23" t="n"/>
+      <c r="U47" s="23" t="n"/>
+      <c r="V47" s="23" t="n"/>
+      <c r="W47" s="23" t="n"/>
+      <c r="X47" s="23" t="n"/>
+      <c r="Y47" s="23" t="n"/>
+      <c r="Z47" s="23" t="n"/>
+      <c r="AA47" s="23" t="n"/>
+      <c r="AB47" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>S229</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="n"/>
+      <c r="D48" s="20" t="n"/>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="21" t="n"/>
+      <c r="I48" s="21" t="n"/>
+      <c r="J48" s="21" t="n"/>
+      <c r="K48" s="21" t="n"/>
+      <c r="L48" s="22" t="n"/>
+      <c r="M48" s="22" t="n"/>
+      <c r="N48" s="22" t="n"/>
+      <c r="O48" s="22" t="n"/>
+      <c r="P48" s="22" t="n"/>
+      <c r="Q48" s="22" t="n"/>
+      <c r="R48" s="22" t="n"/>
+      <c r="S48" s="22" t="n"/>
+      <c r="T48" s="23" t="n"/>
+      <c r="U48" s="23" t="n"/>
+      <c r="V48" s="23" t="n"/>
+      <c r="W48" s="23" t="n"/>
+      <c r="X48" s="23" t="n"/>
+      <c r="Y48" s="23" t="n"/>
+      <c r="Z48" s="23" t="n"/>
+      <c r="AA48" s="23" t="n"/>
+      <c r="AB48" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>S228</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="21" t="n"/>
+      <c r="I49" s="21" t="n"/>
+      <c r="J49" s="21" t="n"/>
+      <c r="K49" s="21" t="n"/>
+      <c r="L49" s="22" t="n"/>
+      <c r="M49" s="22" t="n"/>
+      <c r="N49" s="22" t="n"/>
+      <c r="O49" s="22" t="n"/>
+      <c r="P49" s="22" t="n"/>
+      <c r="Q49" s="22" t="n"/>
+      <c r="R49" s="22" t="n"/>
+      <c r="S49" s="22" t="n"/>
+      <c r="T49" s="23" t="n"/>
+      <c r="U49" s="23" t="n"/>
+      <c r="V49" s="23" t="n"/>
+      <c r="W49" s="23" t="n"/>
+      <c r="X49" s="23" t="n"/>
+      <c r="Y49" s="23" t="n"/>
+      <c r="Z49" s="23" t="n"/>
+      <c r="AA49" s="23" t="n"/>
+      <c r="AB49" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>S227</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="n"/>
+      <c r="D50" s="20" t="n"/>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="n"/>
+      <c r="H50" s="21" t="n"/>
+      <c r="I50" s="21" t="n"/>
+      <c r="J50" s="21" t="n"/>
+      <c r="K50" s="21" t="n"/>
+      <c r="L50" s="22" t="n"/>
+      <c r="M50" s="22" t="n"/>
+      <c r="N50" s="22" t="n"/>
+      <c r="O50" s="22" t="n"/>
+      <c r="P50" s="22" t="n"/>
+      <c r="Q50" s="22" t="n"/>
+      <c r="R50" s="22" t="n"/>
+      <c r="S50" s="22" t="n"/>
+      <c r="T50" s="23" t="n"/>
+      <c r="U50" s="23" t="n"/>
+      <c r="V50" s="23" t="n"/>
+      <c r="W50" s="23" t="n"/>
+      <c r="X50" s="23" t="n"/>
+      <c r="Y50" s="23" t="n"/>
+      <c r="Z50" s="23" t="n"/>
+      <c r="AA50" s="23" t="n"/>
+      <c r="AB50" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>S226</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="21" t="n"/>
+      <c r="I51" s="21" t="n"/>
+      <c r="J51" s="21" t="n"/>
+      <c r="K51" s="21" t="n"/>
+      <c r="L51" s="22" t="n"/>
+      <c r="M51" s="22" t="n"/>
+      <c r="N51" s="22" t="n"/>
+      <c r="O51" s="22" t="n"/>
+      <c r="P51" s="22" t="n"/>
+      <c r="Q51" s="22" t="n"/>
+      <c r="R51" s="22" t="n"/>
+      <c r="S51" s="22" t="n"/>
+      <c r="T51" s="23" t="n"/>
+      <c r="U51" s="23" t="n"/>
+      <c r="V51" s="23" t="n"/>
+      <c r="W51" s="23" t="n"/>
+      <c r="X51" s="23" t="n"/>
+      <c r="Y51" s="23" t="n"/>
+      <c r="Z51" s="23" t="n"/>
+      <c r="AA51" s="23" t="n"/>
+      <c r="AB51" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>S225</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="21" t="n"/>
+      <c r="I52" s="21" t="n"/>
+      <c r="J52" s="21" t="n"/>
+      <c r="K52" s="21" t="n"/>
+      <c r="L52" s="22" t="n"/>
+      <c r="M52" s="22" t="n"/>
+      <c r="N52" s="22" t="n"/>
+      <c r="O52" s="22" t="n"/>
+      <c r="P52" s="22" t="n"/>
+      <c r="Q52" s="22" t="n"/>
+      <c r="R52" s="22" t="n"/>
+      <c r="S52" s="22" t="n"/>
+      <c r="T52" s="23" t="n"/>
+      <c r="U52" s="23" t="n"/>
+      <c r="V52" s="23" t="n"/>
+      <c r="W52" s="23" t="n"/>
+      <c r="X52" s="23" t="n"/>
+      <c r="Y52" s="23" t="n"/>
+      <c r="Z52" s="23" t="n"/>
+      <c r="AA52" s="23" t="n"/>
+      <c r="AB52" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>S224</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="20" t="n"/>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="21" t="n"/>
+      <c r="I53" s="21" t="n"/>
+      <c r="J53" s="21" t="n"/>
+      <c r="K53" s="21" t="n"/>
+      <c r="L53" s="22" t="n"/>
+      <c r="M53" s="22" t="n"/>
+      <c r="N53" s="22" t="n"/>
+      <c r="O53" s="22" t="n"/>
+      <c r="P53" s="22" t="n"/>
+      <c r="Q53" s="22" t="n"/>
+      <c r="R53" s="22" t="n"/>
+      <c r="S53" s="22" t="n"/>
+      <c r="T53" s="23" t="n"/>
+      <c r="U53" s="23" t="n"/>
+      <c r="V53" s="23" t="n"/>
+      <c r="W53" s="23" t="n"/>
+      <c r="X53" s="23" t="n"/>
+      <c r="Y53" s="23" t="n"/>
+      <c r="Z53" s="23" t="n"/>
+      <c r="AA53" s="23" t="n"/>
+      <c r="AB53" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>S222</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="n"/>
+      <c r="D54" s="20" t="n"/>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="21" t="n"/>
+      <c r="I54" s="21" t="n"/>
+      <c r="J54" s="21" t="n"/>
+      <c r="K54" s="21" t="n"/>
+      <c r="L54" s="22" t="n"/>
+      <c r="M54" s="22" t="n"/>
+      <c r="N54" s="22" t="n"/>
+      <c r="O54" s="22" t="n"/>
+      <c r="P54" s="22" t="n"/>
+      <c r="Q54" s="22" t="n"/>
+      <c r="R54" s="22" t="n"/>
+      <c r="S54" s="22" t="n"/>
+      <c r="T54" s="23" t="n"/>
+      <c r="U54" s="23" t="n"/>
+      <c r="V54" s="23" t="n"/>
+      <c r="W54" s="23" t="n"/>
+      <c r="X54" s="23" t="n"/>
+      <c r="Y54" s="23" t="n"/>
+      <c r="Z54" s="23" t="n"/>
+      <c r="AA54" s="23" t="n"/>
+      <c r="AB54" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>S221</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="21" t="n"/>
+      <c r="I55" s="21" t="n"/>
+      <c r="J55" s="21" t="n"/>
+      <c r="K55" s="21" t="n"/>
+      <c r="L55" s="22" t="n"/>
+      <c r="M55" s="22" t="n"/>
+      <c r="N55" s="22" t="n"/>
+      <c r="O55" s="22" t="n"/>
+      <c r="P55" s="22" t="n"/>
+      <c r="Q55" s="22" t="n"/>
+      <c r="R55" s="22" t="n"/>
+      <c r="S55" s="22" t="n"/>
+      <c r="T55" s="23" t="n"/>
+      <c r="U55" s="23" t="n"/>
+      <c r="V55" s="23" t="n"/>
+      <c r="W55" s="23" t="n"/>
+      <c r="X55" s="23" t="n"/>
+      <c r="Y55" s="23" t="n"/>
+      <c r="Z55" s="23" t="n"/>
+      <c r="AA55" s="23" t="n"/>
+      <c r="AB55" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>S220</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="n"/>
+      <c r="D56" s="20" t="n"/>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="21" t="n"/>
+      <c r="I56" s="21" t="n"/>
+      <c r="J56" s="21" t="n"/>
+      <c r="K56" s="21" t="n"/>
+      <c r="L56" s="22" t="n"/>
+      <c r="M56" s="22" t="n"/>
+      <c r="N56" s="22" t="n"/>
+      <c r="O56" s="22" t="n"/>
+      <c r="P56" s="22" t="n"/>
+      <c r="Q56" s="22" t="n"/>
+      <c r="R56" s="22" t="n"/>
+      <c r="S56" s="22" t="n"/>
+      <c r="T56" s="23" t="n"/>
+      <c r="U56" s="23" t="n"/>
+      <c r="V56" s="23" t="n"/>
+      <c r="W56" s="23" t="n"/>
+      <c r="X56" s="23" t="n"/>
+      <c r="Y56" s="23" t="n"/>
+      <c r="Z56" s="23" t="n"/>
+      <c r="AA56" s="23" t="n"/>
+      <c r="AB56" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>S219</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="21" t="n"/>
+      <c r="I57" s="21" t="n"/>
+      <c r="J57" s="21" t="n"/>
+      <c r="K57" s="21" t="n"/>
+      <c r="L57" s="22" t="n"/>
+      <c r="M57" s="22" t="n"/>
+      <c r="N57" s="22" t="n"/>
+      <c r="O57" s="22" t="n"/>
+      <c r="P57" s="22" t="n"/>
+      <c r="Q57" s="22" t="n"/>
+      <c r="R57" s="22" t="n"/>
+      <c r="S57" s="22" t="n"/>
+      <c r="T57" s="23" t="n"/>
+      <c r="U57" s="23" t="n"/>
+      <c r="V57" s="23" t="n"/>
+      <c r="W57" s="23" t="n"/>
+      <c r="X57" s="23" t="n"/>
+      <c r="Y57" s="23" t="n"/>
+      <c r="Z57" s="23" t="n"/>
+      <c r="AA57" s="23" t="n"/>
+      <c r="AB57" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>S218</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="20" t="n"/>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="21" t="n"/>
+      <c r="I58" s="21" t="n"/>
+      <c r="J58" s="21" t="n"/>
+      <c r="K58" s="21" t="n"/>
+      <c r="L58" s="22" t="n"/>
+      <c r="M58" s="22" t="n"/>
+      <c r="N58" s="22" t="n"/>
+      <c r="O58" s="22" t="n"/>
+      <c r="P58" s="22" t="n"/>
+      <c r="Q58" s="22" t="n"/>
+      <c r="R58" s="22" t="n"/>
+      <c r="S58" s="22" t="n"/>
+      <c r="T58" s="23" t="n"/>
+      <c r="U58" s="23" t="n"/>
+      <c r="V58" s="23" t="n"/>
+      <c r="W58" s="23" t="n"/>
+      <c r="X58" s="23" t="n"/>
+      <c r="Y58" s="23" t="n"/>
+      <c r="Z58" s="23" t="n"/>
+      <c r="AA58" s="23" t="n"/>
+      <c r="AB58" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>S217</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="n"/>
+      <c r="D59" s="20" t="n"/>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="21" t="n"/>
+      <c r="I59" s="21" t="n"/>
+      <c r="J59" s="21" t="n"/>
+      <c r="K59" s="21" t="n"/>
+      <c r="L59" s="22" t="n"/>
+      <c r="M59" s="22" t="n"/>
+      <c r="N59" s="22" t="n"/>
+      <c r="O59" s="22" t="n"/>
+      <c r="P59" s="22" t="n"/>
+      <c r="Q59" s="22" t="n"/>
+      <c r="R59" s="22" t="n"/>
+      <c r="S59" s="22" t="n"/>
+      <c r="T59" s="23" t="n"/>
+      <c r="U59" s="23" t="n"/>
+      <c r="V59" s="23" t="n"/>
+      <c r="W59" s="23" t="n"/>
+      <c r="X59" s="23" t="n"/>
+      <c r="Y59" s="23" t="n"/>
+      <c r="Z59" s="23" t="n"/>
+      <c r="AA59" s="23" t="n"/>
+      <c r="AB59" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>S215</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="n"/>
+      <c r="D60" s="20" t="n"/>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="21" t="n"/>
+      <c r="I60" s="21" t="n"/>
+      <c r="J60" s="21" t="n"/>
+      <c r="K60" s="21" t="n"/>
+      <c r="L60" s="22" t="n"/>
+      <c r="M60" s="22" t="n"/>
+      <c r="N60" s="22" t="n"/>
+      <c r="O60" s="22" t="n"/>
+      <c r="P60" s="22" t="n"/>
+      <c r="Q60" s="22" t="n"/>
+      <c r="R60" s="22" t="n"/>
+      <c r="S60" s="22" t="n"/>
+      <c r="T60" s="23" t="n"/>
+      <c r="U60" s="23" t="n"/>
+      <c r="V60" s="23" t="n"/>
+      <c r="W60" s="23" t="n"/>
+      <c r="X60" s="23" t="n"/>
+      <c r="Y60" s="23" t="n"/>
+      <c r="Z60" s="23" t="n"/>
+      <c r="AA60" s="23" t="n"/>
+      <c r="AB60" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>S214</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="21" t="n"/>
+      <c r="H61" s="21" t="n"/>
+      <c r="I61" s="21" t="n"/>
+      <c r="J61" s="21" t="n"/>
+      <c r="K61" s="21" t="n"/>
+      <c r="L61" s="22" t="n"/>
+      <c r="M61" s="22" t="n"/>
+      <c r="N61" s="22" t="n"/>
+      <c r="O61" s="22" t="n"/>
+      <c r="P61" s="22" t="n"/>
+      <c r="Q61" s="22" t="n"/>
+      <c r="R61" s="22" t="n"/>
+      <c r="S61" s="22" t="n"/>
+      <c r="T61" s="23" t="n"/>
+      <c r="U61" s="23" t="n"/>
+      <c r="V61" s="23" t="n"/>
+      <c r="W61" s="23" t="n"/>
+      <c r="X61" s="23" t="n"/>
+      <c r="Y61" s="23" t="n"/>
+      <c r="Z61" s="23" t="n"/>
+      <c r="AA61" s="23" t="n"/>
+      <c r="AB61" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>S213</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="n"/>
+      <c r="D62" s="20" t="n"/>
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="21" t="n"/>
+      <c r="H62" s="21" t="n"/>
+      <c r="I62" s="21" t="n"/>
+      <c r="J62" s="21" t="n"/>
+      <c r="K62" s="21" t="n"/>
+      <c r="L62" s="22" t="n"/>
+      <c r="M62" s="22" t="n"/>
+      <c r="N62" s="22" t="n"/>
+      <c r="O62" s="22" t="n"/>
+      <c r="P62" s="22" t="n"/>
+      <c r="Q62" s="22" t="n"/>
+      <c r="R62" s="22" t="n"/>
+      <c r="S62" s="22" t="n"/>
+      <c r="T62" s="23" t="n"/>
+      <c r="U62" s="23" t="n"/>
+      <c r="V62" s="23" t="n"/>
+      <c r="W62" s="23" t="n"/>
+      <c r="X62" s="23" t="n"/>
+      <c r="Y62" s="23" t="n"/>
+      <c r="Z62" s="23" t="n"/>
+      <c r="AA62" s="23" t="n"/>
+      <c r="AB62" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>S212</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="n"/>
+      <c r="D63" s="20" t="n"/>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
+      <c r="J63" s="21" t="n"/>
+      <c r="K63" s="21" t="n"/>
+      <c r="L63" s="22" t="n"/>
+      <c r="M63" s="22" t="n"/>
+      <c r="N63" s="22" t="n"/>
+      <c r="O63" s="22" t="n"/>
+      <c r="P63" s="22" t="n"/>
+      <c r="Q63" s="22" t="n"/>
+      <c r="R63" s="22" t="n"/>
+      <c r="S63" s="22" t="n"/>
+      <c r="T63" s="23" t="n"/>
+      <c r="U63" s="23" t="n"/>
+      <c r="V63" s="23" t="n"/>
+      <c r="W63" s="23" t="n"/>
+      <c r="X63" s="23" t="n"/>
+      <c r="Y63" s="23" t="n"/>
+      <c r="Z63" s="23" t="n"/>
+      <c r="AA63" s="23" t="n"/>
+      <c r="AB63" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>S211</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="n"/>
+      <c r="D64" s="20" t="n"/>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="n"/>
+      <c r="H64" s="21" t="n"/>
+      <c r="I64" s="21" t="n"/>
+      <c r="J64" s="21" t="n"/>
+      <c r="K64" s="21" t="n"/>
+      <c r="L64" s="22" t="n"/>
+      <c r="M64" s="22" t="n"/>
+      <c r="N64" s="22" t="n"/>
+      <c r="O64" s="22" t="n"/>
+      <c r="P64" s="22" t="n"/>
+      <c r="Q64" s="22" t="n"/>
+      <c r="R64" s="22" t="n"/>
+      <c r="S64" s="22" t="n"/>
+      <c r="T64" s="23" t="n"/>
+      <c r="U64" s="23" t="n"/>
+      <c r="V64" s="23" t="n"/>
+      <c r="W64" s="23" t="n"/>
+      <c r="X64" s="23" t="n"/>
+      <c r="Y64" s="23" t="n"/>
+      <c r="Z64" s="23" t="n"/>
+      <c r="AA64" s="23" t="n"/>
+      <c r="AB64" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t>S210</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="20" t="n"/>
+      <c r="E65" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="21" t="n"/>
+      <c r="I65" s="21" t="n"/>
+      <c r="J65" s="21" t="n"/>
+      <c r="K65" s="21" t="n"/>
+      <c r="L65" s="22" t="n"/>
+      <c r="M65" s="22" t="n"/>
+      <c r="N65" s="22" t="n"/>
+      <c r="O65" s="22" t="n"/>
+      <c r="P65" s="22" t="n"/>
+      <c r="Q65" s="22" t="n"/>
+      <c r="R65" s="22" t="n"/>
+      <c r="S65" s="22" t="n"/>
+      <c r="T65" s="23" t="n"/>
+      <c r="U65" s="23" t="n"/>
+      <c r="V65" s="23" t="n"/>
+      <c r="W65" s="23" t="n"/>
+      <c r="X65" s="23" t="n"/>
+      <c r="Y65" s="23" t="n"/>
+      <c r="Z65" s="23" t="n"/>
+      <c r="AA65" s="23" t="n"/>
+      <c r="AB65" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>S209</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="n"/>
+      <c r="D66" s="20" t="n"/>
+      <c r="E66" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="21" t="n"/>
+      <c r="I66" s="21" t="n"/>
+      <c r="J66" s="21" t="n"/>
+      <c r="K66" s="21" t="n"/>
+      <c r="L66" s="22" t="n"/>
+      <c r="M66" s="22" t="n"/>
+      <c r="N66" s="22" t="n"/>
+      <c r="O66" s="22" t="n"/>
+      <c r="P66" s="22" t="n"/>
+      <c r="Q66" s="22" t="n"/>
+      <c r="R66" s="22" t="n"/>
+      <c r="S66" s="22" t="n"/>
+      <c r="T66" s="23" t="n"/>
+      <c r="U66" s="23" t="n"/>
+      <c r="V66" s="23" t="n"/>
+      <c r="W66" s="23" t="n"/>
+      <c r="X66" s="23" t="n"/>
+      <c r="Y66" s="23" t="n"/>
+      <c r="Z66" s="23" t="n"/>
+      <c r="AA66" s="23" t="n"/>
+      <c r="AB66" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>S208</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F67" s="21" t="n"/>
+      <c r="G67" s="21" t="n"/>
+      <c r="H67" s="21" t="n"/>
+      <c r="I67" s="21" t="n"/>
+      <c r="J67" s="21" t="n"/>
+      <c r="K67" s="21" t="n"/>
+      <c r="L67" s="22" t="n"/>
+      <c r="M67" s="22" t="n"/>
+      <c r="N67" s="22" t="n"/>
+      <c r="O67" s="22" t="n"/>
+      <c r="P67" s="22" t="n"/>
+      <c r="Q67" s="22" t="n"/>
+      <c r="R67" s="22" t="n"/>
+      <c r="S67" s="22" t="n"/>
+      <c r="T67" s="23" t="n"/>
+      <c r="U67" s="23" t="n"/>
+      <c r="V67" s="23" t="n"/>
+      <c r="W67" s="23" t="n"/>
+      <c r="X67" s="23" t="n"/>
+      <c r="Y67" s="23" t="n"/>
+      <c r="Z67" s="23" t="n"/>
+      <c r="AA67" s="23" t="n"/>
+      <c r="AB67" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>S207</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
+      <c r="E68" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F68" s="21" t="n"/>
+      <c r="G68" s="21" t="n"/>
+      <c r="H68" s="21" t="n"/>
+      <c r="I68" s="21" t="n"/>
+      <c r="J68" s="21" t="n"/>
+      <c r="K68" s="21" t="n"/>
+      <c r="L68" s="22" t="n"/>
+      <c r="M68" s="22" t="n"/>
+      <c r="N68" s="22" t="n"/>
+      <c r="O68" s="22" t="n"/>
+      <c r="P68" s="22" t="n"/>
+      <c r="Q68" s="22" t="n"/>
+      <c r="R68" s="22" t="n"/>
+      <c r="S68" s="22" t="n"/>
+      <c r="T68" s="23" t="n"/>
+      <c r="U68" s="23" t="n"/>
+      <c r="V68" s="23" t="n"/>
+      <c r="W68" s="23" t="n"/>
+      <c r="X68" s="23" t="n"/>
+      <c r="Y68" s="23" t="n"/>
+      <c r="Z68" s="23" t="n"/>
+      <c r="AA68" s="23" t="n"/>
+      <c r="AB68" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>S203</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="20" t="n"/>
+      <c r="E69" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F69" s="21" t="n"/>
+      <c r="G69" s="21" t="n"/>
+      <c r="H69" s="21" t="n"/>
+      <c r="I69" s="21" t="n"/>
+      <c r="J69" s="21" t="n"/>
+      <c r="K69" s="21" t="n"/>
+      <c r="L69" s="22" t="n"/>
+      <c r="M69" s="22" t="n"/>
+      <c r="N69" s="22" t="n"/>
+      <c r="O69" s="22" t="n"/>
+      <c r="P69" s="22" t="n"/>
+      <c r="Q69" s="22" t="n"/>
+      <c r="R69" s="22" t="n"/>
+      <c r="S69" s="22" t="n"/>
+      <c r="T69" s="23" t="n"/>
+      <c r="U69" s="23" t="n"/>
+      <c r="V69" s="23" t="n"/>
+      <c r="W69" s="23" t="n"/>
+      <c r="X69" s="23" t="n"/>
+      <c r="Y69" s="23" t="n"/>
+      <c r="Z69" s="23" t="n"/>
+      <c r="AA69" s="23" t="n"/>
+      <c r="AB69" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20" t="inlineStr">
+        <is>
+          <t>S202</t>
+        </is>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="n"/>
+      <c r="D70" s="20" t="n"/>
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F70" s="21" t="n"/>
+      <c r="G70" s="21" t="n"/>
+      <c r="H70" s="21" t="n"/>
+      <c r="I70" s="21" t="n"/>
+      <c r="J70" s="21" t="n"/>
+      <c r="K70" s="21" t="n"/>
+      <c r="L70" s="22" t="n"/>
+      <c r="M70" s="22" t="n"/>
+      <c r="N70" s="22" t="n"/>
+      <c r="O70" s="22" t="n"/>
+      <c r="P70" s="22" t="n"/>
+      <c r="Q70" s="22" t="n"/>
+      <c r="R70" s="22" t="n"/>
+      <c r="S70" s="22" t="n"/>
+      <c r="T70" s="23" t="n"/>
+      <c r="U70" s="23" t="n"/>
+      <c r="V70" s="23" t="n"/>
+      <c r="W70" s="23" t="n"/>
+      <c r="X70" s="23" t="n"/>
+      <c r="Y70" s="23" t="n"/>
+      <c r="Z70" s="23" t="n"/>
+      <c r="AA70" s="23" t="n"/>
+      <c r="AB70" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>S201</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+      <c r="E71" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="n"/>
+      <c r="G71" s="21" t="n"/>
+      <c r="H71" s="21" t="n"/>
+      <c r="I71" s="21" t="n"/>
+      <c r="J71" s="21" t="n"/>
+      <c r="K71" s="21" t="n"/>
+      <c r="L71" s="22" t="n"/>
+      <c r="M71" s="22" t="n"/>
+      <c r="N71" s="22" t="n"/>
+      <c r="O71" s="22" t="n"/>
+      <c r="P71" s="22" t="n"/>
+      <c r="Q71" s="22" t="n"/>
+      <c r="R71" s="22" t="n"/>
+      <c r="S71" s="22" t="n"/>
+      <c r="T71" s="23" t="n"/>
+      <c r="U71" s="23" t="n"/>
+      <c r="V71" s="23" t="n"/>
+      <c r="W71" s="23" t="n"/>
+      <c r="X71" s="23" t="n"/>
+      <c r="Y71" s="23" t="n"/>
+      <c r="Z71" s="23" t="n"/>
+      <c r="AA71" s="23" t="n"/>
+      <c r="AB71" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>S198</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="n"/>
+      <c r="D72" s="20" t="n"/>
+      <c r="E72" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="21" t="n"/>
+      <c r="I72" s="21" t="n"/>
+      <c r="J72" s="21" t="n"/>
+      <c r="K72" s="21" t="n"/>
+      <c r="L72" s="22" t="n"/>
+      <c r="M72" s="22" t="n"/>
+      <c r="N72" s="22" t="n"/>
+      <c r="O72" s="22" t="n"/>
+      <c r="P72" s="22" t="n"/>
+      <c r="Q72" s="22" t="n"/>
+      <c r="R72" s="22" t="n"/>
+      <c r="S72" s="22" t="n"/>
+      <c r="T72" s="23" t="n"/>
+      <c r="U72" s="23" t="n"/>
+      <c r="V72" s="23" t="n"/>
+      <c r="W72" s="23" t="n"/>
+      <c r="X72" s="23" t="n"/>
+      <c r="Y72" s="23" t="n"/>
+      <c r="Z72" s="23" t="n"/>
+      <c r="AA72" s="23" t="n"/>
+      <c r="AB72" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>S195</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="n"/>
+      <c r="D73" s="20" t="n"/>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F73" s="21" t="n"/>
+      <c r="G73" s="21" t="n"/>
+      <c r="H73" s="21" t="n"/>
+      <c r="I73" s="21" t="n"/>
+      <c r="J73" s="21" t="n"/>
+      <c r="K73" s="21" t="n"/>
+      <c r="L73" s="22" t="n"/>
+      <c r="M73" s="22" t="n"/>
+      <c r="N73" s="22" t="n"/>
+      <c r="O73" s="22" t="n"/>
+      <c r="P73" s="22" t="n"/>
+      <c r="Q73" s="22" t="n"/>
+      <c r="R73" s="22" t="n"/>
+      <c r="S73" s="22" t="n"/>
+      <c r="T73" s="23" t="n"/>
+      <c r="U73" s="23" t="n"/>
+      <c r="V73" s="23" t="n"/>
+      <c r="W73" s="23" t="n"/>
+      <c r="X73" s="23" t="n"/>
+      <c r="Y73" s="23" t="n"/>
+      <c r="Z73" s="23" t="n"/>
+      <c r="AA73" s="23" t="n"/>
+      <c r="AB73" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>S186</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="n"/>
+      <c r="D74" s="20" t="n"/>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F74" s="21" t="n"/>
+      <c r="G74" s="21" t="n"/>
+      <c r="H74" s="21" t="n"/>
+      <c r="I74" s="21" t="n"/>
+      <c r="J74" s="21" t="n"/>
+      <c r="K74" s="21" t="n"/>
+      <c r="L74" s="22" t="n"/>
+      <c r="M74" s="22" t="n"/>
+      <c r="N74" s="22" t="n"/>
+      <c r="O74" s="22" t="n"/>
+      <c r="P74" s="22" t="n"/>
+      <c r="Q74" s="22" t="n"/>
+      <c r="R74" s="22" t="n"/>
+      <c r="S74" s="22" t="n"/>
+      <c r="T74" s="23" t="n"/>
+      <c r="U74" s="23" t="n"/>
+      <c r="V74" s="23" t="n"/>
+      <c r="W74" s="23" t="n"/>
+      <c r="X74" s="23" t="n"/>
+      <c r="Y74" s="23" t="n"/>
+      <c r="Z74" s="23" t="n"/>
+      <c r="AA74" s="23" t="n"/>
+      <c r="AB74" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>S185</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F75" s="21" t="n"/>
+      <c r="G75" s="21" t="n"/>
+      <c r="H75" s="21" t="n"/>
+      <c r="I75" s="21" t="n"/>
+      <c r="J75" s="21" t="n"/>
+      <c r="K75" s="21" t="n"/>
+      <c r="L75" s="22" t="n"/>
+      <c r="M75" s="22" t="n"/>
+      <c r="N75" s="22" t="n"/>
+      <c r="O75" s="22" t="n"/>
+      <c r="P75" s="22" t="n"/>
+      <c r="Q75" s="22" t="n"/>
+      <c r="R75" s="22" t="n"/>
+      <c r="S75" s="22" t="n"/>
+      <c r="T75" s="23" t="n"/>
+      <c r="U75" s="23" t="n"/>
+      <c r="V75" s="23" t="n"/>
+      <c r="W75" s="23" t="n"/>
+      <c r="X75" s="23" t="n"/>
+      <c r="Y75" s="23" t="n"/>
+      <c r="Z75" s="23" t="n"/>
+      <c r="AA75" s="23" t="n"/>
+      <c r="AB75" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20" t="inlineStr">
+        <is>
+          <t>S184</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="n"/>
+      <c r="D76" s="20" t="n"/>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F76" s="21" t="n"/>
+      <c r="G76" s="21" t="n"/>
+      <c r="H76" s="21" t="n"/>
+      <c r="I76" s="21" t="n"/>
+      <c r="J76" s="21" t="n"/>
+      <c r="K76" s="21" t="n"/>
+      <c r="L76" s="22" t="n"/>
+      <c r="M76" s="22" t="n"/>
+      <c r="N76" s="22" t="n"/>
+      <c r="O76" s="22" t="n"/>
+      <c r="P76" s="22" t="n"/>
+      <c r="Q76" s="22" t="n"/>
+      <c r="R76" s="22" t="n"/>
+      <c r="S76" s="22" t="n"/>
+      <c r="T76" s="23" t="n"/>
+      <c r="U76" s="23" t="n"/>
+      <c r="V76" s="23" t="n"/>
+      <c r="W76" s="23" t="n"/>
+      <c r="X76" s="23" t="n"/>
+      <c r="Y76" s="23" t="n"/>
+      <c r="Z76" s="23" t="n"/>
+      <c r="AA76" s="23" t="n"/>
+      <c r="AB76" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="20" t="inlineStr">
+        <is>
+          <t>S183</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F77" s="21" t="n"/>
+      <c r="G77" s="21" t="n"/>
+      <c r="H77" s="21" t="n"/>
+      <c r="I77" s="21" t="n"/>
+      <c r="J77" s="21" t="n"/>
+      <c r="K77" s="21" t="n"/>
+      <c r="L77" s="22" t="n"/>
+      <c r="M77" s="22" t="n"/>
+      <c r="N77" s="22" t="n"/>
+      <c r="O77" s="22" t="n"/>
+      <c r="P77" s="22" t="n"/>
+      <c r="Q77" s="22" t="n"/>
+      <c r="R77" s="22" t="n"/>
+      <c r="S77" s="22" t="n"/>
+      <c r="T77" s="23" t="n"/>
+      <c r="U77" s="23" t="n"/>
+      <c r="V77" s="23" t="n"/>
+      <c r="W77" s="23" t="n"/>
+      <c r="X77" s="23" t="n"/>
+      <c r="Y77" s="23" t="n"/>
+      <c r="Z77" s="23" t="n"/>
+      <c r="AA77" s="23" t="n"/>
+      <c r="AB77" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>S179</t>
+        </is>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="n"/>
+      <c r="D78" s="20" t="n"/>
+      <c r="E78" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F78" s="21" t="n"/>
+      <c r="G78" s="21" t="n"/>
+      <c r="H78" s="21" t="n"/>
+      <c r="I78" s="21" t="n"/>
+      <c r="J78" s="21" t="n"/>
+      <c r="K78" s="21" t="n"/>
+      <c r="L78" s="22" t="n"/>
+      <c r="M78" s="22" t="n"/>
+      <c r="N78" s="22" t="n"/>
+      <c r="O78" s="22" t="n"/>
+      <c r="P78" s="22" t="n"/>
+      <c r="Q78" s="22" t="n"/>
+      <c r="R78" s="22" t="n"/>
+      <c r="S78" s="22" t="n"/>
+      <c r="T78" s="23" t="n"/>
+      <c r="U78" s="23" t="n"/>
+      <c r="V78" s="23" t="n"/>
+      <c r="W78" s="23" t="n"/>
+      <c r="X78" s="23" t="n"/>
+      <c r="Y78" s="23" t="n"/>
+      <c r="Z78" s="23" t="n"/>
+      <c r="AA78" s="23" t="n"/>
+      <c r="AB78" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20" t="inlineStr">
+        <is>
+          <t>S174</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="n"/>
+      <c r="D79" s="20" t="n"/>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F79" s="21" t="n"/>
+      <c r="G79" s="21" t="n"/>
+      <c r="H79" s="21" t="n"/>
+      <c r="I79" s="21" t="n"/>
+      <c r="J79" s="21" t="n"/>
+      <c r="K79" s="21" t="n"/>
+      <c r="L79" s="22" t="n"/>
+      <c r="M79" s="22" t="n"/>
+      <c r="N79" s="22" t="n"/>
+      <c r="O79" s="22" t="n"/>
+      <c r="P79" s="22" t="n"/>
+      <c r="Q79" s="22" t="n"/>
+      <c r="R79" s="22" t="n"/>
+      <c r="S79" s="22" t="n"/>
+      <c r="T79" s="23" t="n"/>
+      <c r="U79" s="23" t="n"/>
+      <c r="V79" s="23" t="n"/>
+      <c r="W79" s="23" t="n"/>
+      <c r="X79" s="23" t="n"/>
+      <c r="Y79" s="23" t="n"/>
+      <c r="Z79" s="23" t="n"/>
+      <c r="AA79" s="23" t="n"/>
+      <c r="AB79" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>S166</t>
+        </is>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="n"/>
+      <c r="D80" s="20" t="n"/>
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F80" s="21" t="n"/>
+      <c r="G80" s="21" t="n"/>
+      <c r="H80" s="21" t="n"/>
+      <c r="I80" s="21" t="n"/>
+      <c r="J80" s="21" t="n"/>
+      <c r="K80" s="21" t="n"/>
+      <c r="L80" s="22" t="n"/>
+      <c r="M80" s="22" t="n"/>
+      <c r="N80" s="22" t="n"/>
+      <c r="O80" s="22" t="n"/>
+      <c r="P80" s="22" t="n"/>
+      <c r="Q80" s="22" t="n"/>
+      <c r="R80" s="22" t="n"/>
+      <c r="S80" s="22" t="n"/>
+      <c r="T80" s="23" t="n"/>
+      <c r="U80" s="23" t="n"/>
+      <c r="V80" s="23" t="n"/>
+      <c r="W80" s="23" t="n"/>
+      <c r="X80" s="23" t="n"/>
+      <c r="Y80" s="23" t="n"/>
+      <c r="Z80" s="23" t="n"/>
+      <c r="AA80" s="23" t="n"/>
+      <c r="AB80" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>S165</t>
+        </is>
+      </c>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="n"/>
+      <c r="D81" s="20" t="n"/>
+      <c r="E81" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F81" s="21" t="n"/>
+      <c r="G81" s="21" t="n"/>
+      <c r="H81" s="21" t="n"/>
+      <c r="I81" s="21" t="n"/>
+      <c r="J81" s="21" t="n"/>
+      <c r="K81" s="21" t="n"/>
+      <c r="L81" s="22" t="n"/>
+      <c r="M81" s="22" t="n"/>
+      <c r="N81" s="22" t="n"/>
+      <c r="O81" s="22" t="n"/>
+      <c r="P81" s="22" t="n"/>
+      <c r="Q81" s="22" t="n"/>
+      <c r="R81" s="22" t="n"/>
+      <c r="S81" s="22" t="n"/>
+      <c r="T81" s="23" t="n"/>
+      <c r="U81" s="23" t="n"/>
+      <c r="V81" s="23" t="n"/>
+      <c r="W81" s="23" t="n"/>
+      <c r="X81" s="23" t="n"/>
+      <c r="Y81" s="23" t="n"/>
+      <c r="Z81" s="23" t="n"/>
+      <c r="AA81" s="23" t="n"/>
+      <c r="AB81" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>S164</t>
+        </is>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="n"/>
+      <c r="D82" s="20" t="n"/>
+      <c r="E82" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F82" s="21" t="n"/>
+      <c r="G82" s="21" t="n"/>
+      <c r="H82" s="21" t="n"/>
+      <c r="I82" s="21" t="n"/>
+      <c r="J82" s="21" t="n"/>
+      <c r="K82" s="21" t="n"/>
+      <c r="L82" s="22" t="n"/>
+      <c r="M82" s="22" t="n"/>
+      <c r="N82" s="22" t="n"/>
+      <c r="O82" s="22" t="n"/>
+      <c r="P82" s="22" t="n"/>
+      <c r="Q82" s="22" t="n"/>
+      <c r="R82" s="22" t="n"/>
+      <c r="S82" s="22" t="n"/>
+      <c r="T82" s="23" t="n"/>
+      <c r="U82" s="23" t="n"/>
+      <c r="V82" s="23" t="n"/>
+      <c r="W82" s="23" t="n"/>
+      <c r="X82" s="23" t="n"/>
+      <c r="Y82" s="23" t="n"/>
+      <c r="Z82" s="23" t="n"/>
+      <c r="AA82" s="23" t="n"/>
+      <c r="AB82" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>S150</t>
+        </is>
+      </c>
+      <c r="B83" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="n"/>
+      <c r="D83" s="20" t="n"/>
+      <c r="E83" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F83" s="21" t="n"/>
+      <c r="G83" s="21" t="n"/>
+      <c r="H83" s="21" t="n"/>
+      <c r="I83" s="21" t="n"/>
+      <c r="J83" s="21" t="n"/>
+      <c r="K83" s="21" t="n"/>
+      <c r="L83" s="22" t="n"/>
+      <c r="M83" s="22" t="n"/>
+      <c r="N83" s="22" t="n"/>
+      <c r="O83" s="22" t="n"/>
+      <c r="P83" s="22" t="n"/>
+      <c r="Q83" s="22" t="n"/>
+      <c r="R83" s="22" t="n"/>
+      <c r="S83" s="22" t="n"/>
+      <c r="T83" s="23" t="n"/>
+      <c r="U83" s="23" t="n"/>
+      <c r="V83" s="23" t="n"/>
+      <c r="W83" s="23" t="n"/>
+      <c r="X83" s="23" t="n"/>
+      <c r="Y83" s="23" t="n"/>
+      <c r="Z83" s="23" t="n"/>
+      <c r="AA83" s="23" t="n"/>
+      <c r="AB83" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>S147</t>
+        </is>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="n"/>
+      <c r="D84" s="20" t="n"/>
+      <c r="E84" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F84" s="21" t="n"/>
+      <c r="G84" s="21" t="n"/>
+      <c r="H84" s="21" t="n"/>
+      <c r="I84" s="21" t="n"/>
+      <c r="J84" s="21" t="n"/>
+      <c r="K84" s="21" t="n"/>
+      <c r="L84" s="22" t="n"/>
+      <c r="M84" s="22" t="n"/>
+      <c r="N84" s="22" t="n"/>
+      <c r="O84" s="22" t="n"/>
+      <c r="P84" s="22" t="n"/>
+      <c r="Q84" s="22" t="n"/>
+      <c r="R84" s="22" t="n"/>
+      <c r="S84" s="22" t="n"/>
+      <c r="T84" s="23" t="n"/>
+      <c r="U84" s="23" t="n"/>
+      <c r="V84" s="23" t="n"/>
+      <c r="W84" s="23" t="n"/>
+      <c r="X84" s="23" t="n"/>
+      <c r="Y84" s="23" t="n"/>
+      <c r="Z84" s="23" t="n"/>
+      <c r="AA84" s="23" t="n"/>
+      <c r="AB84" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20" t="inlineStr">
+        <is>
+          <t>S146</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C85" s="20" t="n"/>
+      <c r="D85" s="20" t="n"/>
+      <c r="E85" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="n"/>
+      <c r="G85" s="21" t="n"/>
+      <c r="H85" s="21" t="n"/>
+      <c r="I85" s="21" t="n"/>
+      <c r="J85" s="21" t="n"/>
+      <c r="K85" s="21" t="n"/>
+      <c r="L85" s="22" t="n"/>
+      <c r="M85" s="22" t="n"/>
+      <c r="N85" s="22" t="n"/>
+      <c r="O85" s="22" t="n"/>
+      <c r="P85" s="22" t="n"/>
+      <c r="Q85" s="22" t="n"/>
+      <c r="R85" s="22" t="n"/>
+      <c r="S85" s="22" t="n"/>
+      <c r="T85" s="23" t="n"/>
+      <c r="U85" s="23" t="n"/>
+      <c r="V85" s="23" t="n"/>
+      <c r="W85" s="23" t="n"/>
+      <c r="X85" s="23" t="n"/>
+      <c r="Y85" s="23" t="n"/>
+      <c r="Z85" s="23" t="n"/>
+      <c r="AA85" s="23" t="n"/>
+      <c r="AB85" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>S145</t>
+        </is>
+      </c>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="n"/>
+      <c r="D86" s="20" t="n"/>
+      <c r="E86" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F86" s="21" t="n"/>
+      <c r="G86" s="21" t="n"/>
+      <c r="H86" s="21" t="n"/>
+      <c r="I86" s="21" t="n"/>
+      <c r="J86" s="21" t="n"/>
+      <c r="K86" s="21" t="n"/>
+      <c r="L86" s="22" t="n"/>
+      <c r="M86" s="22" t="n"/>
+      <c r="N86" s="22" t="n"/>
+      <c r="O86" s="22" t="n"/>
+      <c r="P86" s="22" t="n"/>
+      <c r="Q86" s="22" t="n"/>
+      <c r="R86" s="22" t="n"/>
+      <c r="S86" s="22" t="n"/>
+      <c r="T86" s="23" t="n"/>
+      <c r="U86" s="23" t="n"/>
+      <c r="V86" s="23" t="n"/>
+      <c r="W86" s="23" t="n"/>
+      <c r="X86" s="23" t="n"/>
+      <c r="Y86" s="23" t="n"/>
+      <c r="Z86" s="23" t="n"/>
+      <c r="AA86" s="23" t="n"/>
+      <c r="AB86" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>S143</t>
+        </is>
+      </c>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C87" s="20" t="n"/>
+      <c r="D87" s="20" t="n"/>
+      <c r="E87" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F87" s="21" t="n"/>
+      <c r="G87" s="21" t="n"/>
+      <c r="H87" s="21" t="n"/>
+      <c r="I87" s="21" t="n"/>
+      <c r="J87" s="21" t="n"/>
+      <c r="K87" s="21" t="n"/>
+      <c r="L87" s="22" t="n"/>
+      <c r="M87" s="22" t="n"/>
+      <c r="N87" s="22" t="n"/>
+      <c r="O87" s="22" t="n"/>
+      <c r="P87" s="22" t="n"/>
+      <c r="Q87" s="22" t="n"/>
+      <c r="R87" s="22" t="n"/>
+      <c r="S87" s="22" t="n"/>
+      <c r="T87" s="23" t="n"/>
+      <c r="U87" s="23" t="n"/>
+      <c r="V87" s="23" t="n"/>
+      <c r="W87" s="23" t="n"/>
+      <c r="X87" s="23" t="n"/>
+      <c r="Y87" s="23" t="n"/>
+      <c r="Z87" s="23" t="n"/>
+      <c r="AA87" s="23" t="n"/>
+      <c r="AB87" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>S140</t>
+        </is>
+      </c>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C88" s="20" t="n"/>
+      <c r="D88" s="20" t="n"/>
+      <c r="E88" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F88" s="21" t="n"/>
+      <c r="G88" s="21" t="n"/>
+      <c r="H88" s="21" t="n"/>
+      <c r="I88" s="21" t="n"/>
+      <c r="J88" s="21" t="n"/>
+      <c r="K88" s="21" t="n"/>
+      <c r="L88" s="22" t="n"/>
+      <c r="M88" s="22" t="n"/>
+      <c r="N88" s="22" t="n"/>
+      <c r="O88" s="22" t="n"/>
+      <c r="P88" s="22" t="n"/>
+      <c r="Q88" s="22" t="n"/>
+      <c r="R88" s="22" t="n"/>
+      <c r="S88" s="22" t="n"/>
+      <c r="T88" s="23" t="n"/>
+      <c r="U88" s="23" t="n"/>
+      <c r="V88" s="23" t="n"/>
+      <c r="W88" s="23" t="n"/>
+      <c r="X88" s="23" t="n"/>
+      <c r="Y88" s="23" t="n"/>
+      <c r="Z88" s="23" t="n"/>
+      <c r="AA88" s="23" t="n"/>
+      <c r="AB88" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>S136</t>
+        </is>
+      </c>
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C89" s="20" t="n"/>
+      <c r="D89" s="20" t="n"/>
+      <c r="E89" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F89" s="21" t="n"/>
+      <c r="G89" s="21" t="n"/>
+      <c r="H89" s="21" t="n"/>
+      <c r="I89" s="21" t="n"/>
+      <c r="J89" s="21" t="n"/>
+      <c r="K89" s="21" t="n"/>
+      <c r="L89" s="22" t="n"/>
+      <c r="M89" s="22" t="n"/>
+      <c r="N89" s="22" t="n"/>
+      <c r="O89" s="22" t="n"/>
+      <c r="P89" s="22" t="n"/>
+      <c r="Q89" s="22" t="n"/>
+      <c r="R89" s="22" t="n"/>
+      <c r="S89" s="22" t="n"/>
+      <c r="T89" s="23" t="n"/>
+      <c r="U89" s="23" t="n"/>
+      <c r="V89" s="23" t="n"/>
+      <c r="W89" s="23" t="n"/>
+      <c r="X89" s="23" t="n"/>
+      <c r="Y89" s="23" t="n"/>
+      <c r="Z89" s="23" t="n"/>
+      <c r="AA89" s="23" t="n"/>
+      <c r="AB89" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>S134</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F90" s="21" t="n"/>
+      <c r="G90" s="21" t="n"/>
+      <c r="H90" s="21" t="n"/>
+      <c r="I90" s="21" t="n"/>
+      <c r="J90" s="21" t="n"/>
+      <c r="K90" s="21" t="n"/>
+      <c r="L90" s="22" t="n"/>
+      <c r="M90" s="22" t="n"/>
+      <c r="N90" s="22" t="n"/>
+      <c r="O90" s="22" t="n"/>
+      <c r="P90" s="22" t="n"/>
+      <c r="Q90" s="22" t="n"/>
+      <c r="R90" s="22" t="n"/>
+      <c r="S90" s="22" t="n"/>
+      <c r="T90" s="23" t="n"/>
+      <c r="U90" s="23" t="n"/>
+      <c r="V90" s="23" t="n"/>
+      <c r="W90" s="23" t="n"/>
+      <c r="X90" s="23" t="n"/>
+      <c r="Y90" s="23" t="n"/>
+      <c r="Z90" s="23" t="n"/>
+      <c r="AA90" s="23" t="n"/>
+      <c r="AB90" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="20" t="inlineStr">
+        <is>
+          <t>S133</t>
+        </is>
+      </c>
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C91" s="20" t="n"/>
+      <c r="D91" s="20" t="n"/>
+      <c r="E91" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="n"/>
+      <c r="G91" s="21" t="n"/>
+      <c r="H91" s="21" t="n"/>
+      <c r="I91" s="21" t="n"/>
+      <c r="J91" s="21" t="n"/>
+      <c r="K91" s="21" t="n"/>
+      <c r="L91" s="22" t="n"/>
+      <c r="M91" s="22" t="n"/>
+      <c r="N91" s="22" t="n"/>
+      <c r="O91" s="22" t="n"/>
+      <c r="P91" s="22" t="n"/>
+      <c r="Q91" s="22" t="n"/>
+      <c r="R91" s="22" t="n"/>
+      <c r="S91" s="22" t="n"/>
+      <c r="T91" s="23" t="n"/>
+      <c r="U91" s="23" t="n"/>
+      <c r="V91" s="23" t="n"/>
+      <c r="W91" s="23" t="n"/>
+      <c r="X91" s="23" t="n"/>
+      <c r="Y91" s="23" t="n"/>
+      <c r="Z91" s="23" t="n"/>
+      <c r="AA91" s="23" t="n"/>
+      <c r="AB91" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>S132</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="n"/>
+      <c r="D92" s="20" t="n"/>
+      <c r="E92" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F92" s="21" t="n"/>
+      <c r="G92" s="21" t="n"/>
+      <c r="H92" s="21" t="n"/>
+      <c r="I92" s="21" t="n"/>
+      <c r="J92" s="21" t="n"/>
+      <c r="K92" s="21" t="n"/>
+      <c r="L92" s="22" t="n"/>
+      <c r="M92" s="22" t="n"/>
+      <c r="N92" s="22" t="n"/>
+      <c r="O92" s="22" t="n"/>
+      <c r="P92" s="22" t="n"/>
+      <c r="Q92" s="22" t="n"/>
+      <c r="R92" s="22" t="n"/>
+      <c r="S92" s="22" t="n"/>
+      <c r="T92" s="23" t="n"/>
+      <c r="U92" s="23" t="n"/>
+      <c r="V92" s="23" t="n"/>
+      <c r="W92" s="23" t="n"/>
+      <c r="X92" s="23" t="n"/>
+      <c r="Y92" s="23" t="n"/>
+      <c r="Z92" s="23" t="n"/>
+      <c r="AA92" s="23" t="n"/>
+      <c r="AB92" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>S130</t>
+        </is>
+      </c>
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="n"/>
+      <c r="D93" s="20" t="n"/>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="n"/>
+      <c r="G93" s="21" t="n"/>
+      <c r="H93" s="21" t="n"/>
+      <c r="I93" s="21" t="n"/>
+      <c r="J93" s="21" t="n"/>
+      <c r="K93" s="21" t="n"/>
+      <c r="L93" s="22" t="n"/>
+      <c r="M93" s="22" t="n"/>
+      <c r="N93" s="22" t="n"/>
+      <c r="O93" s="22" t="n"/>
+      <c r="P93" s="22" t="n"/>
+      <c r="Q93" s="22" t="n"/>
+      <c r="R93" s="22" t="n"/>
+      <c r="S93" s="22" t="n"/>
+      <c r="T93" s="23" t="n"/>
+      <c r="U93" s="23" t="n"/>
+      <c r="V93" s="23" t="n"/>
+      <c r="W93" s="23" t="n"/>
+      <c r="X93" s="23" t="n"/>
+      <c r="Y93" s="23" t="n"/>
+      <c r="Z93" s="23" t="n"/>
+      <c r="AA93" s="23" t="n"/>
+      <c r="AB93" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>S129</t>
+        </is>
+      </c>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="n"/>
+      <c r="D94" s="20" t="n"/>
+      <c r="E94" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F94" s="21" t="n"/>
+      <c r="G94" s="21" t="n"/>
+      <c r="H94" s="21" t="n"/>
+      <c r="I94" s="21" t="n"/>
+      <c r="J94" s="21" t="n"/>
+      <c r="K94" s="21" t="n"/>
+      <c r="L94" s="22" t="n"/>
+      <c r="M94" s="22" t="n"/>
+      <c r="N94" s="22" t="n"/>
+      <c r="O94" s="22" t="n"/>
+      <c r="P94" s="22" t="n"/>
+      <c r="Q94" s="22" t="n"/>
+      <c r="R94" s="22" t="n"/>
+      <c r="S94" s="22" t="n"/>
+      <c r="T94" s="23" t="n"/>
+      <c r="U94" s="23" t="n"/>
+      <c r="V94" s="23" t="n"/>
+      <c r="W94" s="23" t="n"/>
+      <c r="X94" s="23" t="n"/>
+      <c r="Y94" s="23" t="n"/>
+      <c r="Z94" s="23" t="n"/>
+      <c r="AA94" s="23" t="n"/>
+      <c r="AB94" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>S126</t>
+        </is>
+      </c>
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C95" s="20" t="n"/>
+      <c r="D95" s="20" t="n"/>
+      <c r="E95" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="n"/>
+      <c r="G95" s="21" t="n"/>
+      <c r="H95" s="21" t="n"/>
+      <c r="I95" s="21" t="n"/>
+      <c r="J95" s="21" t="n"/>
+      <c r="K95" s="21" t="n"/>
+      <c r="L95" s="22" t="n"/>
+      <c r="M95" s="22" t="n"/>
+      <c r="N95" s="22" t="n"/>
+      <c r="O95" s="22" t="n"/>
+      <c r="P95" s="22" t="n"/>
+      <c r="Q95" s="22" t="n"/>
+      <c r="R95" s="22" t="n"/>
+      <c r="S95" s="22" t="n"/>
+      <c r="T95" s="23" t="n"/>
+      <c r="U95" s="23" t="n"/>
+      <c r="V95" s="23" t="n"/>
+      <c r="W95" s="23" t="n"/>
+      <c r="X95" s="23" t="n"/>
+      <c r="Y95" s="23" t="n"/>
+      <c r="Z95" s="23" t="n"/>
+      <c r="AA95" s="23" t="n"/>
+      <c r="AB95" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>S125</t>
+        </is>
+      </c>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="n"/>
+      <c r="D96" s="20" t="n"/>
+      <c r="E96" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F96" s="21" t="n"/>
+      <c r="G96" s="21" t="n"/>
+      <c r="H96" s="21" t="n"/>
+      <c r="I96" s="21" t="n"/>
+      <c r="J96" s="21" t="n"/>
+      <c r="K96" s="21" t="n"/>
+      <c r="L96" s="22" t="n"/>
+      <c r="M96" s="22" t="n"/>
+      <c r="N96" s="22" t="n"/>
+      <c r="O96" s="22" t="n"/>
+      <c r="P96" s="22" t="n"/>
+      <c r="Q96" s="22" t="n"/>
+      <c r="R96" s="22" t="n"/>
+      <c r="S96" s="22" t="n"/>
+      <c r="T96" s="23" t="n"/>
+      <c r="U96" s="23" t="n"/>
+      <c r="V96" s="23" t="n"/>
+      <c r="W96" s="23" t="n"/>
+      <c r="X96" s="23" t="n"/>
+      <c r="Y96" s="23" t="n"/>
+      <c r="Z96" s="23" t="n"/>
+      <c r="AA96" s="23" t="n"/>
+      <c r="AB96" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>S123</t>
+        </is>
+      </c>
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C97" s="20" t="n"/>
+      <c r="D97" s="20" t="n"/>
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F97" s="21" t="n"/>
+      <c r="G97" s="21" t="n"/>
+      <c r="H97" s="21" t="n"/>
+      <c r="I97" s="21" t="n"/>
+      <c r="J97" s="21" t="n"/>
+      <c r="K97" s="21" t="n"/>
+      <c r="L97" s="22" t="n"/>
+      <c r="M97" s="22" t="n"/>
+      <c r="N97" s="22" t="n"/>
+      <c r="O97" s="22" t="n"/>
+      <c r="P97" s="22" t="n"/>
+      <c r="Q97" s="22" t="n"/>
+      <c r="R97" s="22" t="n"/>
+      <c r="S97" s="22" t="n"/>
+      <c r="T97" s="23" t="n"/>
+      <c r="U97" s="23" t="n"/>
+      <c r="V97" s="23" t="n"/>
+      <c r="W97" s="23" t="n"/>
+      <c r="X97" s="23" t="n"/>
+      <c r="Y97" s="23" t="n"/>
+      <c r="Z97" s="23" t="n"/>
+      <c r="AA97" s="23" t="n"/>
+      <c r="AB97" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="n"/>
+      <c r="D98" s="20" t="n"/>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F98" s="21" t="n"/>
+      <c r="G98" s="21" t="n"/>
+      <c r="H98" s="21" t="n"/>
+      <c r="I98" s="21" t="n"/>
+      <c r="J98" s="21" t="n"/>
+      <c r="K98" s="21" t="n"/>
+      <c r="L98" s="22" t="n"/>
+      <c r="M98" s="22" t="n"/>
+      <c r="N98" s="22" t="n"/>
+      <c r="O98" s="22" t="n"/>
+      <c r="P98" s="22" t="n"/>
+      <c r="Q98" s="22" t="n"/>
+      <c r="R98" s="22" t="n"/>
+      <c r="S98" s="22" t="n"/>
+      <c r="T98" s="23" t="n"/>
+      <c r="U98" s="23" t="n"/>
+      <c r="V98" s="23" t="n"/>
+      <c r="W98" s="23" t="n"/>
+      <c r="X98" s="23" t="n"/>
+      <c r="Y98" s="23" t="n"/>
+      <c r="Z98" s="23" t="n"/>
+      <c r="AA98" s="23" t="n"/>
+      <c r="AB98" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>S121</t>
+        </is>
+      </c>
+      <c r="B99" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C99" s="20" t="n"/>
+      <c r="D99" s="20" t="n"/>
+      <c r="E99" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="n"/>
+      <c r="G99" s="21" t="n"/>
+      <c r="H99" s="21" t="n"/>
+      <c r="I99" s="21" t="n"/>
+      <c r="J99" s="21" t="n"/>
+      <c r="K99" s="21" t="n"/>
+      <c r="L99" s="22" t="n"/>
+      <c r="M99" s="22" t="n"/>
+      <c r="N99" s="22" t="n"/>
+      <c r="O99" s="22" t="n"/>
+      <c r="P99" s="22" t="n"/>
+      <c r="Q99" s="22" t="n"/>
+      <c r="R99" s="22" t="n"/>
+      <c r="S99" s="22" t="n"/>
+      <c r="T99" s="23" t="n"/>
+      <c r="U99" s="23" t="n"/>
+      <c r="V99" s="23" t="n"/>
+      <c r="W99" s="23" t="n"/>
+      <c r="X99" s="23" t="n"/>
+      <c r="Y99" s="23" t="n"/>
+      <c r="Z99" s="23" t="n"/>
+      <c r="AA99" s="23" t="n"/>
+      <c r="AB99" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>S120</t>
+        </is>
+      </c>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="n"/>
+      <c r="D100" s="20" t="n"/>
+      <c r="E100" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F100" s="21" t="n"/>
+      <c r="G100" s="21" t="n"/>
+      <c r="H100" s="21" t="n"/>
+      <c r="I100" s="21" t="n"/>
+      <c r="J100" s="21" t="n"/>
+      <c r="K100" s="21" t="n"/>
+      <c r="L100" s="22" t="n"/>
+      <c r="M100" s="22" t="n"/>
+      <c r="N100" s="22" t="n"/>
+      <c r="O100" s="22" t="n"/>
+      <c r="P100" s="22" t="n"/>
+      <c r="Q100" s="22" t="n"/>
+      <c r="R100" s="22" t="n"/>
+      <c r="S100" s="22" t="n"/>
+      <c r="T100" s="23" t="n"/>
+      <c r="U100" s="23" t="n"/>
+      <c r="V100" s="23" t="n"/>
+      <c r="W100" s="23" t="n"/>
+      <c r="X100" s="23" t="n"/>
+      <c r="Y100" s="23" t="n"/>
+      <c r="Z100" s="23" t="n"/>
+      <c r="AA100" s="23" t="n"/>
+      <c r="AB100" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="20" t="inlineStr">
+        <is>
+          <t>S119</t>
+        </is>
+      </c>
+      <c r="B101" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C101" s="20" t="n"/>
+      <c r="D101" s="20" t="n"/>
+      <c r="E101" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="n"/>
+      <c r="G101" s="21" t="n"/>
+      <c r="H101" s="21" t="n"/>
+      <c r="I101" s="21" t="n"/>
+      <c r="J101" s="21" t="n"/>
+      <c r="K101" s="21" t="n"/>
+      <c r="L101" s="22" t="n"/>
+      <c r="M101" s="22" t="n"/>
+      <c r="N101" s="22" t="n"/>
+      <c r="O101" s="22" t="n"/>
+      <c r="P101" s="22" t="n"/>
+      <c r="Q101" s="22" t="n"/>
+      <c r="R101" s="22" t="n"/>
+      <c r="S101" s="22" t="n"/>
+      <c r="T101" s="23" t="n"/>
+      <c r="U101" s="23" t="n"/>
+      <c r="V101" s="23" t="n"/>
+      <c r="W101" s="23" t="n"/>
+      <c r="X101" s="23" t="n"/>
+      <c r="Y101" s="23" t="n"/>
+      <c r="Z101" s="23" t="n"/>
+      <c r="AA101" s="23" t="n"/>
+      <c r="AB101" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>S117</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="n"/>
+      <c r="D102" s="20" t="n"/>
+      <c r="E102" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F102" s="21" t="n"/>
+      <c r="G102" s="21" t="n"/>
+      <c r="H102" s="21" t="n"/>
+      <c r="I102" s="21" t="n"/>
+      <c r="J102" s="21" t="n"/>
+      <c r="K102" s="21" t="n"/>
+      <c r="L102" s="22" t="n"/>
+      <c r="M102" s="22" t="n"/>
+      <c r="N102" s="22" t="n"/>
+      <c r="O102" s="22" t="n"/>
+      <c r="P102" s="22" t="n"/>
+      <c r="Q102" s="22" t="n"/>
+      <c r="R102" s="22" t="n"/>
+      <c r="S102" s="22" t="n"/>
+      <c r="T102" s="23" t="n"/>
+      <c r="U102" s="23" t="n"/>
+      <c r="V102" s="23" t="n"/>
+      <c r="W102" s="23" t="n"/>
+      <c r="X102" s="23" t="n"/>
+      <c r="Y102" s="23" t="n"/>
+      <c r="Z102" s="23" t="n"/>
+      <c r="AA102" s="23" t="n"/>
+      <c r="AB102" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t>S112</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C103" s="20" t="n"/>
+      <c r="D103" s="20" t="n"/>
+      <c r="E103" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="n"/>
+      <c r="G103" s="21" t="n"/>
+      <c r="H103" s="21" t="n"/>
+      <c r="I103" s="21" t="n"/>
+      <c r="J103" s="21" t="n"/>
+      <c r="K103" s="21" t="n"/>
+      <c r="L103" s="22" t="n"/>
+      <c r="M103" s="22" t="n"/>
+      <c r="N103" s="22" t="n"/>
+      <c r="O103" s="22" t="n"/>
+      <c r="P103" s="22" t="n"/>
+      <c r="Q103" s="22" t="n"/>
+      <c r="R103" s="22" t="n"/>
+      <c r="S103" s="22" t="n"/>
+      <c r="T103" s="23" t="n"/>
+      <c r="U103" s="23" t="n"/>
+      <c r="V103" s="23" t="n"/>
+      <c r="W103" s="23" t="n"/>
+      <c r="X103" s="23" t="n"/>
+      <c r="Y103" s="23" t="n"/>
+      <c r="Z103" s="23" t="n"/>
+      <c r="AA103" s="23" t="n"/>
+      <c r="AB103" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>S111</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="n"/>
+      <c r="D104" s="20" t="n"/>
+      <c r="E104" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F104" s="21" t="n"/>
+      <c r="G104" s="21" t="n"/>
+      <c r="H104" s="21" t="n"/>
+      <c r="I104" s="21" t="n"/>
+      <c r="J104" s="21" t="n"/>
+      <c r="K104" s="21" t="n"/>
+      <c r="L104" s="22" t="n"/>
+      <c r="M104" s="22" t="n"/>
+      <c r="N104" s="22" t="n"/>
+      <c r="O104" s="22" t="n"/>
+      <c r="P104" s="22" t="n"/>
+      <c r="Q104" s="22" t="n"/>
+      <c r="R104" s="22" t="n"/>
+      <c r="S104" s="22" t="n"/>
+      <c r="T104" s="23" t="n"/>
+      <c r="U104" s="23" t="n"/>
+      <c r="V104" s="23" t="n"/>
+      <c r="W104" s="23" t="n"/>
+      <c r="X104" s="23" t="n"/>
+      <c r="Y104" s="23" t="n"/>
+      <c r="Z104" s="23" t="n"/>
+      <c r="AA104" s="23" t="n"/>
+      <c r="AB104" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>S109</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C105" s="20" t="n"/>
+      <c r="D105" s="20" t="n"/>
+      <c r="E105" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="n"/>
+      <c r="G105" s="21" t="n"/>
+      <c r="H105" s="21" t="n"/>
+      <c r="I105" s="21" t="n"/>
+      <c r="J105" s="21" t="n"/>
+      <c r="K105" s="21" t="n"/>
+      <c r="L105" s="22" t="n"/>
+      <c r="M105" s="22" t="n"/>
+      <c r="N105" s="22" t="n"/>
+      <c r="O105" s="22" t="n"/>
+      <c r="P105" s="22" t="n"/>
+      <c r="Q105" s="22" t="n"/>
+      <c r="R105" s="22" t="n"/>
+      <c r="S105" s="22" t="n"/>
+      <c r="T105" s="23" t="n"/>
+      <c r="U105" s="23" t="n"/>
+      <c r="V105" s="23" t="n"/>
+      <c r="W105" s="23" t="n"/>
+      <c r="X105" s="23" t="n"/>
+      <c r="Y105" s="23" t="n"/>
+      <c r="Z105" s="23" t="n"/>
+      <c r="AA105" s="23" t="n"/>
+      <c r="AB105" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>S101</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="n"/>
+      <c r="D106" s="20" t="n"/>
+      <c r="E106" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F106" s="21" t="n"/>
+      <c r="G106" s="21" t="n"/>
+      <c r="H106" s="21" t="n"/>
+      <c r="I106" s="21" t="n"/>
+      <c r="J106" s="21" t="n"/>
+      <c r="K106" s="21" t="n"/>
+      <c r="L106" s="22" t="n"/>
+      <c r="M106" s="22" t="n"/>
+      <c r="N106" s="22" t="n"/>
+      <c r="O106" s="22" t="n"/>
+      <c r="P106" s="22" t="n"/>
+      <c r="Q106" s="22" t="n"/>
+      <c r="R106" s="22" t="n"/>
+      <c r="S106" s="22" t="n"/>
+      <c r="T106" s="23" t="n"/>
+      <c r="U106" s="23" t="n"/>
+      <c r="V106" s="23" t="n"/>
+      <c r="W106" s="23" t="n"/>
+      <c r="X106" s="23" t="n"/>
+      <c r="Y106" s="23" t="n"/>
+      <c r="Z106" s="23" t="n"/>
+      <c r="AA106" s="23" t="n"/>
+      <c r="AB106" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>R847</t>
+        </is>
+      </c>
+      <c r="B107" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C107" s="20" t="n"/>
+      <c r="D107" s="20" t="n"/>
+      <c r="E107" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="n"/>
+      <c r="G107" s="21" t="n"/>
+      <c r="H107" s="21" t="n"/>
+      <c r="I107" s="21" t="n"/>
+      <c r="J107" s="21" t="n"/>
+      <c r="K107" s="21" t="n"/>
+      <c r="L107" s="22" t="n"/>
+      <c r="M107" s="22" t="n"/>
+      <c r="N107" s="22" t="n"/>
+      <c r="O107" s="22" t="n"/>
+      <c r="P107" s="22" t="n"/>
+      <c r="Q107" s="22" t="n"/>
+      <c r="R107" s="22" t="n"/>
+      <c r="S107" s="22" t="n"/>
+      <c r="T107" s="23" t="n"/>
+      <c r="U107" s="23" t="n"/>
+      <c r="V107" s="23" t="n"/>
+      <c r="W107" s="23" t="n"/>
+      <c r="X107" s="23" t="n"/>
+      <c r="Y107" s="23" t="n"/>
+      <c r="Z107" s="23" t="n"/>
+      <c r="AA107" s="23" t="n"/>
+      <c r="AB107" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>R707</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="n"/>
+      <c r="D108" s="20" t="n"/>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F108" s="21" t="n"/>
+      <c r="G108" s="21" t="n"/>
+      <c r="H108" s="21" t="n"/>
+      <c r="I108" s="21" t="n"/>
+      <c r="J108" s="21" t="n"/>
+      <c r="K108" s="21" t="n"/>
+      <c r="L108" s="22" t="n"/>
+      <c r="M108" s="22" t="n"/>
+      <c r="N108" s="22" t="n"/>
+      <c r="O108" s="22" t="n"/>
+      <c r="P108" s="22" t="n"/>
+      <c r="Q108" s="22" t="n"/>
+      <c r="R108" s="22" t="n"/>
+      <c r="S108" s="22" t="n"/>
+      <c r="T108" s="23" t="n"/>
+      <c r="U108" s="23" t="n"/>
+      <c r="V108" s="23" t="n"/>
+      <c r="W108" s="23" t="n"/>
+      <c r="X108" s="23" t="n"/>
+      <c r="Y108" s="23" t="n"/>
+      <c r="Z108" s="23" t="n"/>
+      <c r="AA108" s="23" t="n"/>
+      <c r="AB108" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20" t="inlineStr">
+        <is>
+          <t>R1932</t>
+        </is>
+      </c>
+      <c r="B109" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C109" s="20" t="n"/>
+      <c r="D109" s="20" t="n"/>
+      <c r="E109" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="n"/>
+      <c r="G109" s="21" t="n"/>
+      <c r="H109" s="21" t="n"/>
+      <c r="I109" s="21" t="n"/>
+      <c r="J109" s="21" t="n"/>
+      <c r="K109" s="21" t="n"/>
+      <c r="L109" s="22" t="n"/>
+      <c r="M109" s="22" t="n"/>
+      <c r="N109" s="22" t="n"/>
+      <c r="O109" s="22" t="n"/>
+      <c r="P109" s="22" t="n"/>
+      <c r="Q109" s="22" t="n"/>
+      <c r="R109" s="22" t="n"/>
+      <c r="S109" s="22" t="n"/>
+      <c r="T109" s="23" t="n"/>
+      <c r="U109" s="23" t="n"/>
+      <c r="V109" s="23" t="n"/>
+      <c r="W109" s="23" t="n"/>
+      <c r="X109" s="23" t="n"/>
+      <c r="Y109" s="23" t="n"/>
+      <c r="Z109" s="23" t="n"/>
+      <c r="AA109" s="23" t="n"/>
+      <c r="AB109" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>R1891</t>
+        </is>
+      </c>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="n"/>
+      <c r="D110" s="20" t="n"/>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F110" s="21" t="n"/>
+      <c r="G110" s="21" t="n"/>
+      <c r="H110" s="21" t="n"/>
+      <c r="I110" s="21" t="n"/>
+      <c r="J110" s="21" t="n"/>
+      <c r="K110" s="21" t="n"/>
+      <c r="L110" s="22" t="n"/>
+      <c r="M110" s="22" t="n"/>
+      <c r="N110" s="22" t="n"/>
+      <c r="O110" s="22" t="n"/>
+      <c r="P110" s="22" t="n"/>
+      <c r="Q110" s="22" t="n"/>
+      <c r="R110" s="22" t="n"/>
+      <c r="S110" s="22" t="n"/>
+      <c r="T110" s="23" t="n"/>
+      <c r="U110" s="23" t="n"/>
+      <c r="V110" s="23" t="n"/>
+      <c r="W110" s="23" t="n"/>
+      <c r="X110" s="23" t="n"/>
+      <c r="Y110" s="23" t="n"/>
+      <c r="Z110" s="23" t="n"/>
+      <c r="AA110" s="23" t="n"/>
+      <c r="AB110" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="20" t="inlineStr">
+        <is>
+          <t>R1785</t>
+        </is>
+      </c>
+      <c r="B111" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C111" s="20" t="n"/>
+      <c r="D111" s="20" t="n"/>
+      <c r="E111" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="n"/>
+      <c r="G111" s="21" t="n"/>
+      <c r="H111" s="21" t="n"/>
+      <c r="I111" s="21" t="n"/>
+      <c r="J111" s="21" t="n"/>
+      <c r="K111" s="21" t="n"/>
+      <c r="L111" s="22" t="n"/>
+      <c r="M111" s="22" t="n"/>
+      <c r="N111" s="22" t="n"/>
+      <c r="O111" s="22" t="n"/>
+      <c r="P111" s="22" t="n"/>
+      <c r="Q111" s="22" t="n"/>
+      <c r="R111" s="22" t="n"/>
+      <c r="S111" s="22" t="n"/>
+      <c r="T111" s="23" t="n"/>
+      <c r="U111" s="23" t="n"/>
+      <c r="V111" s="23" t="n"/>
+      <c r="W111" s="23" t="n"/>
+      <c r="X111" s="23" t="n"/>
+      <c r="Y111" s="23" t="n"/>
+      <c r="Z111" s="23" t="n"/>
+      <c r="AA111" s="23" t="n"/>
+      <c r="AB111" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>R1784</t>
+        </is>
+      </c>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="n"/>
+      <c r="D112" s="20" t="n"/>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="n"/>
+      <c r="G112" s="21" t="n"/>
+      <c r="H112" s="21" t="n"/>
+      <c r="I112" s="21" t="n"/>
+      <c r="J112" s="21" t="n"/>
+      <c r="K112" s="21" t="n"/>
+      <c r="L112" s="22" t="n"/>
+      <c r="M112" s="22" t="n"/>
+      <c r="N112" s="22" t="n"/>
+      <c r="O112" s="22" t="n"/>
+      <c r="P112" s="22" t="n"/>
+      <c r="Q112" s="22" t="n"/>
+      <c r="R112" s="22" t="n"/>
+      <c r="S112" s="22" t="n"/>
+      <c r="T112" s="23" t="n"/>
+      <c r="U112" s="23" t="n"/>
+      <c r="V112" s="23" t="n"/>
+      <c r="W112" s="23" t="n"/>
+      <c r="X112" s="23" t="n"/>
+      <c r="Y112" s="23" t="n"/>
+      <c r="Z112" s="23" t="n"/>
+      <c r="AA112" s="23" t="n"/>
+      <c r="AB112" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20" t="inlineStr">
+        <is>
+          <t>R1783</t>
+        </is>
+      </c>
+      <c r="B113" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C113" s="20" t="n"/>
+      <c r="D113" s="20" t="n"/>
+      <c r="E113" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="n"/>
+      <c r="G113" s="21" t="n"/>
+      <c r="H113" s="21" t="n"/>
+      <c r="I113" s="21" t="n"/>
+      <c r="J113" s="21" t="n"/>
+      <c r="K113" s="21" t="n"/>
+      <c r="L113" s="22" t="n"/>
+      <c r="M113" s="22" t="n"/>
+      <c r="N113" s="22" t="n"/>
+      <c r="O113" s="22" t="n"/>
+      <c r="P113" s="22" t="n"/>
+      <c r="Q113" s="22" t="n"/>
+      <c r="R113" s="22" t="n"/>
+      <c r="S113" s="22" t="n"/>
+      <c r="T113" s="23" t="n"/>
+      <c r="U113" s="23" t="n"/>
+      <c r="V113" s="23" t="n"/>
+      <c r="W113" s="23" t="n"/>
+      <c r="X113" s="23" t="n"/>
+      <c r="Y113" s="23" t="n"/>
+      <c r="Z113" s="23" t="n"/>
+      <c r="AA113" s="23" t="n"/>
+      <c r="AB113" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>R1772</t>
+        </is>
+      </c>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="n"/>
+      <c r="D114" s="20" t="n"/>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F114" s="21" t="n"/>
+      <c r="G114" s="21" t="n"/>
+      <c r="H114" s="21" t="n"/>
+      <c r="I114" s="21" t="n"/>
+      <c r="J114" s="21" t="n"/>
+      <c r="K114" s="21" t="n"/>
+      <c r="L114" s="22" t="n"/>
+      <c r="M114" s="22" t="n"/>
+      <c r="N114" s="22" t="n"/>
+      <c r="O114" s="22" t="n"/>
+      <c r="P114" s="22" t="n"/>
+      <c r="Q114" s="22" t="n"/>
+      <c r="R114" s="22" t="n"/>
+      <c r="S114" s="22" t="n"/>
+      <c r="T114" s="23" t="n"/>
+      <c r="U114" s="23" t="n"/>
+      <c r="V114" s="23" t="n"/>
+      <c r="W114" s="23" t="n"/>
+      <c r="X114" s="23" t="n"/>
+      <c r="Y114" s="23" t="n"/>
+      <c r="Z114" s="23" t="n"/>
+      <c r="AA114" s="23" t="n"/>
+      <c r="AB114" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20" t="inlineStr">
+        <is>
+          <t>R1714</t>
+        </is>
+      </c>
+      <c r="B115" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C115" s="20" t="n"/>
+      <c r="D115" s="20" t="n"/>
+      <c r="E115" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="n"/>
+      <c r="G115" s="21" t="n"/>
+      <c r="H115" s="21" t="n"/>
+      <c r="I115" s="21" t="n"/>
+      <c r="J115" s="21" t="n"/>
+      <c r="K115" s="21" t="n"/>
+      <c r="L115" s="22" t="n"/>
+      <c r="M115" s="22" t="n"/>
+      <c r="N115" s="22" t="n"/>
+      <c r="O115" s="22" t="n"/>
+      <c r="P115" s="22" t="n"/>
+      <c r="Q115" s="22" t="n"/>
+      <c r="R115" s="22" t="n"/>
+      <c r="S115" s="22" t="n"/>
+      <c r="T115" s="23" t="n"/>
+      <c r="U115" s="23" t="n"/>
+      <c r="V115" s="23" t="n"/>
+      <c r="W115" s="23" t="n"/>
+      <c r="X115" s="23" t="n"/>
+      <c r="Y115" s="23" t="n"/>
+      <c r="Z115" s="23" t="n"/>
+      <c r="AA115" s="23" t="n"/>
+      <c r="AB115" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>R1713</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="n"/>
+      <c r="D116" s="20" t="n"/>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F116" s="21" t="n"/>
+      <c r="G116" s="21" t="n"/>
+      <c r="H116" s="21" t="n"/>
+      <c r="I116" s="21" t="n"/>
+      <c r="J116" s="21" t="n"/>
+      <c r="K116" s="21" t="n"/>
+      <c r="L116" s="22" t="n"/>
+      <c r="M116" s="22" t="n"/>
+      <c r="N116" s="22" t="n"/>
+      <c r="O116" s="22" t="n"/>
+      <c r="P116" s="22" t="n"/>
+      <c r="Q116" s="22" t="n"/>
+      <c r="R116" s="22" t="n"/>
+      <c r="S116" s="22" t="n"/>
+      <c r="T116" s="23" t="n"/>
+      <c r="U116" s="23" t="n"/>
+      <c r="V116" s="23" t="n"/>
+      <c r="W116" s="23" t="n"/>
+      <c r="X116" s="23" t="n"/>
+      <c r="Y116" s="23" t="n"/>
+      <c r="Z116" s="23" t="n"/>
+      <c r="AA116" s="23" t="n"/>
+      <c r="AB116" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
+        <is>
+          <t>R1709</t>
+        </is>
+      </c>
+      <c r="B117" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C117" s="20" t="n"/>
+      <c r="D117" s="20" t="n"/>
+      <c r="E117" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="n"/>
+      <c r="G117" s="21" t="n"/>
+      <c r="H117" s="21" t="n"/>
+      <c r="I117" s="21" t="n"/>
+      <c r="J117" s="21" t="n"/>
+      <c r="K117" s="21" t="n"/>
+      <c r="L117" s="22" t="n"/>
+      <c r="M117" s="22" t="n"/>
+      <c r="N117" s="22" t="n"/>
+      <c r="O117" s="22" t="n"/>
+      <c r="P117" s="22" t="n"/>
+      <c r="Q117" s="22" t="n"/>
+      <c r="R117" s="22" t="n"/>
+      <c r="S117" s="22" t="n"/>
+      <c r="T117" s="23" t="n"/>
+      <c r="U117" s="23" t="n"/>
+      <c r="V117" s="23" t="n"/>
+      <c r="W117" s="23" t="n"/>
+      <c r="X117" s="23" t="n"/>
+      <c r="Y117" s="23" t="n"/>
+      <c r="Z117" s="23" t="n"/>
+      <c r="AA117" s="23" t="n"/>
+      <c r="AB117" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>R1689</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="n"/>
+      <c r="D118" s="20" t="n"/>
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F118" s="21" t="n"/>
+      <c r="G118" s="21" t="n"/>
+      <c r="H118" s="21" t="n"/>
+      <c r="I118" s="21" t="n"/>
+      <c r="J118" s="21" t="n"/>
+      <c r="K118" s="21" t="n"/>
+      <c r="L118" s="22" t="n"/>
+      <c r="M118" s="22" t="n"/>
+      <c r="N118" s="22" t="n"/>
+      <c r="O118" s="22" t="n"/>
+      <c r="P118" s="22" t="n"/>
+      <c r="Q118" s="22" t="n"/>
+      <c r="R118" s="22" t="n"/>
+      <c r="S118" s="22" t="n"/>
+      <c r="T118" s="23" t="n"/>
+      <c r="U118" s="23" t="n"/>
+      <c r="V118" s="23" t="n"/>
+      <c r="W118" s="23" t="n"/>
+      <c r="X118" s="23" t="n"/>
+      <c r="Y118" s="23" t="n"/>
+      <c r="Z118" s="23" t="n"/>
+      <c r="AA118" s="23" t="n"/>
+      <c r="AB118" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>R1688</t>
+        </is>
+      </c>
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C119" s="20" t="n"/>
+      <c r="D119" s="20" t="n"/>
+      <c r="E119" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="n"/>
+      <c r="G119" s="21" t="n"/>
+      <c r="H119" s="21" t="n"/>
+      <c r="I119" s="21" t="n"/>
+      <c r="J119" s="21" t="n"/>
+      <c r="K119" s="21" t="n"/>
+      <c r="L119" s="22" t="n"/>
+      <c r="M119" s="22" t="n"/>
+      <c r="N119" s="22" t="n"/>
+      <c r="O119" s="22" t="n"/>
+      <c r="P119" s="22" t="n"/>
+      <c r="Q119" s="22" t="n"/>
+      <c r="R119" s="22" t="n"/>
+      <c r="S119" s="22" t="n"/>
+      <c r="T119" s="23" t="n"/>
+      <c r="U119" s="23" t="n"/>
+      <c r="V119" s="23" t="n"/>
+      <c r="W119" s="23" t="n"/>
+      <c r="X119" s="23" t="n"/>
+      <c r="Y119" s="23" t="n"/>
+      <c r="Z119" s="23" t="n"/>
+      <c r="AA119" s="23" t="n"/>
+      <c r="AB119" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>R1687</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="n"/>
+      <c r="D120" s="20" t="n"/>
+      <c r="E120" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F120" s="21" t="n"/>
+      <c r="G120" s="21" t="n"/>
+      <c r="H120" s="21" t="n"/>
+      <c r="I120" s="21" t="n"/>
+      <c r="J120" s="21" t="n"/>
+      <c r="K120" s="21" t="n"/>
+      <c r="L120" s="22" t="n"/>
+      <c r="M120" s="22" t="n"/>
+      <c r="N120" s="22" t="n"/>
+      <c r="O120" s="22" t="n"/>
+      <c r="P120" s="22" t="n"/>
+      <c r="Q120" s="22" t="n"/>
+      <c r="R120" s="22" t="n"/>
+      <c r="S120" s="22" t="n"/>
+      <c r="T120" s="23" t="n"/>
+      <c r="U120" s="23" t="n"/>
+      <c r="V120" s="23" t="n"/>
+      <c r="W120" s="23" t="n"/>
+      <c r="X120" s="23" t="n"/>
+      <c r="Y120" s="23" t="n"/>
+      <c r="Z120" s="23" t="n"/>
+      <c r="AA120" s="23" t="n"/>
+      <c r="AB120" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20" t="inlineStr">
+        <is>
+          <t>R1682</t>
+        </is>
+      </c>
+      <c r="B121" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C121" s="20" t="n"/>
+      <c r="D121" s="20" t="n"/>
+      <c r="E121" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="n"/>
+      <c r="G121" s="21" t="n"/>
+      <c r="H121" s="21" t="n"/>
+      <c r="I121" s="21" t="n"/>
+      <c r="J121" s="21" t="n"/>
+      <c r="K121" s="21" t="n"/>
+      <c r="L121" s="22" t="n"/>
+      <c r="M121" s="22" t="n"/>
+      <c r="N121" s="22" t="n"/>
+      <c r="O121" s="22" t="n"/>
+      <c r="P121" s="22" t="n"/>
+      <c r="Q121" s="22" t="n"/>
+      <c r="R121" s="22" t="n"/>
+      <c r="S121" s="22" t="n"/>
+      <c r="T121" s="23" t="n"/>
+      <c r="U121" s="23" t="n"/>
+      <c r="V121" s="23" t="n"/>
+      <c r="W121" s="23" t="n"/>
+      <c r="X121" s="23" t="n"/>
+      <c r="Y121" s="23" t="n"/>
+      <c r="Z121" s="23" t="n"/>
+      <c r="AA121" s="23" t="n"/>
+      <c r="AB121" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>R1680</t>
+        </is>
+      </c>
+      <c r="B122" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="n"/>
+      <c r="D122" s="20" t="n"/>
+      <c r="E122" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F122" s="21" t="n"/>
+      <c r="G122" s="21" t="n"/>
+      <c r="H122" s="21" t="n"/>
+      <c r="I122" s="21" t="n"/>
+      <c r="J122" s="21" t="n"/>
+      <c r="K122" s="21" t="n"/>
+      <c r="L122" s="22" t="n"/>
+      <c r="M122" s="22" t="n"/>
+      <c r="N122" s="22" t="n"/>
+      <c r="O122" s="22" t="n"/>
+      <c r="P122" s="22" t="n"/>
+      <c r="Q122" s="22" t="n"/>
+      <c r="R122" s="22" t="n"/>
+      <c r="S122" s="22" t="n"/>
+      <c r="T122" s="23" t="n"/>
+      <c r="U122" s="23" t="n"/>
+      <c r="V122" s="23" t="n"/>
+      <c r="W122" s="23" t="n"/>
+      <c r="X122" s="23" t="n"/>
+      <c r="Y122" s="23" t="n"/>
+      <c r="Z122" s="23" t="n"/>
+      <c r="AA122" s="23" t="n"/>
+      <c r="AB122" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="20" t="inlineStr">
+        <is>
+          <t>R1623</t>
+        </is>
+      </c>
+      <c r="B123" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C123" s="20" t="n"/>
+      <c r="D123" s="20" t="n"/>
+      <c r="E123" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="n"/>
+      <c r="G123" s="21" t="n"/>
+      <c r="H123" s="21" t="n"/>
+      <c r="I123" s="21" t="n"/>
+      <c r="J123" s="21" t="n"/>
+      <c r="K123" s="21" t="n"/>
+      <c r="L123" s="22" t="n"/>
+      <c r="M123" s="22" t="n"/>
+      <c r="N123" s="22" t="n"/>
+      <c r="O123" s="22" t="n"/>
+      <c r="P123" s="22" t="n"/>
+      <c r="Q123" s="22" t="n"/>
+      <c r="R123" s="22" t="n"/>
+      <c r="S123" s="22" t="n"/>
+      <c r="T123" s="23" t="n"/>
+      <c r="U123" s="23" t="n"/>
+      <c r="V123" s="23" t="n"/>
+      <c r="W123" s="23" t="n"/>
+      <c r="X123" s="23" t="n"/>
+      <c r="Y123" s="23" t="n"/>
+      <c r="Z123" s="23" t="n"/>
+      <c r="AA123" s="23" t="n"/>
+      <c r="AB123" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>R1527</t>
+        </is>
+      </c>
+      <c r="B124" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="n"/>
+      <c r="D124" s="20" t="n"/>
+      <c r="E124" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F124" s="21" t="n"/>
+      <c r="G124" s="21" t="n"/>
+      <c r="H124" s="21" t="n"/>
+      <c r="I124" s="21" t="n"/>
+      <c r="J124" s="21" t="n"/>
+      <c r="K124" s="21" t="n"/>
+      <c r="L124" s="22" t="n"/>
+      <c r="M124" s="22" t="n"/>
+      <c r="N124" s="22" t="n"/>
+      <c r="O124" s="22" t="n"/>
+      <c r="P124" s="22" t="n"/>
+      <c r="Q124" s="22" t="n"/>
+      <c r="R124" s="22" t="n"/>
+      <c r="S124" s="22" t="n"/>
+      <c r="T124" s="23" t="n"/>
+      <c r="U124" s="23" t="n"/>
+      <c r="V124" s="23" t="n"/>
+      <c r="W124" s="23" t="n"/>
+      <c r="X124" s="23" t="n"/>
+      <c r="Y124" s="23" t="n"/>
+      <c r="Z124" s="23" t="n"/>
+      <c r="AA124" s="23" t="n"/>
+      <c r="AB124" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="20" t="inlineStr">
+        <is>
+          <t>R1526</t>
+        </is>
+      </c>
+      <c r="B125" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C125" s="20" t="n"/>
+      <c r="D125" s="20" t="n"/>
+      <c r="E125" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="n"/>
+      <c r="G125" s="21" t="n"/>
+      <c r="H125" s="21" t="n"/>
+      <c r="I125" s="21" t="n"/>
+      <c r="J125" s="21" t="n"/>
+      <c r="K125" s="21" t="n"/>
+      <c r="L125" s="22" t="n"/>
+      <c r="M125" s="22" t="n"/>
+      <c r="N125" s="22" t="n"/>
+      <c r="O125" s="22" t="n"/>
+      <c r="P125" s="22" t="n"/>
+      <c r="Q125" s="22" t="n"/>
+      <c r="R125" s="22" t="n"/>
+      <c r="S125" s="22" t="n"/>
+      <c r="T125" s="23" t="n"/>
+      <c r="U125" s="23" t="n"/>
+      <c r="V125" s="23" t="n"/>
+      <c r="W125" s="23" t="n"/>
+      <c r="X125" s="23" t="n"/>
+      <c r="Y125" s="23" t="n"/>
+      <c r="Z125" s="23" t="n"/>
+      <c r="AA125" s="23" t="n"/>
+      <c r="AB125" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
+        <is>
+          <t>R1522</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="n"/>
+      <c r="D126" s="20" t="n"/>
+      <c r="E126" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F126" s="21" t="n"/>
+      <c r="G126" s="21" t="n"/>
+      <c r="H126" s="21" t="n"/>
+      <c r="I126" s="21" t="n"/>
+      <c r="J126" s="21" t="n"/>
+      <c r="K126" s="21" t="n"/>
+      <c r="L126" s="22" t="n"/>
+      <c r="M126" s="22" t="n"/>
+      <c r="N126" s="22" t="n"/>
+      <c r="O126" s="22" t="n"/>
+      <c r="P126" s="22" t="n"/>
+      <c r="Q126" s="22" t="n"/>
+      <c r="R126" s="22" t="n"/>
+      <c r="S126" s="22" t="n"/>
+      <c r="T126" s="23" t="n"/>
+      <c r="U126" s="23" t="n"/>
+      <c r="V126" s="23" t="n"/>
+      <c r="W126" s="23" t="n"/>
+      <c r="X126" s="23" t="n"/>
+      <c r="Y126" s="23" t="n"/>
+      <c r="Z126" s="23" t="n"/>
+      <c r="AA126" s="23" t="n"/>
+      <c r="AB126" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20" t="inlineStr">
+        <is>
+          <t>R1432</t>
+        </is>
+      </c>
+      <c r="B127" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C127" s="20" t="n"/>
+      <c r="D127" s="20" t="n"/>
+      <c r="E127" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="n"/>
+      <c r="G127" s="21" t="n"/>
+      <c r="H127" s="21" t="n"/>
+      <c r="I127" s="21" t="n"/>
+      <c r="J127" s="21" t="n"/>
+      <c r="K127" s="21" t="n"/>
+      <c r="L127" s="22" t="n"/>
+      <c r="M127" s="22" t="n"/>
+      <c r="N127" s="22" t="n"/>
+      <c r="O127" s="22" t="n"/>
+      <c r="P127" s="22" t="n"/>
+      <c r="Q127" s="22" t="n"/>
+      <c r="R127" s="22" t="n"/>
+      <c r="S127" s="22" t="n"/>
+      <c r="T127" s="23" t="n"/>
+      <c r="U127" s="23" t="n"/>
+      <c r="V127" s="23" t="n"/>
+      <c r="W127" s="23" t="n"/>
+      <c r="X127" s="23" t="n"/>
+      <c r="Y127" s="23" t="n"/>
+      <c r="Z127" s="23" t="n"/>
+      <c r="AA127" s="23" t="n"/>
+      <c r="AB127" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>R1431</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="n"/>
+      <c r="D128" s="20" t="n"/>
+      <c r="E128" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F128" s="21" t="n"/>
+      <c r="G128" s="21" t="n"/>
+      <c r="H128" s="21" t="n"/>
+      <c r="I128" s="21" t="n"/>
+      <c r="J128" s="21" t="n"/>
+      <c r="K128" s="21" t="n"/>
+      <c r="L128" s="22" t="n"/>
+      <c r="M128" s="22" t="n"/>
+      <c r="N128" s="22" t="n"/>
+      <c r="O128" s="22" t="n"/>
+      <c r="P128" s="22" t="n"/>
+      <c r="Q128" s="22" t="n"/>
+      <c r="R128" s="22" t="n"/>
+      <c r="S128" s="22" t="n"/>
+      <c r="T128" s="23" t="n"/>
+      <c r="U128" s="23" t="n"/>
+      <c r="V128" s="23" t="n"/>
+      <c r="W128" s="23" t="n"/>
+      <c r="X128" s="23" t="n"/>
+      <c r="Y128" s="23" t="n"/>
+      <c r="Z128" s="23" t="n"/>
+      <c r="AA128" s="23" t="n"/>
+      <c r="AB128" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="20" t="inlineStr">
+        <is>
+          <t>R1263</t>
+        </is>
+      </c>
+      <c r="B129" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C129" s="20" t="n"/>
+      <c r="D129" s="20" t="n"/>
+      <c r="E129" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="n"/>
+      <c r="G129" s="21" t="n"/>
+      <c r="H129" s="21" t="n"/>
+      <c r="I129" s="21" t="n"/>
+      <c r="J129" s="21" t="n"/>
+      <c r="K129" s="21" t="n"/>
+      <c r="L129" s="22" t="n"/>
+      <c r="M129" s="22" t="n"/>
+      <c r="N129" s="22" t="n"/>
+      <c r="O129" s="22" t="n"/>
+      <c r="P129" s="22" t="n"/>
+      <c r="Q129" s="22" t="n"/>
+      <c r="R129" s="22" t="n"/>
+      <c r="S129" s="22" t="n"/>
+      <c r="T129" s="23" t="n"/>
+      <c r="U129" s="23" t="n"/>
+      <c r="V129" s="23" t="n"/>
+      <c r="W129" s="23" t="n"/>
+      <c r="X129" s="23" t="n"/>
+      <c r="Y129" s="23" t="n"/>
+      <c r="Z129" s="23" t="n"/>
+      <c r="AA129" s="23" t="n"/>
+      <c r="AB129" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>R1262</t>
+        </is>
+      </c>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="n"/>
+      <c r="D130" s="20" t="n"/>
+      <c r="E130" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F130" s="21" t="n"/>
+      <c r="G130" s="21" t="n"/>
+      <c r="H130" s="21" t="n"/>
+      <c r="I130" s="21" t="n"/>
+      <c r="J130" s="21" t="n"/>
+      <c r="K130" s="21" t="n"/>
+      <c r="L130" s="22" t="n"/>
+      <c r="M130" s="22" t="n"/>
+      <c r="N130" s="22" t="n"/>
+      <c r="O130" s="22" t="n"/>
+      <c r="P130" s="22" t="n"/>
+      <c r="Q130" s="22" t="n"/>
+      <c r="R130" s="22" t="n"/>
+      <c r="S130" s="22" t="n"/>
+      <c r="T130" s="23" t="n"/>
+      <c r="U130" s="23" t="n"/>
+      <c r="V130" s="23" t="n"/>
+      <c r="W130" s="23" t="n"/>
+      <c r="X130" s="23" t="n"/>
+      <c r="Y130" s="23" t="n"/>
+      <c r="Z130" s="23" t="n"/>
+      <c r="AA130" s="23" t="n"/>
+      <c r="AB130" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="20" t="inlineStr">
+        <is>
+          <t>R1261</t>
+        </is>
+      </c>
+      <c r="B131" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C131" s="20" t="n"/>
+      <c r="D131" s="20" t="n"/>
+      <c r="E131" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="n"/>
+      <c r="G131" s="21" t="n"/>
+      <c r="H131" s="21" t="n"/>
+      <c r="I131" s="21" t="n"/>
+      <c r="J131" s="21" t="n"/>
+      <c r="K131" s="21" t="n"/>
+      <c r="L131" s="22" t="n"/>
+      <c r="M131" s="22" t="n"/>
+      <c r="N131" s="22" t="n"/>
+      <c r="O131" s="22" t="n"/>
+      <c r="P131" s="22" t="n"/>
+      <c r="Q131" s="22" t="n"/>
+      <c r="R131" s="22" t="n"/>
+      <c r="S131" s="22" t="n"/>
+      <c r="T131" s="23" t="n"/>
+      <c r="U131" s="23" t="n"/>
+      <c r="V131" s="23" t="n"/>
+      <c r="W131" s="23" t="n"/>
+      <c r="X131" s="23" t="n"/>
+      <c r="Y131" s="23" t="n"/>
+      <c r="Z131" s="23" t="n"/>
+      <c r="AA131" s="23" t="n"/>
+      <c r="AB131" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>R1177</t>
+        </is>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="n"/>
+      <c r="D132" s="20" t="n"/>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F132" s="21" t="n"/>
+      <c r="G132" s="21" t="n"/>
+      <c r="H132" s="21" t="n"/>
+      <c r="I132" s="21" t="n"/>
+      <c r="J132" s="21" t="n"/>
+      <c r="K132" s="21" t="n"/>
+      <c r="L132" s="22" t="n"/>
+      <c r="M132" s="22" t="n"/>
+      <c r="N132" s="22" t="n"/>
+      <c r="O132" s="22" t="n"/>
+      <c r="P132" s="22" t="n"/>
+      <c r="Q132" s="22" t="n"/>
+      <c r="R132" s="22" t="n"/>
+      <c r="S132" s="22" t="n"/>
+      <c r="T132" s="23" t="n"/>
+      <c r="U132" s="23" t="n"/>
+      <c r="V132" s="23" t="n"/>
+      <c r="W132" s="23" t="n"/>
+      <c r="X132" s="23" t="n"/>
+      <c r="Y132" s="23" t="n"/>
+      <c r="Z132" s="23" t="n"/>
+      <c r="AA132" s="23" t="n"/>
+      <c r="AB132" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="inlineStr">
+        <is>
+          <t>R1175</t>
+        </is>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C133" s="20" t="n"/>
+      <c r="D133" s="20" t="n"/>
+      <c r="E133" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="n"/>
+      <c r="G133" s="21" t="n"/>
+      <c r="H133" s="21" t="n"/>
+      <c r="I133" s="21" t="n"/>
+      <c r="J133" s="21" t="n"/>
+      <c r="K133" s="21" t="n"/>
+      <c r="L133" s="22" t="n"/>
+      <c r="M133" s="22" t="n"/>
+      <c r="N133" s="22" t="n"/>
+      <c r="O133" s="22" t="n"/>
+      <c r="P133" s="22" t="n"/>
+      <c r="Q133" s="22" t="n"/>
+      <c r="R133" s="22" t="n"/>
+      <c r="S133" s="22" t="n"/>
+      <c r="T133" s="23" t="n"/>
+      <c r="U133" s="23" t="n"/>
+      <c r="V133" s="23" t="n"/>
+      <c r="W133" s="23" t="n"/>
+      <c r="X133" s="23" t="n"/>
+      <c r="Y133" s="23" t="n"/>
+      <c r="Z133" s="23" t="n"/>
+      <c r="AA133" s="23" t="n"/>
+      <c r="AB133" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="20" t="inlineStr">
+        <is>
+          <t>R1174</t>
+        </is>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C134" s="20" t="n"/>
+      <c r="D134" s="20" t="n"/>
+      <c r="E134" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F134" s="21" t="n"/>
+      <c r="G134" s="21" t="n"/>
+      <c r="H134" s="21" t="n"/>
+      <c r="I134" s="21" t="n"/>
+      <c r="J134" s="21" t="n"/>
+      <c r="K134" s="21" t="n"/>
+      <c r="L134" s="22" t="n"/>
+      <c r="M134" s="22" t="n"/>
+      <c r="N134" s="22" t="n"/>
+      <c r="O134" s="22" t="n"/>
+      <c r="P134" s="22" t="n"/>
+      <c r="Q134" s="22" t="n"/>
+      <c r="R134" s="22" t="n"/>
+      <c r="S134" s="22" t="n"/>
+      <c r="T134" s="23" t="n"/>
+      <c r="U134" s="23" t="n"/>
+      <c r="V134" s="23" t="n"/>
+      <c r="W134" s="23" t="n"/>
+      <c r="X134" s="23" t="n"/>
+      <c r="Y134" s="23" t="n"/>
+      <c r="Z134" s="23" t="n"/>
+      <c r="AA134" s="23" t="n"/>
+      <c r="AB134" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>R1170</t>
+        </is>
+      </c>
+      <c r="B135" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C135" s="20" t="n"/>
+      <c r="D135" s="20" t="n"/>
+      <c r="E135" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F135" s="21" t="n"/>
+      <c r="G135" s="21" t="n"/>
+      <c r="H135" s="21" t="n"/>
+      <c r="I135" s="21" t="n"/>
+      <c r="J135" s="21" t="n"/>
+      <c r="K135" s="21" t="n"/>
+      <c r="L135" s="22" t="n"/>
+      <c r="M135" s="22" t="n"/>
+      <c r="N135" s="22" t="n"/>
+      <c r="O135" s="22" t="n"/>
+      <c r="P135" s="22" t="n"/>
+      <c r="Q135" s="22" t="n"/>
+      <c r="R135" s="22" t="n"/>
+      <c r="S135" s="22" t="n"/>
+      <c r="T135" s="23" t="n"/>
+      <c r="U135" s="23" t="n"/>
+      <c r="V135" s="23" t="n"/>
+      <c r="W135" s="23" t="n"/>
+      <c r="X135" s="23" t="n"/>
+      <c r="Y135" s="23" t="n"/>
+      <c r="Z135" s="23" t="n"/>
+      <c r="AA135" s="23" t="n"/>
+      <c r="AB135" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>R1169</t>
+        </is>
+      </c>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C136" s="20" t="n"/>
+      <c r="D136" s="20" t="n"/>
+      <c r="E136" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F136" s="21" t="n"/>
+      <c r="G136" s="21" t="n"/>
+      <c r="H136" s="21" t="n"/>
+      <c r="I136" s="21" t="n"/>
+      <c r="J136" s="21" t="n"/>
+      <c r="K136" s="21" t="n"/>
+      <c r="L136" s="22" t="n"/>
+      <c r="M136" s="22" t="n"/>
+      <c r="N136" s="22" t="n"/>
+      <c r="O136" s="22" t="n"/>
+      <c r="P136" s="22" t="n"/>
+      <c r="Q136" s="22" t="n"/>
+      <c r="R136" s="22" t="n"/>
+      <c r="S136" s="22" t="n"/>
+      <c r="T136" s="23" t="n"/>
+      <c r="U136" s="23" t="n"/>
+      <c r="V136" s="23" t="n"/>
+      <c r="W136" s="23" t="n"/>
+      <c r="X136" s="23" t="n"/>
+      <c r="Y136" s="23" t="n"/>
+      <c r="Z136" s="23" t="n"/>
+      <c r="AA136" s="23" t="n"/>
+      <c r="AB136" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>R1089</t>
+        </is>
+      </c>
+      <c r="B137" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C137" s="20" t="n"/>
+      <c r="D137" s="20" t="n"/>
+      <c r="E137" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F137" s="21" t="n"/>
+      <c r="G137" s="21" t="n"/>
+      <c r="H137" s="21" t="n"/>
+      <c r="I137" s="21" t="n"/>
+      <c r="J137" s="21" t="n"/>
+      <c r="K137" s="21" t="n"/>
+      <c r="L137" s="22" t="n"/>
+      <c r="M137" s="22" t="n"/>
+      <c r="N137" s="22" t="n"/>
+      <c r="O137" s="22" t="n"/>
+      <c r="P137" s="22" t="n"/>
+      <c r="Q137" s="22" t="n"/>
+      <c r="R137" s="22" t="n"/>
+      <c r="S137" s="22" t="n"/>
+      <c r="T137" s="23" t="n"/>
+      <c r="U137" s="23" t="n"/>
+      <c r="V137" s="23" t="n"/>
+      <c r="W137" s="23" t="n"/>
+      <c r="X137" s="23" t="n"/>
+      <c r="Y137" s="23" t="n"/>
+      <c r="Z137" s="23" t="n"/>
+      <c r="AA137" s="23" t="n"/>
+      <c r="AB137" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>R1054</t>
+        </is>
+      </c>
+      <c r="B138" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C138" s="20" t="n"/>
+      <c r="D138" s="20" t="n"/>
+      <c r="E138" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F138" s="21" t="n"/>
+      <c r="G138" s="21" t="n"/>
+      <c r="H138" s="21" t="n"/>
+      <c r="I138" s="21" t="n"/>
+      <c r="J138" s="21" t="n"/>
+      <c r="K138" s="21" t="n"/>
+      <c r="L138" s="22" t="n"/>
+      <c r="M138" s="22" t="n"/>
+      <c r="N138" s="22" t="n"/>
+      <c r="O138" s="22" t="n"/>
+      <c r="P138" s="22" t="n"/>
+      <c r="Q138" s="22" t="n"/>
+      <c r="R138" s="22" t="n"/>
+      <c r="S138" s="22" t="n"/>
+      <c r="T138" s="23" t="n"/>
+      <c r="U138" s="23" t="n"/>
+      <c r="V138" s="23" t="n"/>
+      <c r="W138" s="23" t="n"/>
+      <c r="X138" s="23" t="n"/>
+      <c r="Y138" s="23" t="n"/>
+      <c r="Z138" s="23" t="n"/>
+      <c r="AA138" s="23" t="n"/>
+      <c r="AB138" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="inlineStr">
+        <is>
+          <t>R1037</t>
+        </is>
+      </c>
+      <c r="B139" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C139" s="20" t="n"/>
+      <c r="D139" s="20" t="n"/>
+      <c r="E139" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="n"/>
+      <c r="G139" s="21" t="n"/>
+      <c r="H139" s="21" t="n"/>
+      <c r="I139" s="21" t="n"/>
+      <c r="J139" s="21" t="n"/>
+      <c r="K139" s="21" t="n"/>
+      <c r="L139" s="22" t="n"/>
+      <c r="M139" s="22" t="n"/>
+      <c r="N139" s="22" t="n"/>
+      <c r="O139" s="22" t="n"/>
+      <c r="P139" s="22" t="n"/>
+      <c r="Q139" s="22" t="n"/>
+      <c r="R139" s="22" t="n"/>
+      <c r="S139" s="22" t="n"/>
+      <c r="T139" s="23" t="n"/>
+      <c r="U139" s="23" t="n"/>
+      <c r="V139" s="23" t="n"/>
+      <c r="W139" s="23" t="n"/>
+      <c r="X139" s="23" t="n"/>
+      <c r="Y139" s="23" t="n"/>
+      <c r="Z139" s="23" t="n"/>
+      <c r="AA139" s="23" t="n"/>
+      <c r="AB139" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>L136</t>
+        </is>
+      </c>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C140" s="20" t="n"/>
+      <c r="D140" s="20" t="n"/>
+      <c r="E140" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F140" s="21" t="n"/>
+      <c r="G140" s="21" t="n"/>
+      <c r="H140" s="21" t="n"/>
+      <c r="I140" s="21" t="n"/>
+      <c r="J140" s="21" t="n"/>
+      <c r="K140" s="21" t="n"/>
+      <c r="L140" s="22" t="n"/>
+      <c r="M140" s="22" t="n"/>
+      <c r="N140" s="22" t="n"/>
+      <c r="O140" s="22" t="n"/>
+      <c r="P140" s="22" t="n"/>
+      <c r="Q140" s="22" t="n"/>
+      <c r="R140" s="22" t="n"/>
+      <c r="S140" s="22" t="n"/>
+      <c r="T140" s="23" t="n"/>
+      <c r="U140" s="23" t="n"/>
+      <c r="V140" s="23" t="n"/>
+      <c r="W140" s="23" t="n"/>
+      <c r="X140" s="23" t="n"/>
+      <c r="Y140" s="23" t="n"/>
+      <c r="Z140" s="23" t="n"/>
+      <c r="AA140" s="23" t="n"/>
+      <c r="AB140" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="inlineStr">
+        <is>
+          <t>L135</t>
+        </is>
+      </c>
+      <c r="B141" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C141" s="20" t="n"/>
+      <c r="D141" s="20" t="n"/>
+      <c r="E141" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F141" s="21" t="n"/>
+      <c r="G141" s="21" t="n"/>
+      <c r="H141" s="21" t="n"/>
+      <c r="I141" s="21" t="n"/>
+      <c r="J141" s="21" t="n"/>
+      <c r="K141" s="21" t="n"/>
+      <c r="L141" s="22" t="n"/>
+      <c r="M141" s="22" t="n"/>
+      <c r="N141" s="22" t="n"/>
+      <c r="O141" s="22" t="n"/>
+      <c r="P141" s="22" t="n"/>
+      <c r="Q141" s="22" t="n"/>
+      <c r="R141" s="22" t="n"/>
+      <c r="S141" s="22" t="n"/>
+      <c r="T141" s="23" t="n"/>
+      <c r="U141" s="23" t="n"/>
+      <c r="V141" s="23" t="n"/>
+      <c r="W141" s="23" t="n"/>
+      <c r="X141" s="23" t="n"/>
+      <c r="Y141" s="23" t="n"/>
+      <c r="Z141" s="23" t="n"/>
+      <c r="AA141" s="23" t="n"/>
+      <c r="AB141" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20" t="inlineStr">
+        <is>
+          <t>L134</t>
+        </is>
+      </c>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C142" s="20" t="n"/>
+      <c r="D142" s="20" t="n"/>
+      <c r="E142" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F142" s="21" t="n"/>
+      <c r="G142" s="21" t="n"/>
+      <c r="H142" s="21" t="n"/>
+      <c r="I142" s="21" t="n"/>
+      <c r="J142" s="21" t="n"/>
+      <c r="K142" s="21" t="n"/>
+      <c r="L142" s="22" t="n"/>
+      <c r="M142" s="22" t="n"/>
+      <c r="N142" s="22" t="n"/>
+      <c r="O142" s="22" t="n"/>
+      <c r="P142" s="22" t="n"/>
+      <c r="Q142" s="22" t="n"/>
+      <c r="R142" s="22" t="n"/>
+      <c r="S142" s="22" t="n"/>
+      <c r="T142" s="23" t="n"/>
+      <c r="U142" s="23" t="n"/>
+      <c r="V142" s="23" t="n"/>
+      <c r="W142" s="23" t="n"/>
+      <c r="X142" s="23" t="n"/>
+      <c r="Y142" s="23" t="n"/>
+      <c r="Z142" s="23" t="n"/>
+      <c r="AA142" s="23" t="n"/>
+      <c r="AB142" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20" t="inlineStr">
+        <is>
+          <t>L133</t>
+        </is>
+      </c>
+      <c r="B143" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C143" s="20" t="n"/>
+      <c r="D143" s="20" t="n"/>
+      <c r="E143" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F143" s="21" t="n"/>
+      <c r="G143" s="21" t="n"/>
+      <c r="H143" s="21" t="n"/>
+      <c r="I143" s="21" t="n"/>
+      <c r="J143" s="21" t="n"/>
+      <c r="K143" s="21" t="n"/>
+      <c r="L143" s="22" t="n"/>
+      <c r="M143" s="22" t="n"/>
+      <c r="N143" s="22" t="n"/>
+      <c r="O143" s="22" t="n"/>
+      <c r="P143" s="22" t="n"/>
+      <c r="Q143" s="22" t="n"/>
+      <c r="R143" s="22" t="n"/>
+      <c r="S143" s="22" t="n"/>
+      <c r="T143" s="23" t="n"/>
+      <c r="U143" s="23" t="n"/>
+      <c r="V143" s="23" t="n"/>
+      <c r="W143" s="23" t="n"/>
+      <c r="X143" s="23" t="n"/>
+      <c r="Y143" s="23" t="n"/>
+      <c r="Z143" s="23" t="n"/>
+      <c r="AA143" s="23" t="n"/>
+      <c r="AB143" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>L132</t>
+        </is>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C144" s="20" t="n"/>
+      <c r="D144" s="20" t="n"/>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F144" s="21" t="n"/>
+      <c r="G144" s="21" t="n"/>
+      <c r="H144" s="21" t="n"/>
+      <c r="I144" s="21" t="n"/>
+      <c r="J144" s="21" t="n"/>
+      <c r="K144" s="21" t="n"/>
+      <c r="L144" s="22" t="n"/>
+      <c r="M144" s="22" t="n"/>
+      <c r="N144" s="22" t="n"/>
+      <c r="O144" s="22" t="n"/>
+      <c r="P144" s="22" t="n"/>
+      <c r="Q144" s="22" t="n"/>
+      <c r="R144" s="22" t="n"/>
+      <c r="S144" s="22" t="n"/>
+      <c r="T144" s="23" t="n"/>
+      <c r="U144" s="23" t="n"/>
+      <c r="V144" s="23" t="n"/>
+      <c r="W144" s="23" t="n"/>
+      <c r="X144" s="23" t="n"/>
+      <c r="Y144" s="23" t="n"/>
+      <c r="Z144" s="23" t="n"/>
+      <c r="AA144" s="23" t="n"/>
+      <c r="AB144" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="20" t="inlineStr">
+        <is>
+          <t>L131</t>
+        </is>
+      </c>
+      <c r="B145" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C145" s="20" t="n"/>
+      <c r="D145" s="20" t="n"/>
+      <c r="E145" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F145" s="21" t="n"/>
+      <c r="G145" s="21" t="n"/>
+      <c r="H145" s="21" t="n"/>
+      <c r="I145" s="21" t="n"/>
+      <c r="J145" s="21" t="n"/>
+      <c r="K145" s="21" t="n"/>
+      <c r="L145" s="22" t="n"/>
+      <c r="M145" s="22" t="n"/>
+      <c r="N145" s="22" t="n"/>
+      <c r="O145" s="22" t="n"/>
+      <c r="P145" s="22" t="n"/>
+      <c r="Q145" s="22" t="n"/>
+      <c r="R145" s="22" t="n"/>
+      <c r="S145" s="22" t="n"/>
+      <c r="T145" s="23" t="n"/>
+      <c r="U145" s="23" t="n"/>
+      <c r="V145" s="23" t="n"/>
+      <c r="W145" s="23" t="n"/>
+      <c r="X145" s="23" t="n"/>
+      <c r="Y145" s="23" t="n"/>
+      <c r="Z145" s="23" t="n"/>
+      <c r="AA145" s="23" t="n"/>
+      <c r="AB145" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="inlineStr">
+        <is>
+          <t>L130</t>
+        </is>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C146" s="20" t="n"/>
+      <c r="D146" s="20" t="n"/>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F146" s="21" t="n"/>
+      <c r="G146" s="21" t="n"/>
+      <c r="H146" s="21" t="n"/>
+      <c r="I146" s="21" t="n"/>
+      <c r="J146" s="21" t="n"/>
+      <c r="K146" s="21" t="n"/>
+      <c r="L146" s="22" t="n"/>
+      <c r="M146" s="22" t="n"/>
+      <c r="N146" s="22" t="n"/>
+      <c r="O146" s="22" t="n"/>
+      <c r="P146" s="22" t="n"/>
+      <c r="Q146" s="22" t="n"/>
+      <c r="R146" s="22" t="n"/>
+      <c r="S146" s="22" t="n"/>
+      <c r="T146" s="23" t="n"/>
+      <c r="U146" s="23" t="n"/>
+      <c r="V146" s="23" t="n"/>
+      <c r="W146" s="23" t="n"/>
+      <c r="X146" s="23" t="n"/>
+      <c r="Y146" s="23" t="n"/>
+      <c r="Z146" s="23" t="n"/>
+      <c r="AA146" s="23" t="n"/>
+      <c r="AB146" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20" t="inlineStr">
+        <is>
+          <t>L129</t>
+        </is>
+      </c>
+      <c r="B147" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C147" s="20" t="n"/>
+      <c r="D147" s="20" t="n"/>
+      <c r="E147" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F147" s="21" t="n"/>
+      <c r="G147" s="21" t="n"/>
+      <c r="H147" s="21" t="n"/>
+      <c r="I147" s="21" t="n"/>
+      <c r="J147" s="21" t="n"/>
+      <c r="K147" s="21" t="n"/>
+      <c r="L147" s="22" t="n"/>
+      <c r="M147" s="22" t="n"/>
+      <c r="N147" s="22" t="n"/>
+      <c r="O147" s="22" t="n"/>
+      <c r="P147" s="22" t="n"/>
+      <c r="Q147" s="22" t="n"/>
+      <c r="R147" s="22" t="n"/>
+      <c r="S147" s="22" t="n"/>
+      <c r="T147" s="23" t="n"/>
+      <c r="U147" s="23" t="n"/>
+      <c r="V147" s="23" t="n"/>
+      <c r="W147" s="23" t="n"/>
+      <c r="X147" s="23" t="n"/>
+      <c r="Y147" s="23" t="n"/>
+      <c r="Z147" s="23" t="n"/>
+      <c r="AA147" s="23" t="n"/>
+      <c r="AB147" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20" t="inlineStr">
+        <is>
+          <t>L128</t>
+        </is>
+      </c>
+      <c r="B148" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C148" s="20" t="n"/>
+      <c r="D148" s="20" t="n"/>
+      <c r="E148" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F148" s="21" t="n"/>
+      <c r="G148" s="21" t="n"/>
+      <c r="H148" s="21" t="n"/>
+      <c r="I148" s="21" t="n"/>
+      <c r="J148" s="21" t="n"/>
+      <c r="K148" s="21" t="n"/>
+      <c r="L148" s="22" t="n"/>
+      <c r="M148" s="22" t="n"/>
+      <c r="N148" s="22" t="n"/>
+      <c r="O148" s="22" t="n"/>
+      <c r="P148" s="22" t="n"/>
+      <c r="Q148" s="22" t="n"/>
+      <c r="R148" s="22" t="n"/>
+      <c r="S148" s="22" t="n"/>
+      <c r="T148" s="23" t="n"/>
+      <c r="U148" s="23" t="n"/>
+      <c r="V148" s="23" t="n"/>
+      <c r="W148" s="23" t="n"/>
+      <c r="X148" s="23" t="n"/>
+      <c r="Y148" s="23" t="n"/>
+      <c r="Z148" s="23" t="n"/>
+      <c r="AA148" s="23" t="n"/>
+      <c r="AB148" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="20" t="inlineStr">
+        <is>
+          <t>L127</t>
+        </is>
+      </c>
+      <c r="B149" s="20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C149" s="20" t="n"/>
+      <c r="D149" s="20" t="n"/>
+      <c r="E149" s="20" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="F149" s="21" t="n"/>
+      <c r="G149" s="21" t="n"/>
+      <c r="H149" s="21" t="n"/>
+      <c r="I149" s="21" t="n"/>
+      <c r="J149" s="21" t="n"/>
+      <c r="K149" s="21" t="n"/>
+      <c r="L149" s="22" t="n"/>
+      <c r="M149" s="22" t="n"/>
+      <c r="N149" s="22" t="n"/>
+      <c r="O149" s="22" t="n"/>
+      <c r="P149" s="22" t="n"/>
+      <c r="Q149" s="22" t="n"/>
+      <c r="R149" s="22" t="n"/>
+      <c r="S149" s="22" t="n"/>
+      <c r="T149" s="23" t="n"/>
+      <c r="U149" s="23" t="n"/>
+      <c r="V149" s="23" t="n"/>
+      <c r="W149" s="23" t="n"/>
+      <c r="X149" s="23" t="n"/>
+      <c r="Y149" s="23" t="n"/>
+      <c r="Z149" s="23" t="n"/>
+      <c r="AA149" s="23" t="n"/>
+      <c r="AB149" s="24" t="inlineStr">
+        <is>
+          <t>catalog: Sets</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB1"/>
+  <autoFilter ref="A1:AB149"/>
   <dataValidations count="13">
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Include?" error="Choose one of: Y, N" promptTitle="Include?" prompt="Y to include this row in the next run, N to stage it without uploading. Blank counts as Y." type="list">
       <formula1>"Y,N"</formula1>
